--- a/Data/Final Data/Selected ESG ETFs.xlsx
+++ b/Data/Final Data/Selected ESG ETFs.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nityaarya/Downloads/blackrock-esg-etf-study/blackrock-esg-etf-study/Data/Processed Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nityaarya/Downloads/Project/blackrock-esg-etf-study/Data/Final Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{667E2308-110D-204C-845E-77E1852E45DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B5B977C-42B6-BF4F-AE45-0426195CC72B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16420" xr2:uid="{A61AF8B7-3585-6343-B574-5450E5520343}"/>
   </bookViews>
@@ -722,9 +722,6 @@
     <t>—</t>
   </si>
   <si>
-    <t>Stated exclusions / business screens (from iShares)</t>
-  </si>
-  <si>
     <t>Civilian firearms; controversial weapons; tobacco; thermal coal; oil sands.</t>
   </si>
   <si>
@@ -1011,6 +1008,9 @@
   </si>
   <si>
     <t>$1.67M</t>
+  </si>
+  <si>
+    <t>Stated exclusions  (from iShares)</t>
   </si>
 </sst>
 </file>
@@ -1176,7 +1176,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1198,6 +1198,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1218,13 +1221,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="10" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1578,9 +1577,9 @@
     <col min="1" max="1" width="6.33203125" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="52.83203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="14.33203125" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="11" hidden="1" customWidth="1"/>
     <col min="7" max="7" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.83203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19.5" bestFit="1" customWidth="1"/>
@@ -1624,15 +1623,15 @@
     <col min="47" max="47" width="7.33203125" bestFit="1" customWidth="1"/>
     <col min="48" max="48" width="9.83203125" bestFit="1" customWidth="1"/>
     <col min="49" max="49" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="19.1640625" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="20.1640625" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="21" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="19.1640625" hidden="1" customWidth="1"/>
+    <col min="51" max="51" width="11.5" hidden="1" customWidth="1"/>
+    <col min="52" max="52" width="18.6640625" hidden="1" customWidth="1"/>
+    <col min="53" max="53" width="20.1640625" hidden="1" customWidth="1"/>
+    <col min="54" max="54" width="11.5" hidden="1" customWidth="1"/>
+    <col min="55" max="55" width="12.33203125" hidden="1" customWidth="1"/>
+    <col min="56" max="56" width="21" hidden="1" customWidth="1"/>
+    <col min="57" max="57" width="12.5" hidden="1" customWidth="1"/>
+    <col min="58" max="58" width="18.33203125" hidden="1" customWidth="1"/>
     <col min="59" max="59" width="193.1640625" customWidth="1"/>
     <col min="60" max="60" width="22.33203125" bestFit="1" customWidth="1"/>
     <col min="61" max="61" width="23.1640625" bestFit="1" customWidth="1"/>
@@ -1678,197 +1677,197 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:102" x14ac:dyDescent="0.2">
-      <c r="A1" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="17" t="s">
+      <c r="A1" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="21" t="s">
         <v>193</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="F1" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="G1" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="17" t="s">
+      <c r="H1" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="17" t="s">
+      <c r="I1" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="17" t="s">
+      <c r="J1" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="17" t="s">
+      <c r="K1" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="17" t="s">
+      <c r="L1" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="17" t="s">
+      <c r="M1" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="17" t="s">
+      <c r="N1" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="17" t="s">
+      <c r="O1" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="17" t="s">
+      <c r="P1" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="17" t="s">
+      <c r="Q1" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="17" t="s">
+      <c r="R1" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="17"/>
-      <c r="T1" s="17"/>
-      <c r="U1" s="17"/>
-      <c r="V1" s="17" t="s">
+      <c r="S1" s="20"/>
+      <c r="T1" s="20"/>
+      <c r="U1" s="20"/>
+      <c r="V1" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="W1" s="17"/>
-      <c r="X1" s="17"/>
-      <c r="Y1" s="17"/>
-      <c r="Z1" s="17"/>
-      <c r="AA1" s="17"/>
-      <c r="AB1" s="17"/>
-      <c r="AC1" s="17" t="s">
+      <c r="W1" s="20"/>
+      <c r="X1" s="20"/>
+      <c r="Y1" s="20"/>
+      <c r="Z1" s="20"/>
+      <c r="AA1" s="20"/>
+      <c r="AB1" s="20"/>
+      <c r="AC1" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="AD1" s="17"/>
-      <c r="AE1" s="17"/>
-      <c r="AF1" s="17"/>
-      <c r="AG1" s="17"/>
-      <c r="AH1" s="17"/>
-      <c r="AI1" s="17"/>
-      <c r="AJ1" s="17" t="s">
+      <c r="AD1" s="20"/>
+      <c r="AE1" s="20"/>
+      <c r="AF1" s="20"/>
+      <c r="AG1" s="20"/>
+      <c r="AH1" s="20"/>
+      <c r="AI1" s="20"/>
+      <c r="AJ1" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="AK1" s="17"/>
-      <c r="AL1" s="17"/>
-      <c r="AM1" s="17"/>
-      <c r="AN1" s="17"/>
-      <c r="AO1" s="17"/>
-      <c r="AP1" s="17"/>
-      <c r="AQ1" s="17" t="s">
+      <c r="AK1" s="20"/>
+      <c r="AL1" s="20"/>
+      <c r="AM1" s="20"/>
+      <c r="AN1" s="20"/>
+      <c r="AO1" s="20"/>
+      <c r="AP1" s="20"/>
+      <c r="AQ1" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="AR1" s="17"/>
-      <c r="AS1" s="17"/>
-      <c r="AT1" s="17"/>
-      <c r="AU1" s="17"/>
-      <c r="AV1" s="17"/>
-      <c r="AW1" s="17"/>
-      <c r="AX1" s="17" t="s">
+      <c r="AR1" s="20"/>
+      <c r="AS1" s="20"/>
+      <c r="AT1" s="20"/>
+      <c r="AU1" s="20"/>
+      <c r="AV1" s="20"/>
+      <c r="AW1" s="20"/>
+      <c r="AX1" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="AY1" s="17"/>
-      <c r="AZ1" s="17"/>
-      <c r="BA1" s="17"/>
-      <c r="BB1" s="17"/>
-      <c r="BC1" s="17" t="s">
+      <c r="AY1" s="20"/>
+      <c r="AZ1" s="20"/>
+      <c r="BA1" s="20"/>
+      <c r="BB1" s="20"/>
+      <c r="BC1" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="BD1" s="17"/>
-      <c r="BE1" s="17"/>
-      <c r="BF1" s="17"/>
-      <c r="BG1" s="23" t="s">
-        <v>228</v>
-      </c>
-      <c r="BH1" s="21" t="s">
+      <c r="BD1" s="20"/>
+      <c r="BE1" s="20"/>
+      <c r="BF1" s="20"/>
+      <c r="BG1" s="26" t="s">
+        <v>324</v>
+      </c>
+      <c r="BH1" s="24" t="s">
         <v>217</v>
       </c>
-      <c r="BI1" s="21"/>
-      <c r="BJ1" s="21"/>
-      <c r="BK1" s="24" t="s">
-        <v>246</v>
-      </c>
-      <c r="BL1" s="24"/>
-      <c r="BM1" s="24"/>
-      <c r="BN1" s="26" t="s">
+      <c r="BI1" s="24"/>
+      <c r="BJ1" s="24"/>
+      <c r="BK1" s="27" t="s">
+        <v>245</v>
+      </c>
+      <c r="BL1" s="27"/>
+      <c r="BM1" s="27"/>
+      <c r="BN1" s="28" t="s">
+        <v>252</v>
+      </c>
+      <c r="BO1" s="28"/>
+      <c r="BP1" s="28"/>
+      <c r="BQ1" s="29" t="s">
         <v>253</v>
       </c>
-      <c r="BO1" s="26"/>
-      <c r="BP1" s="26"/>
-      <c r="BQ1" s="27" t="s">
-        <v>254</v>
-      </c>
-      <c r="BR1" s="27"/>
-      <c r="BS1" s="27"/>
-      <c r="BT1" s="28" t="s">
-        <v>257</v>
-      </c>
-      <c r="BU1" s="28"/>
-      <c r="BV1" s="28"/>
-      <c r="BW1" s="22" t="s">
+      <c r="BR1" s="29"/>
+      <c r="BS1" s="29"/>
+      <c r="BT1" s="30" t="s">
+        <v>256</v>
+      </c>
+      <c r="BU1" s="30"/>
+      <c r="BV1" s="30"/>
+      <c r="BW1" s="25" t="s">
         <v>218</v>
       </c>
-      <c r="BX1" s="22"/>
-      <c r="BY1" s="22"/>
-      <c r="BZ1" s="22"/>
-      <c r="CA1" s="22"/>
-      <c r="CB1" s="22"/>
-      <c r="CC1" s="22"/>
-      <c r="CD1" s="20" t="s">
+      <c r="BX1" s="25"/>
+      <c r="BY1" s="25"/>
+      <c r="BZ1" s="25"/>
+      <c r="CA1" s="25"/>
+      <c r="CB1" s="25"/>
+      <c r="CC1" s="25"/>
+      <c r="CD1" s="23" t="s">
         <v>219</v>
       </c>
-      <c r="CE1" s="20"/>
-      <c r="CF1" s="20"/>
+      <c r="CE1" s="23"/>
+      <c r="CF1" s="23"/>
       <c r="CG1" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="CH1" s="13" t="s">
+      <c r="CH1" s="16" t="s">
         <v>194</v>
       </c>
-      <c r="CI1" s="14"/>
-      <c r="CJ1" s="14"/>
-      <c r="CK1" s="14"/>
-      <c r="CL1" s="14"/>
-      <c r="CM1" s="14"/>
-      <c r="CN1" s="14"/>
-      <c r="CO1" s="14"/>
-      <c r="CP1" s="14"/>
-      <c r="CQ1" s="14"/>
-      <c r="CR1" s="15" t="s">
+      <c r="CI1" s="17"/>
+      <c r="CJ1" s="17"/>
+      <c r="CK1" s="17"/>
+      <c r="CL1" s="17"/>
+      <c r="CM1" s="17"/>
+      <c r="CN1" s="17"/>
+      <c r="CO1" s="17"/>
+      <c r="CP1" s="17"/>
+      <c r="CQ1" s="17"/>
+      <c r="CR1" s="18" t="s">
         <v>209</v>
       </c>
-      <c r="CS1" s="16"/>
-      <c r="CT1" s="16"/>
-      <c r="CU1" s="16"/>
-      <c r="CV1" s="16"/>
-      <c r="CW1" s="16"/>
-      <c r="CX1" s="16"/>
+      <c r="CS1" s="19"/>
+      <c r="CT1" s="19"/>
+      <c r="CU1" s="19"/>
+      <c r="CV1" s="19"/>
+      <c r="CW1" s="19"/>
+      <c r="CX1" s="19"/>
     </row>
     <row r="2" spans="1:102" x14ac:dyDescent="0.2">
-      <c r="A2" s="19"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
-      <c r="L2" s="17"/>
-      <c r="M2" s="17"/>
-      <c r="N2" s="17"/>
-      <c r="O2" s="17"/>
-      <c r="P2" s="17"/>
-      <c r="Q2" s="17"/>
+      <c r="A2" s="22"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
       <c r="R2" s="1" t="s">
         <v>23</v>
       </c>
@@ -1992,7 +1991,7 @@
       <c r="BF2" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="BG2" s="23"/>
+      <c r="BG2" s="26"/>
       <c r="BH2" s="2" t="s">
         <v>114</v>
       </c>
@@ -2003,40 +2002,40 @@
         <v>116</v>
       </c>
       <c r="BK2" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="BL2" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="BM2" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="BN2" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="BO2" s="13" t="s">
         <v>251</v>
       </c>
-      <c r="BM2" s="2" t="s">
+      <c r="BP2" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="BQ2" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="BN2" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="BO2" s="25" t="s">
-        <v>252</v>
-      </c>
-      <c r="BP2" s="2" t="s">
+      <c r="BR2" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="BS2" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="BT2" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="BQ2" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="BR2" s="25" t="s">
-        <v>255</v>
-      </c>
-      <c r="BS2" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="BT2" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="BU2" s="25" t="s">
-        <v>258</v>
+      <c r="BU2" s="13" t="s">
+        <v>257</v>
       </c>
       <c r="BV2" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="BW2" s="2" t="s">
         <v>121</v>
@@ -2299,7 +2298,7 @@
         <v>50</v>
       </c>
       <c r="BG3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="BH3" s="9">
         <v>6.5000000000000002E-2</v>
@@ -2314,36 +2313,36 @@
         <v>0.21</v>
       </c>
       <c r="BL3" t="s">
-        <v>294</v>
-      </c>
-      <c r="BM3" s="30">
+        <v>293</v>
+      </c>
+      <c r="BM3">
         <v>23</v>
       </c>
       <c r="BN3" s="11">
         <v>0.14000000000000001</v>
       </c>
       <c r="BO3" s="11" t="s">
-        <v>250</v>
-      </c>
-      <c r="BP3" s="31">
+        <v>249</v>
+      </c>
+      <c r="BP3" s="15">
         <v>36</v>
       </c>
       <c r="BQ3" s="9">
         <v>7.4999999999999997E-3</v>
       </c>
       <c r="BR3" t="s">
-        <v>256</v>
-      </c>
-      <c r="BS3" s="30">
+        <v>255</v>
+      </c>
+      <c r="BS3">
         <v>3</v>
       </c>
       <c r="BT3" s="9">
         <v>3.3399999999999999E-2</v>
       </c>
       <c r="BU3" t="s">
-        <v>259</v>
-      </c>
-      <c r="BV3" s="30">
+        <v>258</v>
+      </c>
+      <c r="BV3">
         <v>14</v>
       </c>
       <c r="BW3" s="12" t="s">
@@ -2607,7 +2606,7 @@
         <v>50</v>
       </c>
       <c r="BG4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BH4" s="9">
         <v>0.10100000000000001</v>
@@ -2622,36 +2621,36 @@
         <v>3.5499999999999997E-2</v>
       </c>
       <c r="BL4" t="s">
-        <v>249</v>
-      </c>
-      <c r="BM4" s="30">
+        <v>248</v>
+      </c>
+      <c r="BM4">
         <v>9</v>
       </c>
       <c r="BN4" s="11">
         <v>0.2</v>
       </c>
       <c r="BO4" t="s">
-        <v>260</v>
-      </c>
-      <c r="BP4" s="31">
+        <v>259</v>
+      </c>
+      <c r="BP4" s="15">
         <v>56</v>
       </c>
       <c r="BQ4" s="9">
         <v>9.9000000000000008E-3</v>
       </c>
       <c r="BR4" t="s">
-        <v>261</v>
-      </c>
-      <c r="BS4" s="30">
+        <v>260</v>
+      </c>
+      <c r="BS4">
         <v>1</v>
       </c>
       <c r="BT4" s="11">
         <v>4.8099999999999997E-2</v>
       </c>
       <c r="BU4" t="s">
-        <v>283</v>
-      </c>
-      <c r="BV4" s="30">
+        <v>282</v>
+      </c>
+      <c r="BV4">
         <v>19</v>
       </c>
       <c r="BW4" t="s">
@@ -2915,13 +2914,13 @@
         <v>50</v>
       </c>
       <c r="BG5" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BH5" s="9">
         <v>5.04E-2</v>
       </c>
       <c r="BI5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="BJ5">
         <v>20</v>
@@ -2930,36 +2929,36 @@
         <v>0</v>
       </c>
       <c r="BL5" t="s">
-        <v>262</v>
-      </c>
-      <c r="BM5" s="30">
+        <v>261</v>
+      </c>
+      <c r="BM5">
         <v>0</v>
       </c>
       <c r="BN5" s="9">
         <v>4.3499999999999997E-2</v>
       </c>
-      <c r="BO5" s="30" t="s">
-        <v>285</v>
-      </c>
-      <c r="BP5" s="31">
+      <c r="BO5" t="s">
+        <v>284</v>
+      </c>
+      <c r="BP5" s="15">
         <v>17</v>
       </c>
       <c r="BQ5" s="11">
         <v>0</v>
       </c>
       <c r="BR5" t="s">
-        <v>262</v>
-      </c>
-      <c r="BS5" s="30">
+        <v>261</v>
+      </c>
+      <c r="BS5">
         <v>0</v>
       </c>
       <c r="BT5" s="9">
         <v>1.3100000000000001E-2</v>
       </c>
       <c r="BU5" t="s">
-        <v>263</v>
-      </c>
-      <c r="BV5" s="30">
+        <v>262</v>
+      </c>
+      <c r="BV5">
         <v>10</v>
       </c>
       <c r="BW5" t="s">
@@ -3223,13 +3222,13 @@
         <v>50</v>
       </c>
       <c r="BG6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="BH6" s="9">
         <v>2.3E-2</v>
       </c>
       <c r="BI6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="BJ6">
         <v>23</v>
@@ -3238,7 +3237,7 @@
         <v>0.24</v>
       </c>
       <c r="BL6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="BM6">
         <v>20</v>
@@ -3247,7 +3246,7 @@
         <v>7.7499999999999999E-2</v>
       </c>
       <c r="BO6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="BP6">
         <v>35</v>
@@ -3256,7 +3255,7 @@
         <v>7.3000000000000001E-3</v>
       </c>
       <c r="BR6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="BS6">
         <v>1</v>
@@ -3265,7 +3264,7 @@
         <v>1.9800000000000002E-2</v>
       </c>
       <c r="BU6" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="BV6">
         <v>8</v>
@@ -3531,7 +3530,7 @@
         <v>50</v>
       </c>
       <c r="BG7" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="BH7" s="9">
         <v>4.3700000000000003E-2</v>
@@ -3546,7 +3545,7 @@
         <v>0.15</v>
       </c>
       <c r="BL7" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="BM7">
         <v>10</v>
@@ -3555,7 +3554,7 @@
         <v>0.09</v>
       </c>
       <c r="BO7" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="BP7">
         <v>17</v>
@@ -3564,7 +3563,7 @@
         <v>3.7000000000000002E-3</v>
       </c>
       <c r="BR7" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="BS7">
         <v>1</v>
@@ -3573,7 +3572,7 @@
         <v>1.9099999999999999E-2</v>
       </c>
       <c r="BU7" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="BV7">
         <v>5</v>
@@ -3839,13 +3838,13 @@
         <v>50</v>
       </c>
       <c r="BG8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="BH8" s="9">
         <v>5.4600000000000003E-2</v>
       </c>
       <c r="BI8" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="BJ8">
         <v>26</v>
@@ -3854,7 +3853,7 @@
         <v>0.23</v>
       </c>
       <c r="BL8" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="BM8">
         <v>20</v>
@@ -3863,7 +3862,7 @@
         <v>0.17</v>
       </c>
       <c r="BO8" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="BP8">
         <v>29</v>
@@ -3872,7 +3871,7 @@
         <v>1.4500000000000001E-2</v>
       </c>
       <c r="BR8" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="BS8">
         <v>3</v>
@@ -3881,7 +3880,7 @@
         <v>1.3899999999999999E-2</v>
       </c>
       <c r="BU8" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="BV8">
         <v>7</v>
@@ -4147,7 +4146,7 @@
         <v>50</v>
       </c>
       <c r="BG9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="BH9" s="9">
         <v>1.0800000000000001E-2</v>
@@ -4162,7 +4161,7 @@
         <v>0.2</v>
       </c>
       <c r="BL9" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="BM9">
         <v>12</v>
@@ -4171,7 +4170,7 @@
         <v>7.8700000000000006E-2</v>
       </c>
       <c r="BO9" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="BP9">
         <v>6</v>
@@ -4180,7 +4179,7 @@
         <v>0</v>
       </c>
       <c r="BR9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="BS9">
         <v>0</v>
@@ -4189,7 +4188,7 @@
         <v>5.4999999999999997E-3</v>
       </c>
       <c r="BU9" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="BV9">
         <v>3</v>
@@ -4455,7 +4454,7 @@
         <v>50</v>
       </c>
       <c r="BG10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="BH10" s="9">
         <v>6.2899999999999998E-2</v>
@@ -4470,7 +4469,7 @@
         <v>1.9599999999999999E-2</v>
       </c>
       <c r="BL10" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="BM10">
         <v>15</v>
@@ -4479,7 +4478,7 @@
         <v>1.9599999999999999E-2</v>
       </c>
       <c r="BO10" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="BP10">
         <v>12</v>
@@ -4488,7 +4487,7 @@
         <v>2.2000000000000001E-3</v>
       </c>
       <c r="BR10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="BS10">
         <v>2</v>
@@ -4497,7 +4496,7 @@
         <v>4.9299999999999997E-2</v>
       </c>
       <c r="BU10" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="BV10">
         <v>34</v>
@@ -4763,7 +4762,7 @@
         <v>50</v>
       </c>
       <c r="BG11" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="BH11" s="9">
         <v>0.2215</v>
@@ -4778,7 +4777,7 @@
         <v>0</v>
       </c>
       <c r="BL11" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="BM11">
         <v>0</v>
@@ -4787,7 +4786,7 @@
         <v>0</v>
       </c>
       <c r="BO11" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="BP11">
         <v>0</v>
@@ -4796,7 +4795,7 @@
         <v>0</v>
       </c>
       <c r="BR11" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="BS11">
         <v>0</v>
@@ -4805,7 +4804,7 @@
         <v>0</v>
       </c>
       <c r="BU11" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="BV11">
         <v>0</v>
@@ -5071,7 +5070,7 @@
         <v>50</v>
       </c>
       <c r="BG12" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="BH12" s="9">
         <v>7.7700000000000005E-2</v>
@@ -5086,7 +5085,7 @@
         <v>0.19</v>
       </c>
       <c r="BL12" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="BM12">
         <v>23</v>
@@ -5095,7 +5094,7 @@
         <v>0.12</v>
       </c>
       <c r="BO12" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="BP12">
         <v>26</v>
@@ -5104,7 +5103,7 @@
         <v>2.5999999999999999E-3</v>
       </c>
       <c r="BR12" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="BS12">
         <v>2</v>
@@ -5113,7 +5112,7 @@
         <v>4.5499999999999999E-2</v>
       </c>
       <c r="BU12" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="BV12">
         <v>15</v>
@@ -5379,7 +5378,7 @@
         <v>50</v>
       </c>
       <c r="BG13" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="BH13" s="9">
         <v>9.1000000000000004E-3</v>
@@ -5394,7 +5393,7 @@
         <v>2.5100000000000001E-2</v>
       </c>
       <c r="BL13" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="BM13">
         <v>11</v>
@@ -5403,7 +5402,7 @@
         <v>4.4900000000000002E-2</v>
       </c>
       <c r="BO13" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="BP13">
         <v>19</v>
@@ -5412,7 +5411,7 @@
         <v>5.7999999999999996E-3</v>
       </c>
       <c r="BR13" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="BS13">
         <v>1</v>
@@ -5421,7 +5420,7 @@
         <v>2.8899999999999999E-2</v>
       </c>
       <c r="BU13" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="BV13">
         <v>10</v>
@@ -5687,7 +5686,7 @@
         <v>50</v>
       </c>
       <c r="BG14" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="BH14" s="9">
         <v>4.19E-2</v>
@@ -5702,7 +5701,7 @@
         <v>0.23</v>
       </c>
       <c r="BL14" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="BM14">
         <v>20</v>
@@ -5711,7 +5710,7 @@
         <v>0.12</v>
       </c>
       <c r="BO14" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="BP14">
         <v>55</v>
@@ -5720,7 +5719,7 @@
         <v>2.3400000000000001E-2</v>
       </c>
       <c r="BR14" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="BS14">
         <v>13</v>
@@ -5729,7 +5728,7 @@
         <v>2.18E-2</v>
       </c>
       <c r="BU14" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="BV14">
         <v>22</v>
@@ -5995,7 +5994,7 @@
         <v>50</v>
       </c>
       <c r="BG15" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="BH15" s="9">
         <v>2.8000000000000001E-2</v>
@@ -6010,7 +6009,7 @@
         <v>0.24</v>
       </c>
       <c r="BL15" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="BM15">
         <v>15</v>
@@ -6019,7 +6018,7 @@
         <v>8.7099999999999997E-2</v>
       </c>
       <c r="BO15" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="BP15">
         <v>28</v>
@@ -6028,7 +6027,7 @@
         <v>1.17E-2</v>
       </c>
       <c r="BR15" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="BS15">
         <v>2</v>
@@ -6037,7 +6036,7 @@
         <v>2.6100000000000002E-2</v>
       </c>
       <c r="BU15" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="BV15">
         <v>6</v>
@@ -6303,13 +6302,13 @@
         <v>50</v>
       </c>
       <c r="BG16" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="BH16" s="9">
         <v>5.3E-3</v>
       </c>
       <c r="BI16" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="BJ16">
         <v>2</v>
@@ -6318,7 +6317,7 @@
         <v>2.0899999999999998E-2</v>
       </c>
       <c r="BL16" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="BM16">
         <v>7</v>
@@ -6327,7 +6326,7 @@
         <v>9.2100000000000001E-2</v>
       </c>
       <c r="BO16" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="BP16">
         <v>36</v>
@@ -6336,7 +6335,7 @@
         <v>0</v>
       </c>
       <c r="BR16" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="BS16">
         <v>0</v>
@@ -6345,7 +6344,7 @@
         <v>4.3E-3</v>
       </c>
       <c r="BU16" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="BV16">
         <v>2</v>
@@ -6611,7 +6610,7 @@
         <v>50</v>
       </c>
       <c r="BG17" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="BH17" s="9">
         <v>4.9200000000000001E-2</v>
@@ -6626,7 +6625,7 @@
         <v>0.23</v>
       </c>
       <c r="BL17" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="BM17">
         <v>26</v>
@@ -6635,7 +6634,7 @@
         <v>0.13</v>
       </c>
       <c r="BO17" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="BP17">
         <v>45</v>
@@ -6644,7 +6643,7 @@
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="BR17" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="BS17">
         <v>4</v>
@@ -6653,7 +6652,7 @@
         <v>1.9300000000000001E-2</v>
       </c>
       <c r="BU17" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="BV17">
         <v>9</v>
@@ -6919,7 +6918,7 @@
         <v>50</v>
       </c>
       <c r="BG18" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="BH18" s="9">
         <v>2.5700000000000001E-2</v>
@@ -6934,7 +6933,7 @@
         <v>1.6799999999999999E-2</v>
       </c>
       <c r="BL18" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="BM18">
         <v>8</v>
@@ -6943,7 +6942,7 @@
         <v>1.9800000000000002E-2</v>
       </c>
       <c r="BO18" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="BP18">
         <v>8</v>
@@ -6952,7 +6951,7 @@
         <v>0</v>
       </c>
       <c r="BR18" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="BS18">
         <v>0</v>
@@ -6961,7 +6960,7 @@
         <v>3.4099999999999998E-2</v>
       </c>
       <c r="BU18" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="BV18">
         <v>9</v>
@@ -7227,7 +7226,7 @@
         <v>50</v>
       </c>
       <c r="BG19" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="BH19" s="9">
         <v>9.8400000000000001E-2</v>
@@ -7242,7 +7241,7 @@
         <v>4.2599999999999999E-2</v>
       </c>
       <c r="BL19" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="BM19">
         <v>10</v>
@@ -7251,7 +7250,7 @@
         <v>0.17</v>
       </c>
       <c r="BO19" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="BP19">
         <v>44</v>
@@ -7260,7 +7259,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="BR19" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="BS19">
         <v>1</v>
@@ -7269,7 +7268,7 @@
         <v>4.5199999999999997E-2</v>
       </c>
       <c r="BU19" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="BV19">
         <v>19</v>
@@ -7535,7 +7534,7 @@
         <v>50</v>
       </c>
       <c r="BG20" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="BH20" s="9">
         <v>2.1600000000000001E-2</v>
@@ -7550,7 +7549,7 @@
         <v>2.8799999999999999E-2</v>
       </c>
       <c r="BL20" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="BM20">
         <v>12</v>
@@ -7559,7 +7558,7 @@
         <v>0.11</v>
       </c>
       <c r="BO20" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="BP20">
         <v>40</v>
@@ -7568,7 +7567,7 @@
         <v>8.3000000000000001E-3</v>
       </c>
       <c r="BR20" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="BS20">
         <v>1</v>
@@ -7577,7 +7576,7 @@
         <v>1.6500000000000001E-2</v>
       </c>
       <c r="BU20" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="BV20">
         <v>11</v>
@@ -7843,7 +7842,7 @@
         <v>50</v>
       </c>
       <c r="BG21" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="BH21" s="9">
         <v>4.1999999999999997E-3</v>
@@ -7858,7 +7857,7 @@
         <v>0</v>
       </c>
       <c r="BL21" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="BM21">
         <v>0</v>
@@ -7867,7 +7866,7 @@
         <v>0.16</v>
       </c>
       <c r="BO21" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="BP21">
         <v>15</v>
@@ -7876,7 +7875,7 @@
         <v>0</v>
       </c>
       <c r="BR21" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="BS21">
         <v>0</v>
@@ -7885,7 +7884,7 @@
         <v>0</v>
       </c>
       <c r="BU21" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="BV21">
         <v>0</v>
@@ -8151,7 +8150,7 @@
         <v>50</v>
       </c>
       <c r="BG22" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="BH22" s="9">
         <v>1.5299999999999999E-2</v>
@@ -8166,7 +8165,7 @@
         <v>0</v>
       </c>
       <c r="BL22" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="BM22">
         <v>0</v>
@@ -8175,7 +8174,7 @@
         <v>5.7700000000000001E-2</v>
       </c>
       <c r="BO22" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="BP22">
         <v>27</v>
@@ -8184,7 +8183,7 @@
         <v>0</v>
       </c>
       <c r="BR22" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="BS22">
         <v>0</v>
@@ -8193,7 +8192,7 @@
         <v>1.55E-2</v>
       </c>
       <c r="BU22" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="BV22">
         <v>7</v>
@@ -8284,9 +8283,7 @@
       </c>
     </row>
     <row r="26" spans="1:102" ht="18" x14ac:dyDescent="0.2">
-      <c r="BV26" s="29">
-        <v>1.55E-2</v>
-      </c>
+      <c r="BV26" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="34">

--- a/Data/Final Data/Selected ESG ETFs.xlsx
+++ b/Data/Final Data/Selected ESG ETFs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nityaarya/Downloads/Project/blackrock-esg-etf-study/Data/Final Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B5B977C-42B6-BF4F-AE45-0426195CC72B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44CAF3DF-DBE6-B445-9D4A-30D9DA05EB2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16420" xr2:uid="{A61AF8B7-3585-6343-B574-5450E5520343}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="21500" windowHeight="16420" xr2:uid="{A61AF8B7-3585-6343-B574-5450E5520343}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1176,7 +1176,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1184,10 +1184,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1201,20 +1197,8 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1224,6 +1208,27 @@
     <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1677,197 +1682,197 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:102" x14ac:dyDescent="0.2">
-      <c r="A1" s="22" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="20" t="s">
+      <c r="A1" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="27" t="s">
         <v>193</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="D1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="20" t="s">
+      <c r="E1" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="20" t="s">
+      <c r="F1" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="20" t="s">
+      <c r="G1" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="20" t="s">
+      <c r="H1" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="20" t="s">
+      <c r="I1" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="20" t="s">
+      <c r="J1" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="20" t="s">
+      <c r="K1" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="20" t="s">
+      <c r="L1" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="20" t="s">
+      <c r="M1" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="20" t="s">
+      <c r="N1" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="20" t="s">
+      <c r="O1" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="20" t="s">
+      <c r="P1" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="20" t="s">
+      <c r="Q1" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="20" t="s">
+      <c r="R1" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="20"/>
-      <c r="T1" s="20"/>
-      <c r="U1" s="20"/>
-      <c r="V1" s="20" t="s">
+      <c r="S1" s="15"/>
+      <c r="T1" s="15"/>
+      <c r="U1" s="15"/>
+      <c r="V1" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="W1" s="20"/>
-      <c r="X1" s="20"/>
-      <c r="Y1" s="20"/>
-      <c r="Z1" s="20"/>
-      <c r="AA1" s="20"/>
-      <c r="AB1" s="20"/>
-      <c r="AC1" s="20" t="s">
+      <c r="W1" s="15"/>
+      <c r="X1" s="15"/>
+      <c r="Y1" s="15"/>
+      <c r="Z1" s="15"/>
+      <c r="AA1" s="15"/>
+      <c r="AB1" s="15"/>
+      <c r="AC1" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="AD1" s="20"/>
-      <c r="AE1" s="20"/>
-      <c r="AF1" s="20"/>
-      <c r="AG1" s="20"/>
-      <c r="AH1" s="20"/>
-      <c r="AI1" s="20"/>
-      <c r="AJ1" s="20" t="s">
+      <c r="AD1" s="15"/>
+      <c r="AE1" s="15"/>
+      <c r="AF1" s="15"/>
+      <c r="AG1" s="15"/>
+      <c r="AH1" s="15"/>
+      <c r="AI1" s="15"/>
+      <c r="AJ1" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="AK1" s="20"/>
-      <c r="AL1" s="20"/>
-      <c r="AM1" s="20"/>
-      <c r="AN1" s="20"/>
-      <c r="AO1" s="20"/>
-      <c r="AP1" s="20"/>
-      <c r="AQ1" s="20" t="s">
+      <c r="AK1" s="15"/>
+      <c r="AL1" s="15"/>
+      <c r="AM1" s="15"/>
+      <c r="AN1" s="15"/>
+      <c r="AO1" s="15"/>
+      <c r="AP1" s="15"/>
+      <c r="AQ1" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="AR1" s="20"/>
-      <c r="AS1" s="20"/>
-      <c r="AT1" s="20"/>
-      <c r="AU1" s="20"/>
-      <c r="AV1" s="20"/>
-      <c r="AW1" s="20"/>
-      <c r="AX1" s="20" t="s">
+      <c r="AR1" s="15"/>
+      <c r="AS1" s="15"/>
+      <c r="AT1" s="15"/>
+      <c r="AU1" s="15"/>
+      <c r="AV1" s="15"/>
+      <c r="AW1" s="15"/>
+      <c r="AX1" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="AY1" s="20"/>
-      <c r="AZ1" s="20"/>
-      <c r="BA1" s="20"/>
-      <c r="BB1" s="20"/>
-      <c r="BC1" s="20" t="s">
+      <c r="AY1" s="15"/>
+      <c r="AZ1" s="15"/>
+      <c r="BA1" s="15"/>
+      <c r="BB1" s="15"/>
+      <c r="BC1" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="BD1" s="20"/>
-      <c r="BE1" s="20"/>
-      <c r="BF1" s="20"/>
-      <c r="BG1" s="26" t="s">
+      <c r="BD1" s="15"/>
+      <c r="BE1" s="15"/>
+      <c r="BF1" s="15"/>
+      <c r="BG1" s="18" t="s">
         <v>324</v>
       </c>
-      <c r="BH1" s="24" t="s">
+      <c r="BH1" s="16" t="s">
         <v>217</v>
       </c>
-      <c r="BI1" s="24"/>
-      <c r="BJ1" s="24"/>
-      <c r="BK1" s="27" t="s">
+      <c r="BI1" s="16"/>
+      <c r="BJ1" s="16"/>
+      <c r="BK1" s="19" t="s">
         <v>245</v>
       </c>
-      <c r="BL1" s="27"/>
-      <c r="BM1" s="27"/>
-      <c r="BN1" s="28" t="s">
+      <c r="BL1" s="19"/>
+      <c r="BM1" s="19"/>
+      <c r="BN1" s="20" t="s">
         <v>252</v>
       </c>
-      <c r="BO1" s="28"/>
-      <c r="BP1" s="28"/>
-      <c r="BQ1" s="29" t="s">
+      <c r="BO1" s="20"/>
+      <c r="BP1" s="20"/>
+      <c r="BQ1" s="21" t="s">
         <v>253</v>
       </c>
-      <c r="BR1" s="29"/>
-      <c r="BS1" s="29"/>
-      <c r="BT1" s="30" t="s">
+      <c r="BR1" s="21"/>
+      <c r="BS1" s="21"/>
+      <c r="BT1" s="22" t="s">
         <v>256</v>
       </c>
-      <c r="BU1" s="30"/>
-      <c r="BV1" s="30"/>
-      <c r="BW1" s="25" t="s">
+      <c r="BU1" s="22"/>
+      <c r="BV1" s="22"/>
+      <c r="BW1" s="17" t="s">
         <v>218</v>
       </c>
-      <c r="BX1" s="25"/>
-      <c r="BY1" s="25"/>
-      <c r="BZ1" s="25"/>
-      <c r="CA1" s="25"/>
-      <c r="CB1" s="25"/>
-      <c r="CC1" s="25"/>
-      <c r="CD1" s="23" t="s">
+      <c r="BX1" s="17"/>
+      <c r="BY1" s="17"/>
+      <c r="BZ1" s="17"/>
+      <c r="CA1" s="17"/>
+      <c r="CB1" s="17"/>
+      <c r="CC1" s="17"/>
+      <c r="CD1" s="14" t="s">
         <v>219</v>
       </c>
-      <c r="CE1" s="23"/>
-      <c r="CF1" s="23"/>
+      <c r="CE1" s="14"/>
+      <c r="CF1" s="14"/>
       <c r="CG1" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="CH1" s="16" t="s">
+      <c r="CH1" s="23" t="s">
         <v>194</v>
       </c>
-      <c r="CI1" s="17"/>
-      <c r="CJ1" s="17"/>
-      <c r="CK1" s="17"/>
-      <c r="CL1" s="17"/>
-      <c r="CM1" s="17"/>
-      <c r="CN1" s="17"/>
-      <c r="CO1" s="17"/>
-      <c r="CP1" s="17"/>
-      <c r="CQ1" s="17"/>
-      <c r="CR1" s="18" t="s">
+      <c r="CI1" s="24"/>
+      <c r="CJ1" s="24"/>
+      <c r="CK1" s="24"/>
+      <c r="CL1" s="24"/>
+      <c r="CM1" s="24"/>
+      <c r="CN1" s="24"/>
+      <c r="CO1" s="24"/>
+      <c r="CP1" s="24"/>
+      <c r="CQ1" s="24"/>
+      <c r="CR1" s="25" t="s">
         <v>209</v>
       </c>
-      <c r="CS1" s="19"/>
-      <c r="CT1" s="19"/>
-      <c r="CU1" s="19"/>
-      <c r="CV1" s="19"/>
-      <c r="CW1" s="19"/>
-      <c r="CX1" s="19"/>
+      <c r="CS1" s="26"/>
+      <c r="CT1" s="26"/>
+      <c r="CU1" s="26"/>
+      <c r="CV1" s="26"/>
+      <c r="CW1" s="26"/>
+      <c r="CX1" s="26"/>
     </row>
     <row r="2" spans="1:102" x14ac:dyDescent="0.2">
-      <c r="A2" s="22"/>
-      <c r="B2" s="20"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
-      <c r="L2" s="20"/>
-      <c r="M2" s="20"/>
-      <c r="N2" s="20"/>
-      <c r="O2" s="20"/>
-      <c r="P2" s="20"/>
-      <c r="Q2" s="20"/>
+      <c r="A2" s="28"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="15"/>
+      <c r="O2" s="15"/>
+      <c r="P2" s="15"/>
+      <c r="Q2" s="15"/>
       <c r="R2" s="1" t="s">
         <v>23</v>
       </c>
@@ -1991,7 +1996,7 @@
       <c r="BF2" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="BG2" s="26"/>
+      <c r="BG2" s="18"/>
       <c r="BH2" s="2" t="s">
         <v>114</v>
       </c>
@@ -2013,7 +2018,7 @@
       <c r="BN2" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="BO2" s="13" t="s">
+      <c r="BO2" s="11" t="s">
         <v>251</v>
       </c>
       <c r="BP2" s="2" t="s">
@@ -2022,7 +2027,7 @@
       <c r="BQ2" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="BR2" s="13" t="s">
+      <c r="BR2" s="11" t="s">
         <v>254</v>
       </c>
       <c r="BS2" s="2" t="s">
@@ -2031,7 +2036,7 @@
       <c r="BT2" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="BU2" s="13" t="s">
+      <c r="BU2" s="11" t="s">
         <v>257</v>
       </c>
       <c r="BV2" s="2" t="s">
@@ -2123,37 +2128,37 @@
       </c>
     </row>
     <row r="3" spans="1:102" ht="17" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="31">
         <v>294</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="31" t="s">
         <v>41</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="G3" s="7">
+      <c r="G3" s="32">
         <v>42705</v>
       </c>
-      <c r="H3" s="8">
+      <c r="H3" s="33">
         <v>0.15</v>
       </c>
-      <c r="I3" s="8">
+      <c r="I3" s="33">
         <v>0.15</v>
       </c>
-      <c r="J3" s="8">
+      <c r="J3" s="33">
         <v>13989919390.35</v>
       </c>
-      <c r="K3" s="7">
+      <c r="K3" s="5">
         <v>45873</v>
       </c>
       <c r="L3" t="s">
@@ -2174,121 +2179,121 @@
       <c r="Q3" t="s">
         <v>49</v>
       </c>
-      <c r="R3" s="8">
+      <c r="R3" s="6">
         <v>1.1073906616908511</v>
       </c>
-      <c r="S3" s="7">
-        <v>45838</v>
-      </c>
-      <c r="T3" s="8">
+      <c r="S3" s="5">
+        <v>45838</v>
+      </c>
+      <c r="T3" s="6">
         <v>7.7337089092143483</v>
       </c>
-      <c r="U3" s="7">
+      <c r="U3" s="5">
         <v>45873</v>
       </c>
-      <c r="V3" s="8">
+      <c r="V3" s="6">
         <v>5.5481720000000001</v>
       </c>
-      <c r="W3" s="8">
+      <c r="W3" s="6">
         <v>14.699521000000001</v>
       </c>
-      <c r="X3" s="8">
+      <c r="X3" s="6">
         <v>18.891756999999998</v>
       </c>
-      <c r="Y3" s="8">
+      <c r="Y3" s="6">
         <v>15.631455000000001</v>
       </c>
       <c r="Z3" t="s">
         <v>50</v>
       </c>
-      <c r="AA3" s="8">
+      <c r="AA3" s="6">
         <v>14.570164999999999</v>
       </c>
-      <c r="AB3" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AC3" s="8">
+      <c r="AB3" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AC3" s="6">
         <v>5.5718839999999998</v>
       </c>
-      <c r="AD3" s="8">
+      <c r="AD3" s="6">
         <v>14.727634999999999</v>
       </c>
-      <c r="AE3" s="8">
+      <c r="AE3" s="6">
         <v>18.938559999999999</v>
       </c>
-      <c r="AF3" s="8">
+      <c r="AF3" s="6">
         <v>15.662542999999999</v>
       </c>
       <c r="AG3" t="s">
         <v>50</v>
       </c>
-      <c r="AH3" s="8">
+      <c r="AH3" s="6">
         <v>14.576081</v>
       </c>
-      <c r="AI3" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AJ3" s="8">
+      <c r="AI3" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AJ3" s="6">
         <v>7.8631840000000004</v>
       </c>
-      <c r="AK3" s="8">
+      <c r="AK3" s="6">
         <v>15.526434999999999</v>
       </c>
-      <c r="AL3" s="8">
+      <c r="AL3" s="6">
         <v>16.222843999999998</v>
       </c>
-      <c r="AM3" s="8">
+      <c r="AM3" s="6">
         <v>14.819998</v>
       </c>
       <c r="AN3" t="s">
         <v>50</v>
       </c>
-      <c r="AO3" s="8">
+      <c r="AO3" s="6">
         <v>14.704357999999999</v>
       </c>
-      <c r="AP3" s="7">
+      <c r="AP3" s="5">
         <v>45869</v>
       </c>
-      <c r="AQ3" s="8">
+      <c r="AQ3" s="6">
         <v>5.5718839999999998</v>
       </c>
-      <c r="AR3" s="8">
+      <c r="AR3" s="6">
         <v>14.727634999999999</v>
       </c>
-      <c r="AS3" s="8">
+      <c r="AS3" s="6">
         <v>18.938559999999999</v>
       </c>
-      <c r="AT3" s="8">
+      <c r="AT3" s="6">
         <v>15.662542999999999</v>
       </c>
       <c r="AU3" t="s">
         <v>50</v>
       </c>
-      <c r="AV3" s="8">
+      <c r="AV3" s="6">
         <v>14.576081</v>
       </c>
-      <c r="AW3" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AX3" s="8">
+      <c r="AW3" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AX3" s="6">
         <v>1.1073906616908511</v>
       </c>
-      <c r="AY3" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AZ3" s="8">
+      <c r="AY3" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AZ3" s="6">
         <v>1.0624</v>
       </c>
-      <c r="BA3" s="8">
+      <c r="BA3" s="6">
         <v>1.0624</v>
       </c>
-      <c r="BB3" s="7">
+      <c r="BB3" s="5">
         <v>45838</v>
       </c>
       <c r="BC3" t="s">
         <v>50</v>
       </c>
-      <c r="BD3" s="8">
+      <c r="BD3" s="6">
         <v>1.74E-3</v>
       </c>
       <c r="BE3" t="s">
@@ -2300,7 +2305,7 @@
       <c r="BG3" t="s">
         <v>228</v>
       </c>
-      <c r="BH3" s="9">
+      <c r="BH3" s="7">
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="BI3" t="s">
@@ -2309,7 +2314,7 @@
       <c r="BJ3">
         <v>27</v>
       </c>
-      <c r="BK3" s="11">
+      <c r="BK3" s="9">
         <v>0.21</v>
       </c>
       <c r="BL3" t="s">
@@ -2318,16 +2323,16 @@
       <c r="BM3">
         <v>23</v>
       </c>
-      <c r="BN3" s="11">
+      <c r="BN3" s="9">
         <v>0.14000000000000001</v>
       </c>
-      <c r="BO3" s="11" t="s">
+      <c r="BO3" s="9" t="s">
         <v>249</v>
       </c>
-      <c r="BP3" s="15">
+      <c r="BP3" s="13">
         <v>36</v>
       </c>
-      <c r="BQ3" s="9">
+      <c r="BQ3" s="7">
         <v>7.4999999999999997E-3</v>
       </c>
       <c r="BR3" t="s">
@@ -2336,7 +2341,7 @@
       <c r="BS3">
         <v>3</v>
       </c>
-      <c r="BT3" s="9">
+      <c r="BT3" s="7">
         <v>3.3399999999999999E-2</v>
       </c>
       <c r="BU3" t="s">
@@ -2345,7 +2350,7 @@
       <c r="BV3">
         <v>14</v>
       </c>
-      <c r="BW3" s="12" t="s">
+      <c r="BW3" s="10" t="s">
         <v>131</v>
       </c>
       <c r="BX3" t="s">
@@ -2366,7 +2371,7 @@
       <c r="CC3" t="s">
         <v>119</v>
       </c>
-      <c r="CD3" s="9">
+      <c r="CD3" s="7">
         <v>0.25259999999999999</v>
       </c>
       <c r="CE3">
@@ -2375,7 +2380,7 @@
       <c r="CF3" t="s">
         <v>146</v>
       </c>
-      <c r="CG3" s="9">
+      <c r="CG3" s="7">
         <v>1.7399999999999999E-2</v>
       </c>
       <c r="CH3" t="s">
@@ -2393,75 +2398,75 @@
       <c r="CL3" t="s">
         <v>208</v>
       </c>
-      <c r="CM3" s="9">
+      <c r="CM3" s="7">
         <v>0.99950000000000006</v>
       </c>
-      <c r="CN3" s="9">
+      <c r="CN3" s="7">
         <v>0.90369999999999995</v>
       </c>
-      <c r="CO3" s="10">
+      <c r="CO3" s="8">
         <v>3717</v>
       </c>
-      <c r="CP3" s="9">
+      <c r="CP3" s="7">
         <v>0.99660000000000004</v>
       </c>
-      <c r="CQ3" s="9">
+      <c r="CQ3" s="7">
         <v>0.99660000000000004</v>
       </c>
-      <c r="CR3" s="9">
-        <v>0</v>
-      </c>
-      <c r="CS3" s="9">
+      <c r="CR3" s="7">
+        <v>0</v>
+      </c>
+      <c r="CS3" s="7">
         <v>1.6000000000000001E-3</v>
       </c>
-      <c r="CT3" s="9">
-        <v>0</v>
-      </c>
-      <c r="CU3" s="9">
-        <v>0</v>
-      </c>
-      <c r="CV3" s="9">
-        <v>0</v>
-      </c>
-      <c r="CW3" s="9">
-        <v>0</v>
-      </c>
-      <c r="CX3" s="9">
+      <c r="CT3" s="7">
+        <v>0</v>
+      </c>
+      <c r="CU3" s="7">
+        <v>0</v>
+      </c>
+      <c r="CV3" s="7">
+        <v>0</v>
+      </c>
+      <c r="CW3" s="7">
+        <v>0</v>
+      </c>
+      <c r="CX3" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:102" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="30" t="s">
         <v>52</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="31">
         <v>385</v>
       </c>
-      <c r="D4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="D4" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="E4" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="32">
         <v>42549</v>
       </c>
-      <c r="H4" s="8">
+      <c r="H4" s="33">
         <v>0.21</v>
       </c>
-      <c r="I4" s="8">
+      <c r="I4" s="33">
         <v>0.21</v>
       </c>
-      <c r="J4" s="8">
+      <c r="J4" s="33">
         <v>9596812876.4200001</v>
       </c>
-      <c r="K4" s="7">
+      <c r="K4" s="5">
         <v>45873</v>
       </c>
       <c r="L4" t="s">
@@ -2482,121 +2487,121 @@
       <c r="Q4" t="s">
         <v>49</v>
       </c>
-      <c r="R4" s="8">
+      <c r="R4" s="6">
         <v>2.9527000000000001</v>
       </c>
-      <c r="S4" s="7">
-        <v>45838</v>
-      </c>
-      <c r="T4" s="8">
+      <c r="S4" s="5">
+        <v>45838</v>
+      </c>
+      <c r="T4" s="6">
         <v>18.184743985123024</v>
       </c>
-      <c r="U4" s="7">
+      <c r="U4" s="5">
         <v>45873</v>
       </c>
-      <c r="V4" s="8">
+      <c r="V4" s="6">
         <v>19.73</v>
       </c>
-      <c r="W4" s="8">
+      <c r="W4" s="6">
         <v>17.510000000000002</v>
       </c>
-      <c r="X4" s="8">
+      <c r="X4" s="6">
         <v>15.77</v>
       </c>
-      <c r="Y4" s="8">
+      <c r="Y4" s="6">
         <v>11.22</v>
       </c>
       <c r="Z4" t="s">
         <v>50</v>
       </c>
-      <c r="AA4" s="8">
+      <c r="AA4" s="6">
         <v>9.23</v>
       </c>
-      <c r="AB4" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AC4" s="8">
+      <c r="AB4" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AC4" s="6">
         <v>19.350000000000001</v>
       </c>
-      <c r="AD4" s="8">
+      <c r="AD4" s="6">
         <v>16.850000000000001</v>
       </c>
-      <c r="AE4" s="8">
+      <c r="AE4" s="6">
         <v>15.69</v>
       </c>
-      <c r="AF4" s="8">
+      <c r="AF4" s="6">
         <v>11.13</v>
       </c>
       <c r="AG4" t="s">
         <v>50</v>
       </c>
-      <c r="AH4" s="8">
+      <c r="AH4" s="6">
         <v>9.2100000000000009</v>
       </c>
-      <c r="AI4" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AJ4" s="8">
+      <c r="AI4" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AJ4" s="6">
         <v>16.72</v>
       </c>
-      <c r="AK4" s="8">
+      <c r="AK4" s="6">
         <v>11.46</v>
       </c>
-      <c r="AL4" s="8">
+      <c r="AL4" s="6">
         <v>12.83</v>
       </c>
-      <c r="AM4" s="8">
+      <c r="AM4" s="6">
         <v>10.119999999999999</v>
       </c>
       <c r="AN4" t="s">
         <v>50</v>
       </c>
-      <c r="AO4" s="8">
+      <c r="AO4" s="6">
         <v>8.83</v>
       </c>
-      <c r="AP4" s="7">
+      <c r="AP4" s="5">
         <v>45869</v>
       </c>
-      <c r="AQ4" s="8">
+      <c r="AQ4" s="6">
         <v>19.350000000000001</v>
       </c>
-      <c r="AR4" s="8">
+      <c r="AR4" s="6">
         <v>16.850000000000001</v>
       </c>
-      <c r="AS4" s="8">
+      <c r="AS4" s="6">
         <v>15.69</v>
       </c>
-      <c r="AT4" s="8">
+      <c r="AT4" s="6">
         <v>11.13</v>
       </c>
       <c r="AU4" t="s">
         <v>50</v>
       </c>
-      <c r="AV4" s="8">
+      <c r="AV4" s="6">
         <v>9.2100000000000009</v>
       </c>
-      <c r="AW4" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AX4" s="8">
+      <c r="AW4" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AX4" s="6">
         <v>2.9527000000000001</v>
       </c>
-      <c r="AY4" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AZ4" s="8">
+      <c r="AY4" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AZ4" s="6">
         <v>2.4481999999999999</v>
       </c>
-      <c r="BA4" s="8">
+      <c r="BA4" s="6">
         <v>2.4481999999999999</v>
       </c>
-      <c r="BB4" s="7">
+      <c r="BB4" s="5">
         <v>45838</v>
       </c>
       <c r="BC4" t="s">
         <v>50</v>
       </c>
-      <c r="BD4" s="8">
+      <c r="BD4" s="6">
         <v>2.3000000000000001E-4</v>
       </c>
       <c r="BE4" t="s">
@@ -2608,7 +2613,7 @@
       <c r="BG4" t="s">
         <v>229</v>
       </c>
-      <c r="BH4" s="9">
+      <c r="BH4" s="7">
         <v>0.10100000000000001</v>
       </c>
       <c r="BI4" t="s">
@@ -2617,7 +2622,7 @@
       <c r="BJ4">
         <v>35</v>
       </c>
-      <c r="BK4" s="9">
+      <c r="BK4" s="7">
         <v>3.5499999999999997E-2</v>
       </c>
       <c r="BL4" t="s">
@@ -2626,16 +2631,16 @@
       <c r="BM4">
         <v>9</v>
       </c>
-      <c r="BN4" s="11">
+      <c r="BN4" s="9">
         <v>0.2</v>
       </c>
       <c r="BO4" t="s">
         <v>259</v>
       </c>
-      <c r="BP4" s="15">
+      <c r="BP4" s="13">
         <v>56</v>
       </c>
-      <c r="BQ4" s="9">
+      <c r="BQ4" s="7">
         <v>9.9000000000000008E-3</v>
       </c>
       <c r="BR4" t="s">
@@ -2644,7 +2649,7 @@
       <c r="BS4">
         <v>1</v>
       </c>
-      <c r="BT4" s="11">
+      <c r="BT4" s="9">
         <v>4.8099999999999997E-2</v>
       </c>
       <c r="BU4" t="s">
@@ -2674,7 +2679,7 @@
       <c r="CC4" t="s">
         <v>119</v>
       </c>
-      <c r="CD4" s="9">
+      <c r="CD4" s="7">
         <v>0.1255</v>
       </c>
       <c r="CE4">
@@ -2683,7 +2688,7 @@
       <c r="CF4" t="s">
         <v>148</v>
       </c>
-      <c r="CG4" s="9">
+      <c r="CG4" s="7">
         <v>4.36E-2</v>
       </c>
       <c r="CH4" t="s">
@@ -2701,75 +2706,75 @@
       <c r="CL4" t="s">
         <v>202</v>
       </c>
-      <c r="CM4" s="9">
+      <c r="CM4" s="7">
         <v>1</v>
       </c>
-      <c r="CN4" s="9">
+      <c r="CN4" s="7">
         <v>0.99060000000000004</v>
       </c>
       <c r="CO4">
         <v>853</v>
       </c>
-      <c r="CP4" s="9">
+      <c r="CP4" s="7">
         <v>0.99239999999999995</v>
       </c>
-      <c r="CQ4" s="9">
+      <c r="CQ4" s="7">
         <v>0.99239999999999995</v>
       </c>
-      <c r="CR4" s="9">
-        <v>0</v>
-      </c>
-      <c r="CS4" s="9">
+      <c r="CR4" s="7">
+        <v>0</v>
+      </c>
+      <c r="CS4" s="7">
         <v>1.43E-2</v>
       </c>
-      <c r="CT4" s="9">
-        <v>0</v>
-      </c>
-      <c r="CU4" s="9">
-        <v>0</v>
-      </c>
-      <c r="CV4" s="9">
-        <v>0</v>
-      </c>
-      <c r="CW4" s="9">
-        <v>0</v>
-      </c>
-      <c r="CX4" s="9">
+      <c r="CT4" s="7">
+        <v>0</v>
+      </c>
+      <c r="CU4" s="7">
+        <v>0</v>
+      </c>
+      <c r="CV4" s="7">
+        <v>0</v>
+      </c>
+      <c r="CW4" s="7">
+        <v>0</v>
+      </c>
+      <c r="CX4" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:102" x14ac:dyDescent="0.2">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="29" t="s">
         <v>57</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="31">
         <v>333</v>
       </c>
-      <c r="D5" t="s">
-        <v>50</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="D5" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="E5" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="31" t="s">
         <v>60</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="32">
         <v>42549</v>
       </c>
-      <c r="H5" s="8">
+      <c r="H5" s="33">
         <v>0.26</v>
       </c>
-      <c r="I5" s="8">
+      <c r="I5" s="33">
         <v>0.26</v>
       </c>
-      <c r="J5" s="8">
+      <c r="J5" s="33">
         <v>5076162057.75</v>
       </c>
-      <c r="K5" s="7">
+      <c r="K5" s="5">
         <v>45873</v>
       </c>
       <c r="L5" t="s">
@@ -2790,121 +2795,121 @@
       <c r="Q5" t="s">
         <v>49</v>
       </c>
-      <c r="R5" s="8">
+      <c r="R5" s="6">
         <v>2.3641999999999999</v>
       </c>
-      <c r="S5" s="7">
-        <v>45838</v>
-      </c>
-      <c r="T5" s="8">
+      <c r="S5" s="5">
+        <v>45838</v>
+      </c>
+      <c r="T5" s="6">
         <v>19.632556279740982</v>
       </c>
-      <c r="U5" s="7">
+      <c r="U5" s="5">
         <v>45873</v>
       </c>
-      <c r="V5" s="8">
+      <c r="V5" s="6">
         <v>18.010000000000002</v>
       </c>
-      <c r="W5" s="8">
+      <c r="W5" s="6">
         <v>20.05</v>
       </c>
-      <c r="X5" s="8">
+      <c r="X5" s="6">
         <v>9.4700000000000006</v>
       </c>
-      <c r="Y5" s="8">
+      <c r="Y5" s="6">
         <v>6.56</v>
       </c>
       <c r="Z5" t="s">
         <v>50</v>
       </c>
-      <c r="AA5" s="8">
+      <c r="AA5" s="6">
         <v>7.35</v>
       </c>
-      <c r="AB5" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AC5" s="8">
+      <c r="AB5" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AC5" s="6">
         <v>18.45</v>
       </c>
-      <c r="AD5" s="8">
+      <c r="AD5" s="6">
         <v>19.87</v>
       </c>
-      <c r="AE5" s="8">
+      <c r="AE5" s="6">
         <v>9.42</v>
       </c>
-      <c r="AF5" s="8">
+      <c r="AF5" s="6">
         <v>6.61</v>
       </c>
       <c r="AG5" t="s">
         <v>50</v>
       </c>
-      <c r="AH5" s="8">
+      <c r="AH5" s="6">
         <v>7.35</v>
       </c>
-      <c r="AI5" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AJ5" s="8">
+      <c r="AI5" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AJ5" s="6">
         <v>19.48</v>
       </c>
-      <c r="AK5" s="8">
+      <c r="AK5" s="6">
         <v>20.190000000000001</v>
       </c>
-      <c r="AL5" s="8">
+      <c r="AL5" s="6">
         <v>10.29</v>
       </c>
-      <c r="AM5" s="8">
+      <c r="AM5" s="6">
         <v>4.9000000000000004</v>
       </c>
       <c r="AN5" t="s">
         <v>50</v>
       </c>
-      <c r="AO5" s="8">
+      <c r="AO5" s="6">
         <v>7.43</v>
       </c>
-      <c r="AP5" s="7">
+      <c r="AP5" s="5">
         <v>45869</v>
       </c>
-      <c r="AQ5" s="8">
+      <c r="AQ5" s="6">
         <v>18.45</v>
       </c>
-      <c r="AR5" s="8">
+      <c r="AR5" s="6">
         <v>19.87</v>
       </c>
-      <c r="AS5" s="8">
+      <c r="AS5" s="6">
         <v>9.42</v>
       </c>
-      <c r="AT5" s="8">
+      <c r="AT5" s="6">
         <v>6.61</v>
       </c>
       <c r="AU5" t="s">
         <v>50</v>
       </c>
-      <c r="AV5" s="8">
+      <c r="AV5" s="6">
         <v>7.35</v>
       </c>
-      <c r="AW5" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AX5" s="8">
+      <c r="AW5" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AX5" s="6">
         <v>2.3641999999999999</v>
       </c>
-      <c r="AY5" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AZ5" s="8">
+      <c r="AY5" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AZ5" s="6">
         <v>1.9725999999999999</v>
       </c>
-      <c r="BA5" s="8">
+      <c r="BA5" s="6">
         <v>1.9725999999999999</v>
       </c>
-      <c r="BB5" s="7">
+      <c r="BB5" s="5">
         <v>45838</v>
       </c>
       <c r="BC5" t="s">
         <v>50</v>
       </c>
-      <c r="BD5" s="8">
+      <c r="BD5" s="6">
         <v>4.3600000000000002E-3</v>
       </c>
       <c r="BE5" t="s">
@@ -2916,7 +2921,7 @@
       <c r="BG5" t="s">
         <v>229</v>
       </c>
-      <c r="BH5" s="9">
+      <c r="BH5" s="7">
         <v>5.04E-2</v>
       </c>
       <c r="BI5" t="s">
@@ -2925,7 +2930,7 @@
       <c r="BJ5">
         <v>20</v>
       </c>
-      <c r="BK5" s="11">
+      <c r="BK5" s="9">
         <v>0</v>
       </c>
       <c r="BL5" t="s">
@@ -2934,16 +2939,16 @@
       <c r="BM5">
         <v>0</v>
       </c>
-      <c r="BN5" s="9">
+      <c r="BN5" s="7">
         <v>4.3499999999999997E-2</v>
       </c>
       <c r="BO5" t="s">
         <v>284</v>
       </c>
-      <c r="BP5" s="15">
+      <c r="BP5" s="13">
         <v>17</v>
       </c>
-      <c r="BQ5" s="11">
+      <c r="BQ5" s="9">
         <v>0</v>
       </c>
       <c r="BR5" t="s">
@@ -2952,7 +2957,7 @@
       <c r="BS5">
         <v>0</v>
       </c>
-      <c r="BT5" s="9">
+      <c r="BT5" s="7">
         <v>1.3100000000000001E-2</v>
       </c>
       <c r="BU5" t="s">
@@ -2982,7 +2987,7 @@
       <c r="CC5" t="s">
         <v>120</v>
       </c>
-      <c r="CD5" s="9">
+      <c r="CD5" s="7">
         <v>0.15140000000000001</v>
       </c>
       <c r="CE5">
@@ -2991,7 +2996,7 @@
       <c r="CF5" t="s">
         <v>150</v>
       </c>
-      <c r="CG5" s="9">
+      <c r="CG5" s="7">
         <v>5.3E-3</v>
       </c>
       <c r="CH5" t="s">
@@ -3009,75 +3014,75 @@
       <c r="CL5" t="s">
         <v>208</v>
       </c>
-      <c r="CM5" s="9">
+      <c r="CM5" s="7">
         <v>1</v>
       </c>
-      <c r="CN5" s="9">
+      <c r="CN5" s="7">
         <v>0.99239999999999995</v>
       </c>
-      <c r="CO5" s="10">
+      <c r="CO5" s="8">
         <v>1314</v>
       </c>
-      <c r="CP5" s="9">
+      <c r="CP5" s="7">
         <v>0.99170000000000003</v>
       </c>
-      <c r="CQ5" s="9">
+      <c r="CQ5" s="7">
         <v>0.98150000000000004</v>
       </c>
-      <c r="CR5" s="9">
-        <v>0</v>
-      </c>
-      <c r="CS5" s="9">
-        <v>0</v>
-      </c>
-      <c r="CT5" s="9">
-        <v>0</v>
-      </c>
-      <c r="CU5" s="9">
-        <v>0</v>
-      </c>
-      <c r="CV5" s="9">
-        <v>0</v>
-      </c>
-      <c r="CW5" s="9">
-        <v>0</v>
-      </c>
-      <c r="CX5" s="9">
+      <c r="CR5" s="7">
+        <v>0</v>
+      </c>
+      <c r="CS5" s="7">
+        <v>0</v>
+      </c>
+      <c r="CT5" s="7">
+        <v>0</v>
+      </c>
+      <c r="CU5" s="7">
+        <v>0</v>
+      </c>
+      <c r="CV5" s="7">
+        <v>0</v>
+      </c>
+      <c r="CW5" s="7">
+        <v>0</v>
+      </c>
+      <c r="CX5" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:102" x14ac:dyDescent="0.2">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="30" t="s">
         <v>63</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="31">
         <v>405</v>
       </c>
-      <c r="D6" t="s">
-        <v>50</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="D6" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="32">
         <v>39035</v>
       </c>
-      <c r="H6" s="8">
+      <c r="H6" s="33">
         <v>0.25</v>
       </c>
-      <c r="I6" s="8">
+      <c r="I6" s="33">
         <v>0.25</v>
       </c>
-      <c r="J6" s="8">
+      <c r="J6" s="33">
         <v>4790621472.6599998</v>
       </c>
-      <c r="K6" s="7">
+      <c r="K6" s="5">
         <v>45873</v>
       </c>
       <c r="L6" t="s">
@@ -3098,121 +3103,121 @@
       <c r="Q6" t="s">
         <v>49</v>
       </c>
-      <c r="R6" s="8">
+      <c r="R6" s="6">
         <v>1.039024618831363</v>
       </c>
-      <c r="S6" s="7">
-        <v>45838</v>
-      </c>
-      <c r="T6" s="8">
+      <c r="S6" s="5">
+        <v>45838</v>
+      </c>
+      <c r="T6" s="6">
         <v>9.6774933404828278</v>
       </c>
-      <c r="U6" s="7">
+      <c r="U6" s="5">
         <v>45873</v>
       </c>
-      <c r="V6" s="8">
+      <c r="V6" s="6">
         <v>5.8750460000000002</v>
       </c>
-      <c r="W6" s="8">
+      <c r="W6" s="6">
         <v>13.096598</v>
       </c>
-      <c r="X6" s="8">
+      <c r="X6" s="6">
         <v>18.817050999999999</v>
       </c>
-      <c r="Y6" s="8">
+      <c r="Y6" s="6">
         <v>15.863987</v>
       </c>
-      <c r="Z6" s="8">
+      <c r="Z6" s="6">
         <v>13.350996</v>
       </c>
-      <c r="AA6" s="8">
+      <c r="AA6" s="6">
         <v>10.098424</v>
       </c>
-      <c r="AB6" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AC6" s="8">
+      <c r="AB6" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AC6" s="6">
         <v>5.8856479999999998</v>
       </c>
-      <c r="AD6" s="8">
+      <c r="AD6" s="6">
         <v>13.093375999999999</v>
       </c>
-      <c r="AE6" s="8">
+      <c r="AE6" s="6">
         <v>18.802195000000001</v>
       </c>
-      <c r="AF6" s="8">
+      <c r="AF6" s="6">
         <v>15.876492000000001</v>
       </c>
-      <c r="AG6" s="8">
+      <c r="AG6" s="6">
         <v>13.342413000000001</v>
       </c>
-      <c r="AH6" s="8">
+      <c r="AH6" s="6">
         <v>10.097659</v>
       </c>
-      <c r="AI6" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AJ6" s="8">
+      <c r="AI6" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AJ6" s="6">
         <v>9.1408799999999992</v>
       </c>
-      <c r="AK6" s="8">
+      <c r="AK6" s="6">
         <v>15.734753</v>
       </c>
-      <c r="AL6" s="8">
+      <c r="AL6" s="6">
         <v>16.747098999999999</v>
       </c>
-      <c r="AM6" s="8">
+      <c r="AM6" s="6">
         <v>15.516323999999999</v>
       </c>
-      <c r="AN6" s="8">
+      <c r="AN6" s="6">
         <v>13.460685</v>
       </c>
-      <c r="AO6" s="8">
+      <c r="AO6" s="6">
         <v>10.229175</v>
       </c>
-      <c r="AP6" s="7">
+      <c r="AP6" s="5">
         <v>45869</v>
       </c>
-      <c r="AQ6" s="8">
+      <c r="AQ6" s="6">
         <v>5.8856479999999998</v>
       </c>
-      <c r="AR6" s="8">
+      <c r="AR6" s="6">
         <v>13.093375999999999</v>
       </c>
-      <c r="AS6" s="8">
+      <c r="AS6" s="6">
         <v>18.802195000000001</v>
       </c>
-      <c r="AT6" s="8">
+      <c r="AT6" s="6">
         <v>15.876492000000001</v>
       </c>
-      <c r="AU6" s="8">
+      <c r="AU6" s="6">
         <v>13.342413000000001</v>
       </c>
-      <c r="AV6" s="8">
+      <c r="AV6" s="6">
         <v>10.097659</v>
       </c>
-      <c r="AW6" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AX6" s="8">
+      <c r="AW6" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AX6" s="6">
         <v>1.039024618831363</v>
       </c>
-      <c r="AY6" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AZ6" s="8">
+      <c r="AY6" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AZ6" s="6">
         <v>0.98180000000000001</v>
       </c>
-      <c r="BA6" s="8">
+      <c r="BA6" s="6">
         <v>0.98180000000000001</v>
       </c>
-      <c r="BB6" s="7">
+      <c r="BB6" s="5">
         <v>45838</v>
       </c>
       <c r="BC6" t="s">
         <v>50</v>
       </c>
-      <c r="BD6" s="8">
+      <c r="BD6" s="6">
         <v>1.3500000000000001E-3</v>
       </c>
       <c r="BE6" t="s">
@@ -3224,7 +3229,7 @@
       <c r="BG6" t="s">
         <v>230</v>
       </c>
-      <c r="BH6" s="9">
+      <c r="BH6" s="7">
         <v>2.3E-2</v>
       </c>
       <c r="BI6" t="s">
@@ -3233,7 +3238,7 @@
       <c r="BJ6">
         <v>23</v>
       </c>
-      <c r="BK6" s="11">
+      <c r="BK6" s="9">
         <v>0.24</v>
       </c>
       <c r="BL6" t="s">
@@ -3242,7 +3247,7 @@
       <c r="BM6">
         <v>20</v>
       </c>
-      <c r="BN6" s="9">
+      <c r="BN6" s="7">
         <v>7.7499999999999999E-2</v>
       </c>
       <c r="BO6" t="s">
@@ -3251,7 +3256,7 @@
       <c r="BP6">
         <v>35</v>
       </c>
-      <c r="BQ6" s="9">
+      <c r="BQ6" s="7">
         <v>7.3000000000000001E-3</v>
       </c>
       <c r="BR6" t="s">
@@ -3260,7 +3265,7 @@
       <c r="BS6">
         <v>1</v>
       </c>
-      <c r="BT6" s="9">
+      <c r="BT6" s="7">
         <v>1.9800000000000002E-2</v>
       </c>
       <c r="BU6" t="s">
@@ -3290,7 +3295,7 @@
       <c r="CC6" t="s">
         <v>119</v>
       </c>
-      <c r="CD6" s="9">
+      <c r="CD6" s="7">
         <v>0.29830000000000001</v>
       </c>
       <c r="CE6">
@@ -3299,7 +3304,7 @@
       <c r="CF6" t="s">
         <v>149</v>
       </c>
-      <c r="CG6" s="11">
+      <c r="CG6" s="9">
         <v>0</v>
       </c>
       <c r="CH6" t="s">
@@ -3317,75 +3322,75 @@
       <c r="CL6" t="s">
         <v>208</v>
       </c>
-      <c r="CM6" s="9">
+      <c r="CM6" s="7">
         <v>0.99950000000000006</v>
       </c>
-      <c r="CN6" s="9">
+      <c r="CN6" s="7">
         <v>0.95609999999999995</v>
       </c>
-      <c r="CO6" s="10">
+      <c r="CO6" s="8">
         <v>3717</v>
       </c>
-      <c r="CP6" s="9">
+      <c r="CP6" s="7">
         <v>0.99829999999999997</v>
       </c>
-      <c r="CQ6" s="9">
+      <c r="CQ6" s="7">
         <v>0.99829999999999997</v>
       </c>
-      <c r="CR6" s="9">
-        <v>0</v>
-      </c>
-      <c r="CS6" s="9">
-        <v>0</v>
-      </c>
-      <c r="CT6" s="9">
-        <v>0</v>
-      </c>
-      <c r="CU6" s="9">
-        <v>0</v>
-      </c>
-      <c r="CV6" s="9">
-        <v>0</v>
-      </c>
-      <c r="CW6" s="9">
-        <v>0</v>
-      </c>
-      <c r="CX6" s="9">
+      <c r="CR6" s="7">
+        <v>0</v>
+      </c>
+      <c r="CS6" s="7">
+        <v>0</v>
+      </c>
+      <c r="CT6" s="7">
+        <v>0</v>
+      </c>
+      <c r="CU6" s="7">
+        <v>0</v>
+      </c>
+      <c r="CV6" s="7">
+        <v>0</v>
+      </c>
+      <c r="CW6" s="7">
+        <v>0</v>
+      </c>
+      <c r="CX6" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:102" x14ac:dyDescent="0.2">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="29" t="s">
         <v>66</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="30" t="s">
         <v>67</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="31">
         <v>189</v>
       </c>
-      <c r="D7" t="s">
-        <v>50</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="D7" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="E7" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="31" t="s">
         <v>69</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="32">
         <v>38376</v>
       </c>
-      <c r="H7" s="8">
+      <c r="H7" s="33">
         <v>0.25</v>
       </c>
-      <c r="I7" s="8">
+      <c r="I7" s="33">
         <v>0.25</v>
       </c>
-      <c r="J7" s="8">
+      <c r="J7" s="33">
         <v>3555990177.1700001</v>
       </c>
-      <c r="K7" s="7">
+      <c r="K7" s="5">
         <v>45873</v>
       </c>
       <c r="L7" t="s">
@@ -3406,121 +3411,121 @@
       <c r="Q7" t="s">
         <v>49</v>
       </c>
-      <c r="R7" s="8">
+      <c r="R7" s="6">
         <v>1.079668776833145</v>
       </c>
-      <c r="S7" s="7">
-        <v>45838</v>
-      </c>
-      <c r="T7" s="8">
+      <c r="S7" s="5">
+        <v>45838</v>
+      </c>
+      <c r="T7" s="6">
         <v>6.6585470969770171</v>
       </c>
-      <c r="U7" s="7">
+      <c r="U7" s="5">
         <v>45873</v>
       </c>
-      <c r="V7" s="8">
+      <c r="V7" s="6">
         <v>4.82151</v>
       </c>
-      <c r="W7" s="8">
+      <c r="W7" s="6">
         <v>14.245222</v>
       </c>
-      <c r="X7" s="8">
+      <c r="X7" s="6">
         <v>17.844851999999999</v>
       </c>
-      <c r="Y7" s="8">
+      <c r="Y7" s="6">
         <v>15.109679</v>
       </c>
-      <c r="Z7" s="8">
+      <c r="Z7" s="6">
         <v>13.158105000000001</v>
       </c>
-      <c r="AA7" s="8">
+      <c r="AA7" s="6">
         <v>9.9182450000000006</v>
       </c>
-      <c r="AB7" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AC7" s="8">
+      <c r="AB7" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AC7" s="6">
         <v>4.7322579999999999</v>
       </c>
-      <c r="AD7" s="8">
+      <c r="AD7" s="6">
         <v>14.081338000000001</v>
       </c>
-      <c r="AE7" s="8">
+      <c r="AE7" s="6">
         <v>17.819554</v>
       </c>
-      <c r="AF7" s="8">
+      <c r="AF7" s="6">
         <v>15.106916999999999</v>
       </c>
-      <c r="AG7" s="8">
+      <c r="AG7" s="6">
         <v>13.15011</v>
       </c>
-      <c r="AH7" s="8">
+      <c r="AH7" s="6">
         <v>9.913316</v>
       </c>
-      <c r="AI7" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AJ7" s="8">
+      <c r="AI7" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AJ7" s="6">
         <v>6.1985190000000001</v>
       </c>
-      <c r="AK7" s="8">
+      <c r="AK7" s="6">
         <v>13.176978</v>
       </c>
-      <c r="AL7" s="8">
+      <c r="AL7" s="6">
         <v>14.809665000000001</v>
       </c>
-      <c r="AM7" s="8">
+      <c r="AM7" s="6">
         <v>14.071407000000001</v>
       </c>
-      <c r="AN7" s="8">
+      <c r="AN7" s="6">
         <v>13.161388000000001</v>
       </c>
-      <c r="AO7" s="8">
+      <c r="AO7" s="6">
         <v>9.945138</v>
       </c>
-      <c r="AP7" s="7">
+      <c r="AP7" s="5">
         <v>45869</v>
       </c>
-      <c r="AQ7" s="8">
+      <c r="AQ7" s="6">
         <v>4.7322579999999999</v>
       </c>
-      <c r="AR7" s="8">
+      <c r="AR7" s="6">
         <v>14.081338000000001</v>
       </c>
-      <c r="AS7" s="8">
+      <c r="AS7" s="6">
         <v>17.819554</v>
       </c>
-      <c r="AT7" s="8">
+      <c r="AT7" s="6">
         <v>15.106916999999999</v>
       </c>
-      <c r="AU7" s="8">
+      <c r="AU7" s="6">
         <v>13.15011</v>
       </c>
-      <c r="AV7" s="8">
+      <c r="AV7" s="6">
         <v>9.913316</v>
       </c>
-      <c r="AW7" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AX7" s="8">
+      <c r="AW7" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AX7" s="6">
         <v>1.079668776833145</v>
       </c>
-      <c r="AY7" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AZ7" s="8">
+      <c r="AY7" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AZ7" s="6">
         <v>0.98580000000000001</v>
       </c>
-      <c r="BA7" s="8">
+      <c r="BA7" s="6">
         <v>0.98580000000000001</v>
       </c>
-      <c r="BB7" s="7">
+      <c r="BB7" s="5">
         <v>45838</v>
       </c>
       <c r="BC7" t="s">
         <v>50</v>
       </c>
-      <c r="BD7" s="8">
+      <c r="BD7" s="6">
         <v>1.25E-3</v>
       </c>
       <c r="BE7" t="s">
@@ -3532,7 +3537,7 @@
       <c r="BG7" t="s">
         <v>231</v>
       </c>
-      <c r="BH7" s="9">
+      <c r="BH7" s="7">
         <v>4.3700000000000003E-2</v>
       </c>
       <c r="BI7" t="s">
@@ -3541,7 +3546,7 @@
       <c r="BJ7">
         <v>9</v>
       </c>
-      <c r="BK7" s="11">
+      <c r="BK7" s="9">
         <v>0.15</v>
       </c>
       <c r="BL7" t="s">
@@ -3550,7 +3555,7 @@
       <c r="BM7">
         <v>10</v>
       </c>
-      <c r="BN7" s="11">
+      <c r="BN7" s="9">
         <v>0.09</v>
       </c>
       <c r="BO7" t="s">
@@ -3559,7 +3564,7 @@
       <c r="BP7">
         <v>17</v>
       </c>
-      <c r="BQ7" s="9">
+      <c r="BQ7" s="7">
         <v>3.7000000000000002E-3</v>
       </c>
       <c r="BR7" t="s">
@@ -3568,7 +3573,7 @@
       <c r="BS7">
         <v>1</v>
       </c>
-      <c r="BT7" s="9">
+      <c r="BT7" s="7">
         <v>1.9099999999999999E-2</v>
       </c>
       <c r="BU7" t="s">
@@ -3598,7 +3603,7 @@
       <c r="CC7" t="s">
         <v>119</v>
       </c>
-      <c r="CD7" s="9">
+      <c r="CD7" s="7">
         <v>0.26939999999999997</v>
       </c>
       <c r="CE7">
@@ -3607,7 +3612,7 @@
       <c r="CF7" t="s">
         <v>151</v>
       </c>
-      <c r="CG7" s="11">
+      <c r="CG7" s="9">
         <v>0</v>
       </c>
       <c r="CH7" t="s">
@@ -3625,75 +3630,75 @@
       <c r="CL7" t="s">
         <v>202</v>
       </c>
-      <c r="CM7" s="9">
+      <c r="CM7" s="7">
         <v>0.99950000000000006</v>
       </c>
-      <c r="CN7" s="9">
+      <c r="CN7" s="7">
         <v>0.996</v>
       </c>
-      <c r="CO7" s="10">
+      <c r="CO7" s="8">
         <v>3717</v>
       </c>
-      <c r="CP7" s="9">
+      <c r="CP7" s="7">
         <v>0.99829999999999997</v>
       </c>
-      <c r="CQ7" s="9">
+      <c r="CQ7" s="7">
         <v>0.99829999999999997</v>
       </c>
-      <c r="CR7" s="9">
-        <v>0</v>
-      </c>
-      <c r="CS7" s="9">
-        <v>0</v>
-      </c>
-      <c r="CT7" s="9">
-        <v>0</v>
-      </c>
-      <c r="CU7" s="9">
-        <v>0</v>
-      </c>
-      <c r="CV7" s="9">
-        <v>0</v>
-      </c>
-      <c r="CW7" s="9">
-        <v>0</v>
-      </c>
-      <c r="CX7" s="9">
+      <c r="CR7" s="7">
+        <v>0</v>
+      </c>
+      <c r="CS7" s="7">
+        <v>0</v>
+      </c>
+      <c r="CT7" s="7">
+        <v>0</v>
+      </c>
+      <c r="CU7" s="7">
+        <v>0</v>
+      </c>
+      <c r="CV7" s="7">
+        <v>0</v>
+      </c>
+      <c r="CW7" s="7">
+        <v>0</v>
+      </c>
+      <c r="CX7" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:102" x14ac:dyDescent="0.2">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="30" t="s">
         <v>71</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="31">
         <v>278</v>
       </c>
-      <c r="D8" t="s">
-        <v>50</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="D8" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="E8" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="F8" t="s">
+      <c r="F8" s="31" t="s">
         <v>73</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="32">
         <v>45083</v>
       </c>
-      <c r="H8" s="8">
+      <c r="H8" s="33">
         <v>0.08</v>
       </c>
-      <c r="I8" s="8">
+      <c r="I8" s="33">
         <v>0.08</v>
       </c>
-      <c r="J8" s="8">
+      <c r="J8" s="33">
         <v>2487467893.4499998</v>
       </c>
-      <c r="K8" s="7">
+      <c r="K8" s="5">
         <v>45873</v>
       </c>
       <c r="L8" t="s">
@@ -3714,22 +3719,22 @@
       <c r="Q8" t="s">
         <v>49</v>
       </c>
-      <c r="R8" s="8">
+      <c r="R8" s="6">
         <v>1.20816079378372</v>
       </c>
-      <c r="S8" s="7">
-        <v>45838</v>
-      </c>
-      <c r="T8" s="8">
+      <c r="S8" s="5">
+        <v>45838</v>
+      </c>
+      <c r="T8" s="6">
         <v>7.7197386275257243</v>
       </c>
-      <c r="U8" s="7">
+      <c r="U8" s="5">
         <v>45873</v>
       </c>
-      <c r="V8" s="8">
+      <c r="V8" s="6">
         <v>5.5974209999999998</v>
       </c>
-      <c r="W8" s="8">
+      <c r="W8" s="6">
         <v>15.150401</v>
       </c>
       <c r="X8" t="s">
@@ -3741,16 +3746,16 @@
       <c r="Z8" t="s">
         <v>50</v>
       </c>
-      <c r="AA8" s="8">
+      <c r="AA8" s="6">
         <v>22.272876</v>
       </c>
-      <c r="AB8" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AC8" s="8">
+      <c r="AB8" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AC8" s="6">
         <v>5.5774749999999997</v>
       </c>
-      <c r="AD8" s="8">
+      <c r="AD8" s="6">
         <v>15.153062</v>
       </c>
       <c r="AE8" t="s">
@@ -3762,16 +3767,16 @@
       <c r="AG8" t="s">
         <v>50</v>
       </c>
-      <c r="AH8" s="8">
+      <c r="AH8" s="6">
         <v>22.307081</v>
       </c>
-      <c r="AI8" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AJ8" s="8">
+      <c r="AI8" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AJ8" s="6">
         <v>7.8709920000000002</v>
       </c>
-      <c r="AK8" s="8">
+      <c r="AK8" s="6">
         <v>16.550301000000001</v>
       </c>
       <c r="AL8" t="s">
@@ -3783,16 +3788,16 @@
       <c r="AN8" t="s">
         <v>50</v>
       </c>
-      <c r="AO8" s="8">
+      <c r="AO8" s="6">
         <v>22.513235999999999</v>
       </c>
-      <c r="AP8" s="7">
+      <c r="AP8" s="5">
         <v>45869</v>
       </c>
-      <c r="AQ8" s="8">
+      <c r="AQ8" s="6">
         <v>5.5774749999999997</v>
       </c>
-      <c r="AR8" s="8">
+      <c r="AR8" s="6">
         <v>15.153062</v>
       </c>
       <c r="AS8" t="s">
@@ -3804,31 +3809,31 @@
       <c r="AU8" t="s">
         <v>50</v>
       </c>
-      <c r="AV8" s="8">
+      <c r="AV8" s="6">
         <v>22.307081</v>
       </c>
-      <c r="AW8" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AX8" s="8">
+      <c r="AW8" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AX8" s="6">
         <v>1.20816079378372</v>
       </c>
-      <c r="AY8" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AZ8" s="8">
+      <c r="AY8" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AZ8" s="6">
         <v>1.1586000000000001</v>
       </c>
-      <c r="BA8" s="8">
+      <c r="BA8" s="6">
         <v>1.1586000000000001</v>
       </c>
-      <c r="BB8" s="7">
+      <c r="BB8" s="5">
         <v>45838</v>
       </c>
       <c r="BC8" t="s">
         <v>50</v>
       </c>
-      <c r="BD8" s="8">
+      <c r="BD8" s="6">
         <v>1.3799999999999999E-3</v>
       </c>
       <c r="BE8" t="s">
@@ -3840,7 +3845,7 @@
       <c r="BG8" t="s">
         <v>232</v>
       </c>
-      <c r="BH8" s="9">
+      <c r="BH8" s="7">
         <v>5.4600000000000003E-2</v>
       </c>
       <c r="BI8" t="s">
@@ -3849,7 +3854,7 @@
       <c r="BJ8">
         <v>26</v>
       </c>
-      <c r="BK8" s="11">
+      <c r="BK8" s="9">
         <v>0.23</v>
       </c>
       <c r="BL8" t="s">
@@ -3858,7 +3863,7 @@
       <c r="BM8">
         <v>20</v>
       </c>
-      <c r="BN8" s="11">
+      <c r="BN8" s="9">
         <v>0.17</v>
       </c>
       <c r="BO8" t="s">
@@ -3867,7 +3872,7 @@
       <c r="BP8">
         <v>29</v>
       </c>
-      <c r="BQ8" s="9">
+      <c r="BQ8" s="7">
         <v>1.4500000000000001E-2</v>
       </c>
       <c r="BR8" t="s">
@@ -3876,7 +3881,7 @@
       <c r="BS8">
         <v>3</v>
       </c>
-      <c r="BT8" s="9">
+      <c r="BT8" s="7">
         <v>1.3899999999999999E-2</v>
       </c>
       <c r="BU8" t="s">
@@ -3906,7 +3911,7 @@
       <c r="CC8" t="s">
         <v>119</v>
       </c>
-      <c r="CD8" s="9">
+      <c r="CD8" s="7">
         <v>0.21149999999999999</v>
       </c>
       <c r="CE8">
@@ -3915,7 +3920,7 @@
       <c r="CF8" t="s">
         <v>152</v>
       </c>
-      <c r="CG8" s="9">
+      <c r="CG8" s="7">
         <v>2.4799999999999999E-2</v>
       </c>
       <c r="CH8" t="s">
@@ -3933,75 +3938,75 @@
       <c r="CL8" t="s">
         <v>208</v>
       </c>
-      <c r="CM8" s="9">
+      <c r="CM8" s="7">
         <v>0.99939999999999996</v>
       </c>
-      <c r="CN8" s="9">
+      <c r="CN8" s="7">
         <v>0.57840000000000003</v>
       </c>
-      <c r="CO8" s="10">
+      <c r="CO8" s="8">
         <v>3717</v>
       </c>
-      <c r="CP8" s="9">
+      <c r="CP8" s="7">
         <v>0.99770000000000003</v>
       </c>
-      <c r="CQ8" s="9">
+      <c r="CQ8" s="7">
         <v>0.99770000000000003</v>
       </c>
-      <c r="CR8" s="9">
-        <v>0</v>
-      </c>
-      <c r="CS8" s="9">
-        <v>0</v>
-      </c>
-      <c r="CT8" s="9">
-        <v>0</v>
-      </c>
-      <c r="CU8" s="9">
-        <v>0</v>
-      </c>
-      <c r="CV8" s="9">
-        <v>0</v>
-      </c>
-      <c r="CW8" s="9">
-        <v>0</v>
-      </c>
-      <c r="CX8" s="9">
+      <c r="CR8" s="7">
+        <v>0</v>
+      </c>
+      <c r="CS8" s="7">
+        <v>0</v>
+      </c>
+      <c r="CT8" s="7">
+        <v>0</v>
+      </c>
+      <c r="CU8" s="7">
+        <v>0</v>
+      </c>
+      <c r="CV8" s="7">
+        <v>0</v>
+      </c>
+      <c r="CW8" s="7">
+        <v>0</v>
+      </c>
+      <c r="CX8" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:102" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="29" t="s">
         <v>74</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="30" t="s">
         <v>75</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="31">
         <v>178</v>
       </c>
-      <c r="D9" t="s">
-        <v>50</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="D9" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="E9" s="31" t="s">
         <v>76</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F9" s="31" t="s">
         <v>77</v>
       </c>
-      <c r="G9" s="7">
+      <c r="G9" s="32">
         <v>44600</v>
       </c>
-      <c r="H9" s="8">
+      <c r="H9" s="33">
         <v>0.1</v>
       </c>
-      <c r="I9" s="8">
+      <c r="I9" s="33">
         <v>0.1</v>
       </c>
-      <c r="J9" s="8">
+      <c r="J9" s="33">
         <v>2177420259.2199998</v>
       </c>
-      <c r="K9" s="7">
+      <c r="K9" s="5">
         <v>45873</v>
       </c>
       <c r="L9" t="s">
@@ -4022,25 +4027,25 @@
       <c r="Q9" t="s">
         <v>49</v>
       </c>
-      <c r="R9" s="8">
+      <c r="R9" s="6">
         <v>0.98873002934529397</v>
       </c>
-      <c r="S9" s="7">
-        <v>45838</v>
-      </c>
-      <c r="T9" s="8">
+      <c r="S9" s="5">
+        <v>45838</v>
+      </c>
+      <c r="T9" s="6">
         <v>5.720454459014058</v>
       </c>
-      <c r="U9" s="7">
+      <c r="U9" s="5">
         <v>45873</v>
       </c>
-      <c r="V9" s="8">
+      <c r="V9" s="6">
         <v>3.5128249999999999</v>
       </c>
-      <c r="W9" s="8">
+      <c r="W9" s="6">
         <v>13.788335</v>
       </c>
-      <c r="X9" s="8">
+      <c r="X9" s="6">
         <v>18.608317</v>
       </c>
       <c r="Y9" t="s">
@@ -4049,19 +4054,19 @@
       <c r="Z9" t="s">
         <v>50</v>
       </c>
-      <c r="AA9" s="8">
+      <c r="AA9" s="6">
         <v>9.9162599999999994</v>
       </c>
-      <c r="AB9" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AC9" s="8">
+      <c r="AB9" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AC9" s="6">
         <v>3.2091080000000001</v>
       </c>
-      <c r="AD9" s="8">
+      <c r="AD9" s="6">
         <v>13.512902</v>
       </c>
-      <c r="AE9" s="8">
+      <c r="AE9" s="6">
         <v>18.640571999999999</v>
       </c>
       <c r="AF9" t="s">
@@ -4070,19 +4075,19 @@
       <c r="AG9" t="s">
         <v>50</v>
       </c>
-      <c r="AH9" s="8">
+      <c r="AH9" s="6">
         <v>9.8785869999999996</v>
       </c>
-      <c r="AI9" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AJ9" s="8">
+      <c r="AI9" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AJ9" s="6">
         <v>5.4437160000000002</v>
       </c>
-      <c r="AK9" s="8">
+      <c r="AK9" s="6">
         <v>14.116254</v>
       </c>
-      <c r="AL9" s="8">
+      <c r="AL9" s="6">
         <v>15.416285</v>
       </c>
       <c r="AM9" t="s">
@@ -4091,19 +4096,19 @@
       <c r="AN9" t="s">
         <v>50</v>
       </c>
-      <c r="AO9" s="8">
+      <c r="AO9" s="6">
         <v>10.247446999999999</v>
       </c>
-      <c r="AP9" s="7">
+      <c r="AP9" s="5">
         <v>45869</v>
       </c>
-      <c r="AQ9" s="8">
+      <c r="AQ9" s="6">
         <v>3.2091080000000001</v>
       </c>
-      <c r="AR9" s="8">
+      <c r="AR9" s="6">
         <v>13.512902</v>
       </c>
-      <c r="AS9" s="8">
+      <c r="AS9" s="6">
         <v>18.640571999999999</v>
       </c>
       <c r="AT9" t="s">
@@ -4112,31 +4117,31 @@
       <c r="AU9" t="s">
         <v>50</v>
       </c>
-      <c r="AV9" s="8">
+      <c r="AV9" s="6">
         <v>9.8785869999999996</v>
       </c>
-      <c r="AW9" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AX9" s="8">
+      <c r="AW9" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AX9" s="6">
         <v>0.98873002934529397</v>
       </c>
-      <c r="AY9" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AZ9" s="8">
+      <c r="AY9" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AZ9" s="6">
         <v>0.90590000000000004</v>
       </c>
-      <c r="BA9" s="8">
+      <c r="BA9" s="6">
         <v>0.90590000000000004</v>
       </c>
-      <c r="BB9" s="7">
+      <c r="BB9" s="5">
         <v>45838</v>
       </c>
       <c r="BC9" t="s">
         <v>50</v>
       </c>
-      <c r="BD9" s="8">
+      <c r="BD9" s="6">
         <v>9.3000000000000005E-4</v>
       </c>
       <c r="BE9" t="s">
@@ -4148,7 +4153,7 @@
       <c r="BG9" t="s">
         <v>233</v>
       </c>
-      <c r="BH9" s="9">
+      <c r="BH9" s="7">
         <v>1.0800000000000001E-2</v>
       </c>
       <c r="BI9" t="s">
@@ -4157,7 +4162,7 @@
       <c r="BJ9">
         <v>2</v>
       </c>
-      <c r="BK9" s="11">
+      <c r="BK9" s="9">
         <v>0.2</v>
       </c>
       <c r="BL9" t="s">
@@ -4166,7 +4171,7 @@
       <c r="BM9">
         <v>12</v>
       </c>
-      <c r="BN9" s="9">
+      <c r="BN9" s="7">
         <v>7.8700000000000006E-2</v>
       </c>
       <c r="BO9" t="s">
@@ -4175,7 +4180,7 @@
       <c r="BP9">
         <v>6</v>
       </c>
-      <c r="BQ9" s="11">
+      <c r="BQ9" s="9">
         <v>0</v>
       </c>
       <c r="BR9" t="s">
@@ -4184,7 +4189,7 @@
       <c r="BS9">
         <v>0</v>
       </c>
-      <c r="BT9" s="9">
+      <c r="BT9" s="7">
         <v>5.4999999999999997E-3</v>
       </c>
       <c r="BU9" t="s">
@@ -4214,7 +4219,7 @@
       <c r="CC9" t="s">
         <v>120</v>
       </c>
-      <c r="CD9" s="9">
+      <c r="CD9" s="7">
         <v>0.30620000000000003</v>
       </c>
       <c r="CE9">
@@ -4223,7 +4228,7 @@
       <c r="CF9" t="s">
         <v>153</v>
       </c>
-      <c r="CG9" s="11">
+      <c r="CG9" s="9">
         <v>0</v>
       </c>
       <c r="CH9" t="s">
@@ -4241,75 +4246,75 @@
       <c r="CL9" t="s">
         <v>202</v>
       </c>
-      <c r="CM9" s="9">
+      <c r="CM9" s="7">
         <v>0.99970000000000003</v>
       </c>
-      <c r="CN9" s="9">
+      <c r="CN9" s="7">
         <v>0.84230000000000005</v>
       </c>
-      <c r="CO9" s="10">
+      <c r="CO9" s="8">
         <v>3717</v>
       </c>
-      <c r="CP9" s="9">
+      <c r="CP9" s="7">
         <v>0.99719999999999998</v>
       </c>
-      <c r="CQ9" s="9">
+      <c r="CQ9" s="7">
         <v>0.99719999999999998</v>
       </c>
-      <c r="CR9" s="9">
-        <v>0</v>
-      </c>
-      <c r="CS9" s="9">
-        <v>0</v>
-      </c>
-      <c r="CT9" s="9">
-        <v>0</v>
-      </c>
-      <c r="CU9" s="9">
-        <v>0</v>
-      </c>
-      <c r="CV9" s="9">
-        <v>0</v>
-      </c>
-      <c r="CW9" s="9">
-        <v>0</v>
-      </c>
-      <c r="CX9" s="9">
+      <c r="CR9" s="7">
+        <v>0</v>
+      </c>
+      <c r="CS9" s="7">
+        <v>0</v>
+      </c>
+      <c r="CT9" s="7">
+        <v>0</v>
+      </c>
+      <c r="CU9" s="7">
+        <v>0</v>
+      </c>
+      <c r="CV9" s="7">
+        <v>0</v>
+      </c>
+      <c r="CW9" s="7">
+        <v>0</v>
+      </c>
+      <c r="CX9" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:102" x14ac:dyDescent="0.2">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="29" t="s">
         <v>78</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="31">
         <v>905</v>
       </c>
-      <c r="D10" t="s">
-        <v>50</v>
-      </c>
-      <c r="E10" t="s">
+      <c r="D10" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="E10" s="31" t="s">
         <v>80</v>
       </c>
-      <c r="F10" t="s">
+      <c r="F10" s="31" t="s">
         <v>81</v>
       </c>
-      <c r="G10" s="7">
+      <c r="G10" s="32">
         <v>43200</v>
       </c>
-      <c r="H10" s="8">
+      <c r="H10" s="33">
         <v>0.17</v>
       </c>
-      <c r="I10" s="8">
+      <c r="I10" s="33">
         <v>0.17</v>
       </c>
-      <c r="J10" s="8">
+      <c r="J10" s="33">
         <v>1878348896.0899999</v>
       </c>
-      <c r="K10" s="7">
+      <c r="K10" s="5">
         <v>45873</v>
       </c>
       <c r="L10" t="s">
@@ -4330,121 +4335,121 @@
       <c r="Q10" t="s">
         <v>49</v>
       </c>
-      <c r="R10" s="8">
+      <c r="R10" s="6">
         <v>1.299487702357762</v>
       </c>
-      <c r="S10" s="7">
-        <v>45838</v>
-      </c>
-      <c r="T10" s="8">
+      <c r="S10" s="5">
+        <v>45838</v>
+      </c>
+      <c r="T10" s="6">
         <v>0.54743110867940192</v>
       </c>
-      <c r="U10" s="7">
+      <c r="U10" s="5">
         <v>45873</v>
       </c>
-      <c r="V10" s="8">
+      <c r="V10" s="6">
         <v>-1.0554140000000001</v>
       </c>
-      <c r="W10" s="8">
+      <c r="W10" s="6">
         <v>8.7506760000000003</v>
       </c>
-      <c r="X10" s="8">
+      <c r="X10" s="6">
         <v>11.062139</v>
       </c>
-      <c r="Y10" s="8">
+      <c r="Y10" s="6">
         <v>11.98718</v>
       </c>
       <c r="Z10" t="s">
         <v>50</v>
       </c>
-      <c r="AA10" s="8">
+      <c r="AA10" s="6">
         <v>8.2874490000000005</v>
       </c>
-      <c r="AB10" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AC10" s="8">
+      <c r="AB10" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AC10" s="6">
         <v>-1.163438</v>
       </c>
-      <c r="AD10" s="8">
+      <c r="AD10" s="6">
         <v>8.7549349999999997</v>
       </c>
-      <c r="AE10" s="8">
+      <c r="AE10" s="6">
         <v>11.003895999999999</v>
       </c>
-      <c r="AF10" s="8">
+      <c r="AF10" s="6">
         <v>11.965971</v>
       </c>
       <c r="AG10" t="s">
         <v>50</v>
       </c>
-      <c r="AH10" s="8">
+      <c r="AH10" s="6">
         <v>8.2785790000000006</v>
       </c>
-      <c r="AI10" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AJ10" s="8">
+      <c r="AI10" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AJ10" s="6">
         <v>0.57562199999999997</v>
       </c>
-      <c r="AK10" s="8">
+      <c r="AK10" s="6">
         <v>2.5751379999999999</v>
       </c>
-      <c r="AL10" s="8">
+      <c r="AL10" s="6">
         <v>8.0057659999999995</v>
       </c>
-      <c r="AM10" s="8">
+      <c r="AM10" s="6">
         <v>11.451181</v>
       </c>
       <c r="AN10" t="s">
         <v>50</v>
       </c>
-      <c r="AO10" s="8">
+      <c r="AO10" s="6">
         <v>8.4295790000000004</v>
       </c>
-      <c r="AP10" s="7">
+      <c r="AP10" s="5">
         <v>45869</v>
       </c>
-      <c r="AQ10" s="8">
+      <c r="AQ10" s="6">
         <v>-1.163438</v>
       </c>
-      <c r="AR10" s="8">
+      <c r="AR10" s="6">
         <v>8.7549349999999997</v>
       </c>
-      <c r="AS10" s="8">
+      <c r="AS10" s="6">
         <v>11.003895999999999</v>
       </c>
-      <c r="AT10" s="8">
+      <c r="AT10" s="6">
         <v>11.965971</v>
       </c>
       <c r="AU10" t="s">
         <v>50</v>
       </c>
-      <c r="AV10" s="8">
+      <c r="AV10" s="6">
         <v>8.2785790000000006</v>
       </c>
-      <c r="AW10" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AX10" s="8">
+      <c r="AW10" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AX10" s="6">
         <v>1.299487702357762</v>
       </c>
-      <c r="AY10" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AZ10" s="8">
+      <c r="AY10" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AZ10" s="6">
         <v>1.3073999999999999</v>
       </c>
-      <c r="BA10" s="8">
+      <c r="BA10" s="6">
         <v>1.3073999999999999</v>
       </c>
-      <c r="BB10" s="7">
+      <c r="BB10" s="5">
         <v>45838</v>
       </c>
       <c r="BC10" t="s">
         <v>50</v>
       </c>
-      <c r="BD10" s="8">
+      <c r="BD10" s="6">
         <v>3.5300000000000002E-3</v>
       </c>
       <c r="BE10" t="s">
@@ -4456,7 +4461,7 @@
       <c r="BG10" t="s">
         <v>229</v>
       </c>
-      <c r="BH10" s="9">
+      <c r="BH10" s="7">
         <v>6.2899999999999998E-2</v>
       </c>
       <c r="BI10" t="s">
@@ -4465,7 +4470,7 @@
       <c r="BJ10">
         <v>45</v>
       </c>
-      <c r="BK10" s="9">
+      <c r="BK10" s="7">
         <v>1.9599999999999999E-2</v>
       </c>
       <c r="BL10" t="s">
@@ -4474,7 +4479,7 @@
       <c r="BM10">
         <v>15</v>
       </c>
-      <c r="BN10" s="9">
+      <c r="BN10" s="7">
         <v>1.9599999999999999E-2</v>
       </c>
       <c r="BO10" t="s">
@@ -4483,7 +4488,7 @@
       <c r="BP10">
         <v>12</v>
       </c>
-      <c r="BQ10" s="9">
+      <c r="BQ10" s="7">
         <v>2.2000000000000001E-3</v>
       </c>
       <c r="BR10" t="s">
@@ -4492,7 +4497,7 @@
       <c r="BS10">
         <v>2</v>
       </c>
-      <c r="BT10" s="9">
+      <c r="BT10" s="7">
         <v>4.9299999999999997E-2</v>
       </c>
       <c r="BU10" t="s">
@@ -4522,7 +4527,7 @@
       <c r="CC10" t="s">
         <v>119</v>
       </c>
-      <c r="CD10" s="9">
+      <c r="CD10" s="7">
         <v>8.6E-3</v>
       </c>
       <c r="CE10">
@@ -4531,7 +4536,7 @@
       <c r="CF10" t="s">
         <v>154</v>
       </c>
-      <c r="CG10" s="9">
+      <c r="CG10" s="7">
         <v>2.0899999999999998E-2</v>
       </c>
       <c r="CH10" t="s">
@@ -4549,75 +4554,75 @@
       <c r="CL10" t="s">
         <v>208</v>
       </c>
-      <c r="CM10" s="9">
+      <c r="CM10" s="7">
         <v>0.99819999999999998</v>
       </c>
-      <c r="CN10" s="9">
+      <c r="CN10" s="7">
         <v>0.89170000000000005</v>
       </c>
-      <c r="CO10" s="10">
+      <c r="CO10" s="8">
         <v>1431</v>
       </c>
-      <c r="CP10" s="9">
+      <c r="CP10" s="7">
         <v>0.99660000000000004</v>
       </c>
-      <c r="CQ10" s="9">
+      <c r="CQ10" s="7">
         <v>0.98280000000000001</v>
       </c>
-      <c r="CR10" s="9">
-        <v>0</v>
-      </c>
-      <c r="CS10" s="9">
-        <v>0</v>
-      </c>
-      <c r="CT10" s="9">
-        <v>0</v>
-      </c>
-      <c r="CU10" s="9">
-        <v>0</v>
-      </c>
-      <c r="CV10" s="9">
-        <v>0</v>
-      </c>
-      <c r="CW10" s="9">
-        <v>0</v>
-      </c>
-      <c r="CX10" s="9">
+      <c r="CR10" s="7">
+        <v>0</v>
+      </c>
+      <c r="CS10" s="7">
+        <v>0</v>
+      </c>
+      <c r="CT10" s="7">
+        <v>0</v>
+      </c>
+      <c r="CU10" s="7">
+        <v>0</v>
+      </c>
+      <c r="CV10" s="7">
+        <v>0</v>
+      </c>
+      <c r="CW10" s="7">
+        <v>0</v>
+      </c>
+      <c r="CX10" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:102" x14ac:dyDescent="0.2">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="29" t="s">
         <v>83</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="31">
         <v>129</v>
       </c>
-      <c r="D11" t="s">
-        <v>50</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="D11" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="E11" s="31" t="s">
         <v>85</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F11" s="31" t="s">
         <v>86</v>
       </c>
-      <c r="G11" s="7">
+      <c r="G11" s="32">
         <v>39623</v>
       </c>
-      <c r="H11" s="8">
+      <c r="H11" s="33">
         <v>0.41</v>
       </c>
-      <c r="I11" s="8">
+      <c r="I11" s="33">
         <v>0.41</v>
       </c>
-      <c r="J11" s="8">
+      <c r="J11" s="33">
         <v>1457155418.3099999</v>
       </c>
-      <c r="K11" s="7">
+      <c r="K11" s="5">
         <v>45873</v>
       </c>
       <c r="L11" t="s">
@@ -4638,121 +4643,121 @@
       <c r="Q11" t="s">
         <v>49</v>
       </c>
-      <c r="R11" s="8">
+      <c r="R11" s="6">
         <v>1.9376</v>
       </c>
-      <c r="S11" s="7">
-        <v>45838</v>
-      </c>
-      <c r="T11" s="8">
+      <c r="S11" s="5">
+        <v>45838</v>
+      </c>
+      <c r="T11" s="6">
         <v>20.161559484429556</v>
       </c>
-      <c r="U11" s="7">
+      <c r="U11" s="5">
         <v>45873</v>
       </c>
-      <c r="V11" s="8">
+      <c r="V11" s="6">
         <v>16.11</v>
       </c>
-      <c r="W11" s="8">
+      <c r="W11" s="6">
         <v>-0.15</v>
       </c>
-      <c r="X11" s="8">
+      <c r="X11" s="6">
         <v>-10.4</v>
       </c>
-      <c r="Y11" s="8">
+      <c r="Y11" s="6">
         <v>2.29</v>
       </c>
-      <c r="Z11" s="8">
+      <c r="Z11" s="6">
         <v>3.49</v>
       </c>
-      <c r="AA11" s="8">
+      <c r="AA11" s="6">
         <v>-5.82</v>
       </c>
-      <c r="AB11" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AC11" s="8">
+      <c r="AB11" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AC11" s="6">
         <v>16.41</v>
       </c>
-      <c r="AD11" s="8">
+      <c r="AD11" s="6">
         <v>0.42</v>
       </c>
-      <c r="AE11" s="8">
+      <c r="AE11" s="6">
         <v>-10.43</v>
       </c>
-      <c r="AF11" s="8">
+      <c r="AF11" s="6">
         <v>2.2400000000000002</v>
       </c>
-      <c r="AG11" s="8">
+      <c r="AG11" s="6">
         <v>3.53</v>
       </c>
-      <c r="AH11" s="8">
+      <c r="AH11" s="6">
         <v>-5.81</v>
       </c>
-      <c r="AI11" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AJ11" s="8">
+      <c r="AI11" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AJ11" s="6">
         <v>19.03</v>
       </c>
-      <c r="AK11" s="8">
+      <c r="AK11" s="6">
         <v>-3.08</v>
       </c>
-      <c r="AL11" s="8">
+      <c r="AL11" s="6">
         <v>-14.33</v>
       </c>
-      <c r="AM11" s="8">
+      <c r="AM11" s="6">
         <v>-0.16</v>
       </c>
-      <c r="AN11" s="8">
+      <c r="AN11" s="6">
         <v>4.32</v>
       </c>
-      <c r="AO11" s="8">
+      <c r="AO11" s="6">
         <v>-5.65</v>
       </c>
-      <c r="AP11" s="7">
+      <c r="AP11" s="5">
         <v>45869</v>
       </c>
-      <c r="AQ11" s="8">
+      <c r="AQ11" s="6">
         <v>16.41</v>
       </c>
-      <c r="AR11" s="8">
+      <c r="AR11" s="6">
         <v>0.42</v>
       </c>
-      <c r="AS11" s="8">
+      <c r="AS11" s="6">
         <v>-10.43</v>
       </c>
-      <c r="AT11" s="8">
+      <c r="AT11" s="6">
         <v>2.2400000000000002</v>
       </c>
-      <c r="AU11" s="8">
+      <c r="AU11" s="6">
         <v>3.53</v>
       </c>
-      <c r="AV11" s="8">
+      <c r="AV11" s="6">
         <v>-5.81</v>
       </c>
-      <c r="AW11" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AX11" s="8">
+      <c r="AW11" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AX11" s="6">
         <v>1.9376</v>
       </c>
-      <c r="AY11" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AZ11" s="8">
+      <c r="AY11" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AZ11" s="6">
         <v>1.7697000000000001</v>
       </c>
-      <c r="BA11" s="8">
+      <c r="BA11" s="6">
         <v>1.7697000000000001</v>
       </c>
-      <c r="BB11" s="7">
+      <c r="BB11" s="5">
         <v>45838</v>
       </c>
       <c r="BC11" t="s">
         <v>50</v>
       </c>
-      <c r="BD11" s="8">
+      <c r="BD11" s="6">
         <v>4.6000000000000001E-4</v>
       </c>
       <c r="BE11" t="s">
@@ -4764,7 +4769,7 @@
       <c r="BG11" t="s">
         <v>234</v>
       </c>
-      <c r="BH11" s="9">
+      <c r="BH11" s="7">
         <v>0.2215</v>
       </c>
       <c r="BI11" t="s">
@@ -4773,7 +4778,7 @@
       <c r="BJ11">
         <v>10</v>
       </c>
-      <c r="BK11" s="11">
+      <c r="BK11" s="9">
         <v>0</v>
       </c>
       <c r="BL11" t="s">
@@ -4782,7 +4787,7 @@
       <c r="BM11">
         <v>0</v>
       </c>
-      <c r="BN11" s="11">
+      <c r="BN11" s="9">
         <v>0</v>
       </c>
       <c r="BO11" t="s">
@@ -4791,7 +4796,7 @@
       <c r="BP11">
         <v>0</v>
       </c>
-      <c r="BQ11" s="11">
+      <c r="BQ11" s="9">
         <v>0</v>
       </c>
       <c r="BR11" t="s">
@@ -4800,7 +4805,7 @@
       <c r="BS11">
         <v>0</v>
       </c>
-      <c r="BT11" s="11">
+      <c r="BT11" s="9">
         <v>0</v>
       </c>
       <c r="BU11" t="s">
@@ -4830,7 +4835,7 @@
       <c r="CC11" t="s">
         <v>120</v>
       </c>
-      <c r="CD11" s="9">
+      <c r="CD11" s="7">
         <v>0.38700000000000001</v>
       </c>
       <c r="CE11">
@@ -4839,7 +4844,7 @@
       <c r="CF11" t="s">
         <v>155</v>
       </c>
-      <c r="CG11" s="11">
+      <c r="CG11" s="9">
         <v>0</v>
       </c>
       <c r="CH11" t="s">
@@ -4857,75 +4862,75 @@
       <c r="CL11" t="s">
         <v>224</v>
       </c>
-      <c r="CM11" s="9">
+      <c r="CM11" s="7">
         <v>0.94389999999999996</v>
       </c>
-      <c r="CN11" s="9">
+      <c r="CN11" s="7">
         <v>0.76</v>
       </c>
       <c r="CO11">
         <v>325</v>
       </c>
-      <c r="CP11" s="9">
+      <c r="CP11" s="7">
         <v>0.96740000000000004</v>
       </c>
-      <c r="CQ11" s="9">
+      <c r="CQ11" s="7">
         <v>0.96550000000000002</v>
       </c>
-      <c r="CR11" s="9">
-        <v>0</v>
-      </c>
-      <c r="CS11" s="9">
-        <v>0</v>
-      </c>
-      <c r="CT11" s="9">
-        <v>0</v>
-      </c>
-      <c r="CU11" s="9">
-        <v>0</v>
-      </c>
-      <c r="CV11" s="9">
-        <v>0</v>
-      </c>
-      <c r="CW11" s="9">
-        <v>0</v>
-      </c>
-      <c r="CX11" s="9">
+      <c r="CR11" s="7">
+        <v>0</v>
+      </c>
+      <c r="CS11" s="7">
+        <v>0</v>
+      </c>
+      <c r="CT11" s="7">
+        <v>0</v>
+      </c>
+      <c r="CU11" s="7">
+        <v>0</v>
+      </c>
+      <c r="CV11" s="7">
+        <v>0</v>
+      </c>
+      <c r="CW11" s="7">
+        <v>0</v>
+      </c>
+      <c r="CX11" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:102" x14ac:dyDescent="0.2">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="29" t="s">
         <v>88</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="30" t="s">
         <v>89</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="31">
         <v>306</v>
       </c>
-      <c r="D12" t="s">
-        <v>50</v>
-      </c>
-      <c r="E12" t="s">
+      <c r="D12" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" s="31" t="s">
         <v>90</v>
       </c>
-      <c r="F12" t="s">
+      <c r="F12" s="31" t="s">
         <v>91</v>
       </c>
-      <c r="G12" s="7">
+      <c r="G12" s="32">
         <v>44292</v>
       </c>
-      <c r="H12" s="8">
+      <c r="H12" s="33">
         <v>0.28999999999999998</v>
       </c>
-      <c r="I12" s="8">
+      <c r="I12" s="33">
         <v>0.14000000000000001</v>
       </c>
-      <c r="J12" s="8">
+      <c r="J12" s="33">
         <v>1305135788.3099999</v>
       </c>
-      <c r="K12" s="7">
+      <c r="K12" s="5">
         <v>45873</v>
       </c>
       <c r="L12" t="s">
@@ -4946,25 +4951,25 @@
       <c r="Q12" t="s">
         <v>92</v>
       </c>
-      <c r="R12" s="8">
+      <c r="R12" s="6">
         <v>1.1874</v>
       </c>
-      <c r="S12" s="7">
-        <v>45838</v>
-      </c>
-      <c r="T12" s="8">
+      <c r="S12" s="5">
+        <v>45838</v>
+      </c>
+      <c r="T12" s="6">
         <v>8.0162786142467954</v>
       </c>
-      <c r="U12" s="7">
+      <c r="U12" s="5">
         <v>45873</v>
       </c>
-      <c r="V12" s="8">
+      <c r="V12" s="6">
         <v>5.63</v>
       </c>
-      <c r="W12" s="8">
+      <c r="W12" s="6">
         <v>14.72</v>
       </c>
-      <c r="X12" s="8">
+      <c r="X12" s="6">
         <v>18.82</v>
       </c>
       <c r="Y12" t="s">
@@ -4973,19 +4978,19 @@
       <c r="Z12" t="s">
         <v>50</v>
       </c>
-      <c r="AA12" s="8">
+      <c r="AA12" s="6">
         <v>10.93</v>
       </c>
-      <c r="AB12" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AC12" s="8">
+      <c r="AB12" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AC12" s="6">
         <v>5.57</v>
       </c>
-      <c r="AD12" s="8">
+      <c r="AD12" s="6">
         <v>14.68</v>
       </c>
-      <c r="AE12" s="8">
+      <c r="AE12" s="6">
         <v>18.97</v>
       </c>
       <c r="AF12" t="s">
@@ -4994,19 +4999,19 @@
       <c r="AG12" t="s">
         <v>50</v>
       </c>
-      <c r="AH12" s="8">
+      <c r="AH12" s="6">
         <v>10.94</v>
       </c>
-      <c r="AI12" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AJ12" s="8">
+      <c r="AI12" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AJ12" s="6">
         <v>8.1199999999999992</v>
       </c>
-      <c r="AK12" s="8">
+      <c r="AK12" s="6">
         <v>15.97</v>
       </c>
-      <c r="AL12" s="8">
+      <c r="AL12" s="6">
         <v>16.2</v>
       </c>
       <c r="AM12" t="s">
@@ -5015,19 +5020,19 @@
       <c r="AN12" t="s">
         <v>50</v>
       </c>
-      <c r="AO12" s="8">
+      <c r="AO12" s="6">
         <v>11.3</v>
       </c>
-      <c r="AP12" s="7">
+      <c r="AP12" s="5">
         <v>45869</v>
       </c>
-      <c r="AQ12" s="8">
+      <c r="AQ12" s="6">
         <v>5.57</v>
       </c>
-      <c r="AR12" s="8">
+      <c r="AR12" s="6">
         <v>14.68</v>
       </c>
-      <c r="AS12" s="8">
+      <c r="AS12" s="6">
         <v>18.97</v>
       </c>
       <c r="AT12" t="s">
@@ -5036,31 +5041,31 @@
       <c r="AU12" t="s">
         <v>50</v>
       </c>
-      <c r="AV12" s="8">
+      <c r="AV12" s="6">
         <v>10.94</v>
       </c>
-      <c r="AW12" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AX12" s="8">
+      <c r="AW12" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AX12" s="6">
         <v>1.1874</v>
       </c>
-      <c r="AY12" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AZ12" s="8">
+      <c r="AY12" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AZ12" s="6">
         <v>1.0831999999999999</v>
       </c>
-      <c r="BA12" s="8">
+      <c r="BA12" s="6">
         <v>0.93879999999999997</v>
       </c>
-      <c r="BB12" s="7">
+      <c r="BB12" s="5">
         <v>45838</v>
       </c>
       <c r="BC12" t="s">
         <v>50</v>
       </c>
-      <c r="BD12" s="8">
+      <c r="BD12" s="6">
         <v>5.96E-3</v>
       </c>
       <c r="BE12" t="s">
@@ -5072,7 +5077,7 @@
       <c r="BG12" t="s">
         <v>235</v>
       </c>
-      <c r="BH12" s="9">
+      <c r="BH12" s="7">
         <v>7.7700000000000005E-2</v>
       </c>
       <c r="BI12" t="s">
@@ -5081,7 +5086,7 @@
       <c r="BJ12">
         <v>29</v>
       </c>
-      <c r="BK12" s="11">
+      <c r="BK12" s="9">
         <v>0.19</v>
       </c>
       <c r="BL12" t="s">
@@ -5090,7 +5095,7 @@
       <c r="BM12">
         <v>23</v>
       </c>
-      <c r="BN12" s="11">
+      <c r="BN12" s="9">
         <v>0.12</v>
       </c>
       <c r="BO12" t="s">
@@ -5099,7 +5104,7 @@
       <c r="BP12">
         <v>26</v>
       </c>
-      <c r="BQ12" s="9">
+      <c r="BQ12" s="7">
         <v>2.5999999999999999E-3</v>
       </c>
       <c r="BR12" t="s">
@@ -5108,7 +5113,7 @@
       <c r="BS12">
         <v>2</v>
       </c>
-      <c r="BT12" s="9">
+      <c r="BT12" s="7">
         <v>4.5499999999999999E-2</v>
       </c>
       <c r="BU12" t="s">
@@ -5138,7 +5143,7 @@
       <c r="CC12" t="s">
         <v>119</v>
       </c>
-      <c r="CD12" s="9">
+      <c r="CD12" s="7">
         <v>0.26069999999999999</v>
       </c>
       <c r="CE12">
@@ -5147,7 +5152,7 @@
       <c r="CF12" t="s">
         <v>156</v>
       </c>
-      <c r="CG12" s="9">
+      <c r="CG12" s="7">
         <v>9.7000000000000003E-3</v>
       </c>
       <c r="CH12" t="s">
@@ -5165,75 +5170,75 @@
       <c r="CL12" t="s">
         <v>208</v>
       </c>
-      <c r="CM12" s="9">
+      <c r="CM12" s="7">
         <v>0.99960000000000004</v>
       </c>
-      <c r="CN12" s="9">
+      <c r="CN12" s="7">
         <v>0.72850000000000004</v>
       </c>
-      <c r="CO12" s="10">
+      <c r="CO12" s="8">
         <v>3717</v>
       </c>
-      <c r="CP12" s="9">
+      <c r="CP12" s="7">
         <v>0.99399999999999999</v>
       </c>
-      <c r="CQ12" s="9">
+      <c r="CQ12" s="7">
         <v>0.99399999999999999</v>
       </c>
-      <c r="CR12" s="9">
-        <v>0</v>
-      </c>
-      <c r="CS12" s="9">
-        <v>0</v>
-      </c>
-      <c r="CT12" s="9">
-        <v>0</v>
-      </c>
-      <c r="CU12" s="9">
-        <v>0</v>
-      </c>
-      <c r="CV12" s="9">
-        <v>0</v>
-      </c>
-      <c r="CW12" s="9">
-        <v>0</v>
-      </c>
-      <c r="CX12" s="9">
+      <c r="CR12" s="7">
+        <v>0</v>
+      </c>
+      <c r="CS12" s="7">
+        <v>0</v>
+      </c>
+      <c r="CT12" s="7">
+        <v>0</v>
+      </c>
+      <c r="CU12" s="7">
+        <v>0</v>
+      </c>
+      <c r="CV12" s="7">
+        <v>0</v>
+      </c>
+      <c r="CW12" s="7">
+        <v>0</v>
+      </c>
+      <c r="CX12" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:102" x14ac:dyDescent="0.2">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="29" t="s">
         <v>93</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="30" t="s">
         <v>94</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="31">
         <v>316</v>
       </c>
-      <c r="D13" t="s">
-        <v>50</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="D13" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="E13" s="31" t="s">
         <v>95</v>
       </c>
-      <c r="F13" t="s">
+      <c r="F13" s="31" t="s">
         <v>96</v>
       </c>
-      <c r="G13" s="7">
+      <c r="G13" s="32">
         <v>43998</v>
       </c>
-      <c r="H13" s="8">
+      <c r="H13" s="33">
         <v>0.1</v>
       </c>
-      <c r="I13" s="8">
+      <c r="I13" s="33">
         <v>0.1</v>
       </c>
-      <c r="J13" s="8">
+      <c r="J13" s="33">
         <v>1263627631.6199999</v>
       </c>
-      <c r="K13" s="7">
+      <c r="K13" s="5">
         <v>45873</v>
       </c>
       <c r="L13" t="s">
@@ -5254,121 +5259,121 @@
       <c r="Q13" t="s">
         <v>49</v>
       </c>
-      <c r="R13" s="8">
+      <c r="R13" s="6">
         <v>0.98970092927779296</v>
       </c>
-      <c r="S13" s="7">
-        <v>45838</v>
-      </c>
-      <c r="T13" s="8">
+      <c r="S13" s="5">
+        <v>45838</v>
+      </c>
+      <c r="T13" s="6">
         <v>12.596989622678947</v>
       </c>
-      <c r="U13" s="7">
+      <c r="U13" s="5">
         <v>45873</v>
       </c>
-      <c r="V13" s="8">
+      <c r="V13" s="6">
         <v>9.1845770000000009</v>
       </c>
-      <c r="W13" s="8">
+      <c r="W13" s="6">
         <v>17.136776000000001</v>
       </c>
-      <c r="X13" s="8">
+      <c r="X13" s="6">
         <v>23.443023</v>
       </c>
-      <c r="Y13" s="8">
+      <c r="Y13" s="6">
         <v>17.478954000000002</v>
       </c>
       <c r="Z13" t="s">
         <v>50</v>
       </c>
-      <c r="AA13" s="8">
+      <c r="AA13" s="6">
         <v>17.443556999999998</v>
       </c>
-      <c r="AB13" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AC13" s="8">
+      <c r="AB13" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AC13" s="6">
         <v>8.9736550000000008</v>
       </c>
-      <c r="AD13" s="8">
+      <c r="AD13" s="6">
         <v>17.024325000000001</v>
       </c>
-      <c r="AE13" s="8">
+      <c r="AE13" s="6">
         <v>23.280222999999999</v>
       </c>
-      <c r="AF13" s="8">
+      <c r="AF13" s="6">
         <v>17.484711000000001</v>
       </c>
       <c r="AG13" t="s">
         <v>50</v>
       </c>
-      <c r="AH13" s="8">
+      <c r="AH13" s="6">
         <v>17.422028999999998</v>
       </c>
-      <c r="AI13" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AJ13" s="8">
+      <c r="AI13" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AJ13" s="6">
         <v>12.093840999999999</v>
       </c>
-      <c r="AK13" s="8">
+      <c r="AK13" s="6">
         <v>18.772189000000001</v>
       </c>
-      <c r="AL13" s="8">
+      <c r="AL13" s="6">
         <v>20.815376000000001</v>
       </c>
-      <c r="AM13" s="8">
+      <c r="AM13" s="6">
         <v>16.845655000000001</v>
       </c>
       <c r="AN13" t="s">
         <v>50</v>
       </c>
-      <c r="AO13" s="8">
+      <c r="AO13" s="6">
         <v>17.733526999999999</v>
       </c>
-      <c r="AP13" s="7">
+      <c r="AP13" s="5">
         <v>45869</v>
       </c>
-      <c r="AQ13" s="8">
+      <c r="AQ13" s="6">
         <v>8.9736550000000008</v>
       </c>
-      <c r="AR13" s="8">
+      <c r="AR13" s="6">
         <v>17.024325000000001</v>
       </c>
-      <c r="AS13" s="8">
+      <c r="AS13" s="6">
         <v>23.280222999999999</v>
       </c>
-      <c r="AT13" s="8">
+      <c r="AT13" s="6">
         <v>17.484711000000001</v>
       </c>
       <c r="AU13" t="s">
         <v>50</v>
       </c>
-      <c r="AV13" s="8">
+      <c r="AV13" s="6">
         <v>17.422028999999998</v>
       </c>
-      <c r="AW13" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AX13" s="8">
+      <c r="AW13" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AX13" s="6">
         <v>0.98970092927779296</v>
       </c>
-      <c r="AY13" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AZ13" s="8">
+      <c r="AY13" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AZ13" s="6">
         <v>0.9133</v>
       </c>
-      <c r="BA13" s="8">
+      <c r="BA13" s="6">
         <v>0.9133</v>
       </c>
-      <c r="BB13" s="7">
+      <c r="BB13" s="5">
         <v>45838</v>
       </c>
       <c r="BC13" t="s">
         <v>50</v>
       </c>
-      <c r="BD13" s="8">
+      <c r="BD13" s="6">
         <v>1.34E-3</v>
       </c>
       <c r="BE13" t="s">
@@ -5380,7 +5385,7 @@
       <c r="BG13" t="s">
         <v>236</v>
       </c>
-      <c r="BH13" s="9">
+      <c r="BH13" s="7">
         <v>9.1000000000000004E-3</v>
       </c>
       <c r="BI13" t="s">
@@ -5389,7 +5394,7 @@
       <c r="BJ13">
         <v>3</v>
       </c>
-      <c r="BK13" s="9">
+      <c r="BK13" s="7">
         <v>2.5100000000000001E-2</v>
       </c>
       <c r="BL13" t="s">
@@ -5398,7 +5403,7 @@
       <c r="BM13">
         <v>11</v>
       </c>
-      <c r="BN13" s="9">
+      <c r="BN13" s="7">
         <v>4.4900000000000002E-2</v>
       </c>
       <c r="BO13" t="s">
@@ -5407,7 +5412,7 @@
       <c r="BP13">
         <v>19</v>
       </c>
-      <c r="BQ13" s="9">
+      <c r="BQ13" s="7">
         <v>5.7999999999999996E-3</v>
       </c>
       <c r="BR13" t="s">
@@ -5416,7 +5421,7 @@
       <c r="BS13">
         <v>1</v>
       </c>
-      <c r="BT13" s="9">
+      <c r="BT13" s="7">
         <v>2.8899999999999999E-2</v>
       </c>
       <c r="BU13" t="s">
@@ -5446,7 +5451,7 @@
       <c r="CC13" t="s">
         <v>119</v>
       </c>
-      <c r="CD13" s="9">
+      <c r="CD13" s="7">
         <v>0.1124</v>
       </c>
       <c r="CE13">
@@ -5455,7 +5460,7 @@
       <c r="CF13" t="s">
         <v>157</v>
       </c>
-      <c r="CG13" s="11">
+      <c r="CG13" s="9">
         <v>0</v>
       </c>
       <c r="CH13" t="s">
@@ -5473,75 +5478,75 @@
       <c r="CL13" t="s">
         <v>208</v>
       </c>
-      <c r="CM13" s="9">
+      <c r="CM13" s="7">
         <v>0.99960000000000004</v>
       </c>
-      <c r="CN13" s="9">
+      <c r="CN13" s="7">
         <v>0.98060000000000003</v>
       </c>
-      <c r="CO13" s="10">
+      <c r="CO13" s="8">
         <v>3717</v>
       </c>
-      <c r="CP13" s="9">
+      <c r="CP13" s="7">
         <v>0.99729999999999996</v>
       </c>
-      <c r="CQ13" s="9">
+      <c r="CQ13" s="7">
         <v>0.99729999999999996</v>
       </c>
-      <c r="CR13" s="9">
-        <v>0</v>
-      </c>
-      <c r="CS13" s="9">
-        <v>0</v>
-      </c>
-      <c r="CT13" s="9">
-        <v>0</v>
-      </c>
-      <c r="CU13" s="9">
-        <v>0</v>
-      </c>
-      <c r="CV13" s="9">
-        <v>0</v>
-      </c>
-      <c r="CW13" s="9">
-        <v>0</v>
-      </c>
-      <c r="CX13" s="9">
+      <c r="CR13" s="7">
+        <v>0</v>
+      </c>
+      <c r="CS13" s="7">
+        <v>0</v>
+      </c>
+      <c r="CT13" s="7">
+        <v>0</v>
+      </c>
+      <c r="CU13" s="7">
+        <v>0</v>
+      </c>
+      <c r="CV13" s="7">
+        <v>0</v>
+      </c>
+      <c r="CW13" s="7">
+        <v>0</v>
+      </c>
+      <c r="CX13" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:102" x14ac:dyDescent="0.2">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="29" t="s">
         <v>98</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="30" t="s">
         <v>99</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="31">
         <v>1019</v>
       </c>
-      <c r="D14" t="s">
-        <v>50</v>
-      </c>
-      <c r="E14" t="s">
+      <c r="D14" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="E14" s="31" t="s">
         <v>100</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F14" s="31" t="s">
         <v>101</v>
       </c>
-      <c r="G14" s="7">
+      <c r="G14" s="32">
         <v>41981</v>
       </c>
-      <c r="H14" s="8">
+      <c r="H14" s="33">
         <v>0.2</v>
       </c>
-      <c r="I14" s="8">
+      <c r="I14" s="33">
         <v>0.2</v>
       </c>
-      <c r="J14" s="8">
+      <c r="J14" s="33">
         <v>1027534118.21</v>
       </c>
-      <c r="K14" s="7">
+      <c r="K14" s="5">
         <v>45873</v>
       </c>
       <c r="L14" t="s">
@@ -5562,121 +5567,121 @@
       <c r="Q14" t="s">
         <v>49</v>
       </c>
-      <c r="R14" s="8">
+      <c r="R14" s="6">
         <v>1.8752</v>
       </c>
-      <c r="S14" s="7">
-        <v>45838</v>
-      </c>
-      <c r="T14" s="8">
+      <c r="S14" s="5">
+        <v>45838</v>
+      </c>
+      <c r="T14" s="6">
         <v>11.476399531700118</v>
       </c>
-      <c r="U14" s="7">
+      <c r="U14" s="5">
         <v>45873</v>
       </c>
-      <c r="V14" s="8">
+      <c r="V14" s="6">
         <v>10.220000000000001</v>
       </c>
-      <c r="W14" s="8">
+      <c r="W14" s="6">
         <v>17.73</v>
       </c>
-      <c r="X14" s="8">
+      <c r="X14" s="6">
         <v>17.91</v>
       </c>
-      <c r="Y14" s="8">
+      <c r="Y14" s="6">
         <v>13.93</v>
       </c>
-      <c r="Z14" s="8">
+      <c r="Z14" s="6">
         <v>10.29</v>
       </c>
-      <c r="AA14" s="8">
+      <c r="AA14" s="6">
         <v>9.9499999999999993</v>
       </c>
-      <c r="AB14" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AC14" s="8">
+      <c r="AB14" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AC14" s="6">
         <v>10.32</v>
       </c>
-      <c r="AD14" s="8">
+      <c r="AD14" s="6">
         <v>17.87</v>
       </c>
-      <c r="AE14" s="8">
+      <c r="AE14" s="6">
         <v>17.920000000000002</v>
       </c>
-      <c r="AF14" s="8">
+      <c r="AF14" s="6">
         <v>13.95</v>
       </c>
-      <c r="AG14" s="8">
+      <c r="AG14" s="6">
         <v>10.26</v>
       </c>
-      <c r="AH14" s="8">
+      <c r="AH14" s="6">
         <v>9.9499999999999993</v>
       </c>
-      <c r="AI14" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AJ14" s="8">
+      <c r="AI14" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AJ14" s="6">
         <v>11.18</v>
       </c>
-      <c r="AK14" s="8">
+      <c r="AK14" s="6">
         <v>16.46</v>
       </c>
-      <c r="AL14" s="8">
+      <c r="AL14" s="6">
         <v>15.6</v>
       </c>
-      <c r="AM14" s="8">
+      <c r="AM14" s="6">
         <v>12.97</v>
       </c>
-      <c r="AN14" s="8">
+      <c r="AN14" s="6">
         <v>10.25</v>
       </c>
-      <c r="AO14" s="8">
+      <c r="AO14" s="6">
         <v>9.9499999999999993</v>
       </c>
-      <c r="AP14" s="7">
+      <c r="AP14" s="5">
         <v>45869</v>
       </c>
-      <c r="AQ14" s="8">
+      <c r="AQ14" s="6">
         <v>10.32</v>
       </c>
-      <c r="AR14" s="8">
+      <c r="AR14" s="6">
         <v>17.87</v>
       </c>
-      <c r="AS14" s="8">
+      <c r="AS14" s="6">
         <v>17.920000000000002</v>
       </c>
-      <c r="AT14" s="8">
+      <c r="AT14" s="6">
         <v>13.95</v>
       </c>
-      <c r="AU14" s="8">
+      <c r="AU14" s="6">
         <v>10.26</v>
       </c>
-      <c r="AV14" s="8">
+      <c r="AV14" s="6">
         <v>9.9499999999999993</v>
       </c>
-      <c r="AW14" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AX14" s="8">
+      <c r="AW14" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AX14" s="6">
         <v>1.8752</v>
       </c>
-      <c r="AY14" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AZ14" s="8">
+      <c r="AY14" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AZ14" s="6">
         <v>1.4822</v>
       </c>
-      <c r="BA14" s="8">
+      <c r="BA14" s="6">
         <v>1.4822</v>
       </c>
-      <c r="BB14" s="7">
+      <c r="BB14" s="5">
         <v>45838</v>
       </c>
       <c r="BC14" t="s">
         <v>50</v>
       </c>
-      <c r="BD14" s="8">
+      <c r="BD14" s="6">
         <v>2.2399999999999998E-3</v>
       </c>
       <c r="BE14" t="s">
@@ -5688,7 +5693,7 @@
       <c r="BG14" t="s">
         <v>237</v>
       </c>
-      <c r="BH14" s="9">
+      <c r="BH14" s="7">
         <v>4.19E-2</v>
       </c>
       <c r="BI14" t="s">
@@ -5697,7 +5702,7 @@
       <c r="BJ14">
         <v>39</v>
       </c>
-      <c r="BK14" s="11">
+      <c r="BK14" s="9">
         <v>0.23</v>
       </c>
       <c r="BL14" t="s">
@@ -5706,7 +5711,7 @@
       <c r="BM14">
         <v>20</v>
       </c>
-      <c r="BN14" s="11">
+      <c r="BN14" s="9">
         <v>0.12</v>
       </c>
       <c r="BO14" t="s">
@@ -5715,7 +5720,7 @@
       <c r="BP14">
         <v>55</v>
       </c>
-      <c r="BQ14" s="9">
+      <c r="BQ14" s="7">
         <v>2.3400000000000001E-2</v>
       </c>
       <c r="BR14" t="s">
@@ -5724,7 +5729,7 @@
       <c r="BS14">
         <v>13</v>
       </c>
-      <c r="BT14" s="9">
+      <c r="BT14" s="7">
         <v>2.18E-2</v>
       </c>
       <c r="BU14" t="s">
@@ -5754,7 +5759,7 @@
       <c r="CC14" t="s">
         <v>130</v>
       </c>
-      <c r="CD14" s="9">
+      <c r="CD14" s="7">
         <v>0.2087</v>
       </c>
       <c r="CE14">
@@ -5763,7 +5768,7 @@
       <c r="CF14" t="s">
         <v>158</v>
       </c>
-      <c r="CG14" s="11">
+      <c r="CG14" s="9">
         <v>0</v>
       </c>
       <c r="CH14" t="s">
@@ -5781,75 +5786,75 @@
       <c r="CL14" t="s">
         <v>202</v>
       </c>
-      <c r="CM14" s="9">
+      <c r="CM14" s="7">
         <v>1</v>
       </c>
-      <c r="CN14" s="9">
+      <c r="CN14" s="7">
         <v>0.34279999999999999</v>
       </c>
-      <c r="CO14" s="10">
+      <c r="CO14" s="8">
         <v>5449</v>
       </c>
-      <c r="CP14" s="9">
+      <c r="CP14" s="7">
         <v>0.99609999999999999</v>
       </c>
-      <c r="CQ14" s="9">
+      <c r="CQ14" s="7">
         <v>0.99529999999999996</v>
       </c>
-      <c r="CR14" s="9">
-        <v>0</v>
-      </c>
-      <c r="CS14" s="9">
-        <v>0</v>
-      </c>
-      <c r="CT14" s="9">
+      <c r="CR14" s="7">
+        <v>0</v>
+      </c>
+      <c r="CS14" s="7">
+        <v>0</v>
+      </c>
+      <c r="CT14" s="7">
         <v>1.5E-3</v>
       </c>
-      <c r="CU14" s="9">
+      <c r="CU14" s="7">
         <v>1.3899999999999999E-2</v>
       </c>
-      <c r="CV14" s="9">
-        <v>0</v>
-      </c>
-      <c r="CW14" s="9">
-        <v>0</v>
-      </c>
-      <c r="CX14" s="9">
+      <c r="CV14" s="7">
+        <v>0</v>
+      </c>
+      <c r="CW14" s="7">
+        <v>0</v>
+      </c>
+      <c r="CX14" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:102" x14ac:dyDescent="0.2">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="29" t="s">
         <v>102</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="30" t="s">
         <v>103</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="31">
         <v>281</v>
       </c>
-      <c r="D15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E15" t="s">
+      <c r="D15" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="E15" s="31" t="s">
         <v>104</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F15" s="31" t="s">
         <v>105</v>
       </c>
-      <c r="G15" s="7">
+      <c r="G15" s="32">
         <v>43592</v>
       </c>
-      <c r="H15" s="8">
+      <c r="H15" s="33">
         <v>0.1</v>
       </c>
-      <c r="I15" s="8">
+      <c r="I15" s="33">
         <v>0.1</v>
       </c>
-      <c r="J15" s="8">
+      <c r="J15" s="33">
         <v>969050560.38</v>
       </c>
-      <c r="K15" s="7">
+      <c r="K15" s="5">
         <v>45873</v>
       </c>
       <c r="L15" t="s">
@@ -5870,121 +5875,121 @@
       <c r="Q15" t="s">
         <v>49</v>
       </c>
-      <c r="R15" s="8">
+      <c r="R15" s="6">
         <v>1.0895163639615051</v>
       </c>
-      <c r="S15" s="7">
-        <v>45838</v>
-      </c>
-      <c r="T15" s="8">
+      <c r="S15" s="5">
+        <v>45838</v>
+      </c>
+      <c r="T15" s="6">
         <v>9.485261272130904</v>
       </c>
-      <c r="U15" s="7">
+      <c r="U15" s="5">
         <v>45873</v>
       </c>
-      <c r="V15" s="8">
+      <c r="V15" s="6">
         <v>5.8909840000000004</v>
       </c>
-      <c r="W15" s="8">
+      <c r="W15" s="6">
         <v>12.642306</v>
       </c>
-      <c r="X15" s="8">
+      <c r="X15" s="6">
         <v>19.377939000000001</v>
       </c>
-      <c r="Y15" s="8">
+      <c r="Y15" s="6">
         <v>16.453164000000001</v>
       </c>
       <c r="Z15" t="s">
         <v>50</v>
       </c>
-      <c r="AA15" s="8">
+      <c r="AA15" s="6">
         <v>15.305603</v>
       </c>
-      <c r="AB15" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AC15" s="8">
+      <c r="AB15" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AC15" s="6">
         <v>5.7084270000000004</v>
       </c>
-      <c r="AD15" s="8">
+      <c r="AD15" s="6">
         <v>12.496555000000001</v>
       </c>
-      <c r="AE15" s="8">
+      <c r="AE15" s="6">
         <v>19.301407999999999</v>
       </c>
-      <c r="AF15" s="8">
+      <c r="AF15" s="6">
         <v>16.461176999999999</v>
       </c>
       <c r="AG15" t="s">
         <v>50</v>
       </c>
-      <c r="AH15" s="8">
+      <c r="AH15" s="6">
         <v>15.304917</v>
       </c>
-      <c r="AI15" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AJ15" s="8">
+      <c r="AI15" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AJ15" s="6">
         <v>8.7716940000000001</v>
       </c>
-      <c r="AK15" s="8">
+      <c r="AK15" s="6">
         <v>15.318251999999999</v>
       </c>
-      <c r="AL15" s="8">
+      <c r="AL15" s="6">
         <v>17.304393999999998</v>
       </c>
-      <c r="AM15" s="8">
+      <c r="AM15" s="6">
         <v>16.13748</v>
       </c>
       <c r="AN15" t="s">
         <v>50</v>
       </c>
-      <c r="AO15" s="8">
+      <c r="AO15" s="6">
         <v>15.57859</v>
       </c>
-      <c r="AP15" s="7">
+      <c r="AP15" s="5">
         <v>45869</v>
       </c>
-      <c r="AQ15" s="8">
+      <c r="AQ15" s="6">
         <v>5.7084270000000004</v>
       </c>
-      <c r="AR15" s="8">
+      <c r="AR15" s="6">
         <v>12.496555000000001</v>
       </c>
-      <c r="AS15" s="8">
+      <c r="AS15" s="6">
         <v>19.301407999999999</v>
       </c>
-      <c r="AT15" s="8">
+      <c r="AT15" s="6">
         <v>16.461176999999999</v>
       </c>
       <c r="AU15" t="s">
         <v>50</v>
       </c>
-      <c r="AV15" s="8">
+      <c r="AV15" s="6">
         <v>15.304917</v>
       </c>
-      <c r="AW15" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AX15" s="8">
+      <c r="AW15" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AX15" s="6">
         <v>1.0895163639615051</v>
       </c>
-      <c r="AY15" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AZ15" s="8">
+      <c r="AY15" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AZ15" s="6">
         <v>1.0663</v>
       </c>
-      <c r="BA15" s="8">
+      <c r="BA15" s="6">
         <v>1.0663</v>
       </c>
-      <c r="BB15" s="7">
+      <c r="BB15" s="5">
         <v>45838</v>
       </c>
       <c r="BC15" t="s">
         <v>50</v>
       </c>
-      <c r="BD15" s="8">
+      <c r="BD15" s="6">
         <v>1.2199999999999999E-3</v>
       </c>
       <c r="BE15" t="s">
@@ -5996,7 +6001,7 @@
       <c r="BG15" t="s">
         <v>238</v>
       </c>
-      <c r="BH15" s="9">
+      <c r="BH15" s="7">
         <v>2.8000000000000001E-2</v>
       </c>
       <c r="BI15" t="s">
@@ -6005,7 +6010,7 @@
       <c r="BJ15">
         <v>20</v>
       </c>
-      <c r="BK15" s="11">
+      <c r="BK15" s="9">
         <v>0.24</v>
       </c>
       <c r="BL15" t="s">
@@ -6014,7 +6019,7 @@
       <c r="BM15">
         <v>15</v>
       </c>
-      <c r="BN15" s="9">
+      <c r="BN15" s="7">
         <v>8.7099999999999997E-2</v>
       </c>
       <c r="BO15" t="s">
@@ -6023,7 +6028,7 @@
       <c r="BP15">
         <v>28</v>
       </c>
-      <c r="BQ15" s="9">
+      <c r="BQ15" s="7">
         <v>1.17E-2</v>
       </c>
       <c r="BR15" t="s">
@@ -6032,7 +6037,7 @@
       <c r="BS15">
         <v>2</v>
       </c>
-      <c r="BT15" s="9">
+      <c r="BT15" s="7">
         <v>2.6100000000000002E-2</v>
       </c>
       <c r="BU15" t="s">
@@ -6062,7 +6067,7 @@
       <c r="CC15" t="s">
         <v>119</v>
       </c>
-      <c r="CD15" s="9">
+      <c r="CD15" s="7">
         <v>0.27950000000000003</v>
       </c>
       <c r="CE15">
@@ -6071,7 +6076,7 @@
       <c r="CF15" t="s">
         <v>159</v>
       </c>
-      <c r="CG15" s="11">
+      <c r="CG15" s="9">
         <v>0</v>
       </c>
       <c r="CH15" t="s">
@@ -6089,75 +6094,75 @@
       <c r="CL15" t="s">
         <v>208</v>
       </c>
-      <c r="CM15" s="9">
+      <c r="CM15" s="7">
         <v>0.99950000000000006</v>
       </c>
-      <c r="CN15" s="9">
+      <c r="CN15" s="7">
         <v>0.96340000000000003</v>
       </c>
-      <c r="CO15" s="10">
+      <c r="CO15" s="8">
         <v>3717</v>
       </c>
-      <c r="CP15" s="9">
+      <c r="CP15" s="7">
         <v>0.99690000000000001</v>
       </c>
-      <c r="CQ15" s="9">
+      <c r="CQ15" s="7">
         <v>0.99690000000000001</v>
       </c>
-      <c r="CR15" s="9">
-        <v>0</v>
-      </c>
-      <c r="CS15" s="9">
-        <v>0</v>
-      </c>
-      <c r="CT15" s="9">
-        <v>0</v>
-      </c>
-      <c r="CU15" s="9">
-        <v>0</v>
-      </c>
-      <c r="CV15" s="9">
-        <v>0</v>
-      </c>
-      <c r="CW15" s="9">
-        <v>0</v>
-      </c>
-      <c r="CX15" s="9">
+      <c r="CR15" s="7">
+        <v>0</v>
+      </c>
+      <c r="CS15" s="7">
+        <v>0</v>
+      </c>
+      <c r="CT15" s="7">
+        <v>0</v>
+      </c>
+      <c r="CU15" s="7">
+        <v>0</v>
+      </c>
+      <c r="CV15" s="7">
+        <v>0</v>
+      </c>
+      <c r="CW15" s="7">
+        <v>0</v>
+      </c>
+      <c r="CX15" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:102" x14ac:dyDescent="0.2">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="29" t="s">
         <v>106</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="31">
         <v>442</v>
       </c>
-      <c r="D16" t="s">
-        <v>50</v>
-      </c>
-      <c r="E16" t="s">
+      <c r="D16" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="E16" s="31" t="s">
         <v>108</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F16" s="31" t="s">
         <v>109</v>
       </c>
-      <c r="G16" s="7">
+      <c r="G16" s="32">
         <v>43998</v>
       </c>
-      <c r="H16" s="8">
+      <c r="H16" s="33">
         <v>0.12</v>
       </c>
-      <c r="I16" s="8">
+      <c r="I16" s="33">
         <v>0.12</v>
       </c>
-      <c r="J16" s="8">
+      <c r="J16" s="33">
         <v>804362959.90999997</v>
       </c>
-      <c r="K16" s="7">
+      <c r="K16" s="5">
         <v>45873</v>
       </c>
       <c r="L16" t="s">
@@ -6178,121 +6183,121 @@
       <c r="Q16" t="s">
         <v>49</v>
       </c>
-      <c r="R16" s="8">
+      <c r="R16" s="6">
         <v>2.7185000000000001</v>
       </c>
-      <c r="S16" s="7">
-        <v>45838</v>
-      </c>
-      <c r="T16" s="8">
+      <c r="S16" s="5">
+        <v>45838</v>
+      </c>
+      <c r="T16" s="6">
         <v>14.355846760592872</v>
       </c>
-      <c r="U16" s="7">
+      <c r="U16" s="5">
         <v>45873</v>
       </c>
-      <c r="V16" s="8">
+      <c r="V16" s="6">
         <v>17.54</v>
       </c>
-      <c r="W16" s="8">
+      <c r="W16" s="6">
         <v>14.03</v>
       </c>
-      <c r="X16" s="8">
+      <c r="X16" s="6">
         <v>15.68</v>
       </c>
-      <c r="Y16" s="8">
+      <c r="Y16" s="6">
         <v>10.3</v>
       </c>
       <c r="Z16" t="s">
         <v>50</v>
       </c>
-      <c r="AA16" s="8">
+      <c r="AA16" s="6">
         <v>10.09</v>
       </c>
-      <c r="AB16" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AC16" s="8">
+      <c r="AB16" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AC16" s="6">
         <v>16.989999999999998</v>
       </c>
-      <c r="AD16" s="8">
+      <c r="AD16" s="6">
         <v>13.61</v>
       </c>
-      <c r="AE16" s="8">
+      <c r="AE16" s="6">
         <v>15.36</v>
       </c>
-      <c r="AF16" s="8">
+      <c r="AF16" s="6">
         <v>10.17</v>
       </c>
       <c r="AG16" t="s">
         <v>50</v>
       </c>
-      <c r="AH16" s="8">
+      <c r="AH16" s="6">
         <v>10.07</v>
       </c>
-      <c r="AI16" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AJ16" s="8">
+      <c r="AI16" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AJ16" s="6">
         <v>12.75</v>
       </c>
-      <c r="AK16" s="8">
+      <c r="AK16" s="6">
         <v>6.3</v>
       </c>
-      <c r="AL16" s="8">
+      <c r="AL16" s="6">
         <v>11.75</v>
       </c>
-      <c r="AM16" s="8">
+      <c r="AM16" s="6">
         <v>8.7899999999999991</v>
       </c>
       <c r="AN16" t="s">
         <v>50</v>
       </c>
-      <c r="AO16" s="8">
+      <c r="AO16" s="6">
         <v>9.0299999999999994</v>
       </c>
-      <c r="AP16" s="7">
+      <c r="AP16" s="5">
         <v>45869</v>
       </c>
-      <c r="AQ16" s="8">
+      <c r="AQ16" s="6">
         <v>16.989999999999998</v>
       </c>
-      <c r="AR16" s="8">
+      <c r="AR16" s="6">
         <v>13.61</v>
       </c>
-      <c r="AS16" s="8">
+      <c r="AS16" s="6">
         <v>15.36</v>
       </c>
-      <c r="AT16" s="8">
+      <c r="AT16" s="6">
         <v>10.17</v>
       </c>
       <c r="AU16" t="s">
         <v>50</v>
       </c>
-      <c r="AV16" s="8">
+      <c r="AV16" s="6">
         <v>10.07</v>
       </c>
-      <c r="AW16" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AX16" s="8">
+      <c r="AW16" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AX16" s="6">
         <v>2.7185000000000001</v>
       </c>
-      <c r="AY16" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AZ16" s="8">
+      <c r="AY16" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AZ16" s="6">
         <v>2.0480999999999998</v>
       </c>
-      <c r="BA16" s="8">
+      <c r="BA16" s="6">
         <v>2.0480999999999998</v>
       </c>
-      <c r="BB16" s="7">
+      <c r="BB16" s="5">
         <v>45838</v>
       </c>
       <c r="BC16" t="s">
         <v>50</v>
       </c>
-      <c r="BD16" s="8">
+      <c r="BD16" s="6">
         <v>1.8000000000000001E-4</v>
       </c>
       <c r="BE16" t="s">
@@ -6304,7 +6309,7 @@
       <c r="BG16" t="s">
         <v>239</v>
       </c>
-      <c r="BH16" s="9">
+      <c r="BH16" s="7">
         <v>5.3E-3</v>
       </c>
       <c r="BI16" t="s">
@@ -6313,7 +6318,7 @@
       <c r="BJ16">
         <v>2</v>
       </c>
-      <c r="BK16" s="9">
+      <c r="BK16" s="7">
         <v>2.0899999999999998E-2</v>
       </c>
       <c r="BL16" t="s">
@@ -6322,7 +6327,7 @@
       <c r="BM16">
         <v>7</v>
       </c>
-      <c r="BN16" s="9">
+      <c r="BN16" s="7">
         <v>9.2100000000000001E-2</v>
       </c>
       <c r="BO16" t="s">
@@ -6331,7 +6336,7 @@
       <c r="BP16">
         <v>36</v>
       </c>
-      <c r="BQ16" s="11">
+      <c r="BQ16" s="9">
         <v>0</v>
       </c>
       <c r="BR16" t="s">
@@ -6340,7 +6345,7 @@
       <c r="BS16">
         <v>0</v>
       </c>
-      <c r="BT16" s="9">
+      <c r="BT16" s="7">
         <v>4.3E-3</v>
       </c>
       <c r="BU16" t="s">
@@ -6370,7 +6375,7 @@
       <c r="CC16" t="s">
         <v>120</v>
       </c>
-      <c r="CD16" s="9">
+      <c r="CD16" s="7">
         <v>0.1396</v>
       </c>
       <c r="CE16">
@@ -6379,7 +6384,7 @@
       <c r="CF16" t="s">
         <v>160</v>
       </c>
-      <c r="CG16" s="11">
+      <c r="CG16" s="9">
         <v>0</v>
       </c>
       <c r="CH16" t="s">
@@ -6397,75 +6402,75 @@
       <c r="CL16" t="s">
         <v>202</v>
       </c>
-      <c r="CM16" s="9">
+      <c r="CM16" s="7">
         <v>1</v>
       </c>
-      <c r="CN16" s="9">
+      <c r="CN16" s="7">
         <v>0.98119999999999996</v>
       </c>
       <c r="CO16">
         <v>853</v>
       </c>
-      <c r="CP16" s="9">
+      <c r="CP16" s="7">
         <v>0.99360000000000004</v>
       </c>
-      <c r="CQ16" s="9">
+      <c r="CQ16" s="7">
         <v>0.99309999999999998</v>
       </c>
-      <c r="CR16" s="9">
-        <v>0</v>
-      </c>
-      <c r="CS16" s="9">
-        <v>0</v>
-      </c>
-      <c r="CT16" s="9">
-        <v>0</v>
-      </c>
-      <c r="CU16" s="9">
-        <v>0</v>
-      </c>
-      <c r="CV16" s="9">
-        <v>0</v>
-      </c>
-      <c r="CW16" s="9">
-        <v>0</v>
-      </c>
-      <c r="CX16" s="9">
+      <c r="CR16" s="7">
+        <v>0</v>
+      </c>
+      <c r="CS16" s="7">
+        <v>0</v>
+      </c>
+      <c r="CT16" s="7">
+        <v>0</v>
+      </c>
+      <c r="CU16" s="7">
+        <v>0</v>
+      </c>
+      <c r="CV16" s="7">
+        <v>0</v>
+      </c>
+      <c r="CW16" s="7">
+        <v>0</v>
+      </c>
+      <c r="CX16" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:102" x14ac:dyDescent="0.2">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="29" t="s">
         <v>110</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="30" t="s">
         <v>111</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="31">
         <v>449</v>
       </c>
-      <c r="D17" t="s">
-        <v>50</v>
-      </c>
-      <c r="E17" t="s">
+      <c r="D17" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="E17" s="31" t="s">
         <v>112</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F17" s="31" t="s">
         <v>113</v>
       </c>
-      <c r="G17" s="7">
+      <c r="G17" s="32">
         <v>44096</v>
       </c>
-      <c r="H17" s="8">
+      <c r="H17" s="33">
         <v>0.08</v>
       </c>
-      <c r="I17" s="8">
+      <c r="I17" s="33">
         <v>0.08</v>
       </c>
-      <c r="J17" s="8">
+      <c r="J17" s="33">
         <v>430814329.23000002</v>
       </c>
-      <c r="K17" s="7">
+      <c r="K17" s="5">
         <v>45873</v>
       </c>
       <c r="L17" t="s">
@@ -6486,25 +6491,25 @@
       <c r="Q17" t="s">
         <v>49</v>
       </c>
-      <c r="R17" s="8">
+      <c r="R17" s="6">
         <v>1.04</v>
       </c>
-      <c r="S17" s="7">
-        <v>45838</v>
-      </c>
-      <c r="T17" s="8">
+      <c r="S17" s="5">
+        <v>45838</v>
+      </c>
+      <c r="T17" s="6">
         <v>7.9577133662577388</v>
       </c>
-      <c r="U17" s="7">
+      <c r="U17" s="5">
         <v>45873</v>
       </c>
-      <c r="V17" s="8">
+      <c r="V17" s="6">
         <v>5.7039999999999997</v>
       </c>
-      <c r="W17" s="8">
+      <c r="W17" s="6">
         <v>14.691000000000001</v>
       </c>
-      <c r="X17" s="8">
+      <c r="X17" s="6">
         <v>20.377300000000002</v>
       </c>
       <c r="Y17" t="s">
@@ -6513,19 +6518,19 @@
       <c r="Z17" t="s">
         <v>50</v>
       </c>
-      <c r="AA17" s="8">
+      <c r="AA17" s="6">
         <v>15.5601</v>
       </c>
-      <c r="AB17" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AC17" s="8">
+      <c r="AB17" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AC17" s="6">
         <v>5.7850000000000001</v>
       </c>
-      <c r="AD17" s="8">
+      <c r="AD17" s="6">
         <v>14.666</v>
       </c>
-      <c r="AE17" s="8">
+      <c r="AE17" s="6">
         <v>20.3874</v>
       </c>
       <c r="AF17" t="s">
@@ -6534,19 +6539,19 @@
       <c r="AG17" t="s">
         <v>50</v>
       </c>
-      <c r="AH17" s="8">
+      <c r="AH17" s="6">
         <v>15.5723</v>
       </c>
-      <c r="AI17" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AJ17" s="8">
+      <c r="AI17" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AJ17" s="6">
         <v>8.1</v>
       </c>
-      <c r="AK17" s="8">
+      <c r="AK17" s="6">
         <v>16.222999999999999</v>
       </c>
-      <c r="AL17" s="8">
+      <c r="AL17" s="6">
         <v>17.639299999999999</v>
       </c>
       <c r="AM17" t="s">
@@ -6555,19 +6560,19 @@
       <c r="AN17" t="s">
         <v>50</v>
       </c>
-      <c r="AO17" s="8">
+      <c r="AO17" s="6">
         <v>15.801399999999999</v>
       </c>
-      <c r="AP17" s="7">
+      <c r="AP17" s="5">
         <v>45869</v>
       </c>
-      <c r="AQ17" s="8">
+      <c r="AQ17" s="6">
         <v>5.7850000000000001</v>
       </c>
-      <c r="AR17" s="8">
+      <c r="AR17" s="6">
         <v>14.666</v>
       </c>
-      <c r="AS17" s="8">
+      <c r="AS17" s="6">
         <v>20.3874</v>
       </c>
       <c r="AT17" t="s">
@@ -6576,31 +6581,31 @@
       <c r="AU17" t="s">
         <v>50</v>
       </c>
-      <c r="AV17" s="8">
+      <c r="AV17" s="6">
         <v>15.5723</v>
       </c>
-      <c r="AW17" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AX17" s="8">
+      <c r="AW17" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AX17" s="6">
         <v>1.04</v>
       </c>
-      <c r="AY17" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AZ17" s="8">
+      <c r="AY17" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AZ17" s="6">
         <v>1.05</v>
       </c>
-      <c r="BA17" s="8">
+      <c r="BA17" s="6">
         <v>1.05</v>
       </c>
-      <c r="BB17" s="7">
+      <c r="BB17" s="5">
         <v>45838</v>
       </c>
       <c r="BC17" t="s">
         <v>50</v>
       </c>
-      <c r="BD17" s="8">
+      <c r="BD17" s="6">
         <v>2.2100000000000002E-3</v>
       </c>
       <c r="BE17" t="s">
@@ -6612,7 +6617,7 @@
       <c r="BG17" t="s">
         <v>240</v>
       </c>
-      <c r="BH17" s="9">
+      <c r="BH17" s="7">
         <v>4.9200000000000001E-2</v>
       </c>
       <c r="BI17" t="s">
@@ -6621,7 +6626,7 @@
       <c r="BJ17">
         <v>28</v>
       </c>
-      <c r="BK17" s="11">
+      <c r="BK17" s="9">
         <v>0.23</v>
       </c>
       <c r="BL17" t="s">
@@ -6630,7 +6635,7 @@
       <c r="BM17">
         <v>26</v>
       </c>
-      <c r="BN17" s="11">
+      <c r="BN17" s="9">
         <v>0.13</v>
       </c>
       <c r="BO17" t="s">
@@ -6639,7 +6644,7 @@
       <c r="BP17">
         <v>45</v>
       </c>
-      <c r="BQ17" s="9">
+      <c r="BQ17" s="7">
         <v>1.0999999999999999E-2</v>
       </c>
       <c r="BR17" t="s">
@@ -6648,7 +6653,7 @@
       <c r="BS17">
         <v>4</v>
       </c>
-      <c r="BT17" s="9">
+      <c r="BT17" s="7">
         <v>1.9300000000000001E-2</v>
       </c>
       <c r="BU17" t="s">
@@ -6678,7 +6683,7 @@
       <c r="CC17" t="s">
         <v>119</v>
       </c>
-      <c r="CD17" s="9">
+      <c r="CD17" s="7">
         <v>0.27929999999999999</v>
       </c>
       <c r="CE17">
@@ -6687,7 +6692,7 @@
       <c r="CF17" t="s">
         <v>161</v>
       </c>
-      <c r="CG17" s="11">
+      <c r="CG17" s="9">
         <v>0</v>
       </c>
       <c r="CH17" t="s">
@@ -6705,75 +6710,75 @@
       <c r="CL17" t="s">
         <v>208</v>
       </c>
-      <c r="CM17" s="9">
+      <c r="CM17" s="7">
         <v>0.99490000000000001</v>
       </c>
-      <c r="CN17" s="9">
+      <c r="CN17" s="7">
         <v>0.46870000000000001</v>
       </c>
-      <c r="CO17" s="10">
+      <c r="CO17" s="8">
         <v>3717</v>
       </c>
-      <c r="CP17" s="9">
+      <c r="CP17" s="7">
         <v>0.99299999999999999</v>
       </c>
-      <c r="CQ17" s="9">
+      <c r="CQ17" s="7">
         <v>0.99299999999999999</v>
       </c>
-      <c r="CR17" s="9">
-        <v>0</v>
-      </c>
-      <c r="CS17" s="9">
-        <v>0</v>
-      </c>
-      <c r="CT17" s="9">
-        <v>0</v>
-      </c>
-      <c r="CU17" s="9">
-        <v>0</v>
-      </c>
-      <c r="CV17" s="9">
-        <v>0</v>
-      </c>
-      <c r="CW17" s="9">
-        <v>0</v>
-      </c>
-      <c r="CX17" s="9">
+      <c r="CR17" s="7">
+        <v>0</v>
+      </c>
+      <c r="CS17" s="7">
+        <v>0</v>
+      </c>
+      <c r="CT17" s="7">
+        <v>0</v>
+      </c>
+      <c r="CU17" s="7">
+        <v>0</v>
+      </c>
+      <c r="CV17" s="7">
+        <v>0</v>
+      </c>
+      <c r="CW17" s="7">
+        <v>0</v>
+      </c>
+      <c r="CX17" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:102" x14ac:dyDescent="0.2">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="30" t="s">
         <v>162</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="30" t="s">
         <v>163</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="31">
         <v>367</v>
       </c>
-      <c r="D18" t="s">
-        <v>50</v>
-      </c>
-      <c r="E18" t="s">
+      <c r="D18" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="E18" s="31" t="s">
         <v>164</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F18" s="31" t="s">
         <v>165</v>
       </c>
-      <c r="G18" s="7">
+      <c r="G18" s="32">
         <v>44096</v>
       </c>
-      <c r="H18" s="8">
+      <c r="H18" s="33">
         <v>0.12</v>
       </c>
-      <c r="I18" s="8">
+      <c r="I18" s="33">
         <v>0.12</v>
       </c>
-      <c r="J18" s="8">
+      <c r="J18" s="33">
         <v>290594113.62</v>
       </c>
-      <c r="K18" s="7">
+      <c r="K18" s="5">
         <v>45873</v>
       </c>
       <c r="L18" t="s">
@@ -6794,25 +6799,25 @@
       <c r="Q18" t="s">
         <v>49</v>
       </c>
-      <c r="R18" s="8">
+      <c r="R18" s="6">
         <v>1.33</v>
       </c>
-      <c r="S18" s="7">
-        <v>45838</v>
-      </c>
-      <c r="T18" s="8">
+      <c r="S18" s="5">
+        <v>45838</v>
+      </c>
+      <c r="T18" s="6">
         <v>1.2894742795488963</v>
       </c>
-      <c r="U18" s="7">
+      <c r="U18" s="5">
         <v>45873</v>
       </c>
-      <c r="V18" s="8">
+      <c r="V18" s="6">
         <v>-0.09</v>
       </c>
-      <c r="W18" s="8">
+      <c r="W18" s="6">
         <v>6.5259999999999998</v>
       </c>
-      <c r="X18" s="8">
+      <c r="X18" s="6">
         <v>12.2591</v>
       </c>
       <c r="Y18" t="s">
@@ -6821,19 +6826,19 @@
       <c r="Z18" t="s">
         <v>50</v>
       </c>
-      <c r="AA18" s="8">
+      <c r="AA18" s="6">
         <v>12.5045</v>
       </c>
-      <c r="AB18" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AC18" s="8">
+      <c r="AB18" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AC18" s="6">
         <v>-0.27100000000000002</v>
       </c>
-      <c r="AD18" s="8">
+      <c r="AD18" s="6">
         <v>6.2789999999999999</v>
       </c>
-      <c r="AE18" s="8">
+      <c r="AE18" s="6">
         <v>12.287599999999999</v>
       </c>
       <c r="AF18" t="s">
@@ -6842,19 +6847,19 @@
       <c r="AG18" t="s">
         <v>50</v>
       </c>
-      <c r="AH18" s="8">
+      <c r="AH18" s="6">
         <v>12.4796</v>
       </c>
-      <c r="AI18" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AJ18" s="8">
+      <c r="AI18" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AJ18" s="6">
         <v>1.413</v>
       </c>
-      <c r="AK18" s="8">
+      <c r="AK18" s="6">
         <v>1.9850000000000001</v>
       </c>
-      <c r="AL18" s="8">
+      <c r="AL18" s="6">
         <v>9.0198999999999998</v>
       </c>
       <c r="AM18" t="s">
@@ -6863,19 +6868,19 @@
       <c r="AN18" t="s">
         <v>50</v>
       </c>
-      <c r="AO18" s="8">
+      <c r="AO18" s="6">
         <v>12.618499999999999</v>
       </c>
-      <c r="AP18" s="7">
+      <c r="AP18" s="5">
         <v>45869</v>
       </c>
-      <c r="AQ18" s="8">
+      <c r="AQ18" s="6">
         <v>-0.27100000000000002</v>
       </c>
-      <c r="AR18" s="8">
+      <c r="AR18" s="6">
         <v>6.2789999999999999</v>
       </c>
-      <c r="AS18" s="8">
+      <c r="AS18" s="6">
         <v>12.287599999999999</v>
       </c>
       <c r="AT18" t="s">
@@ -6884,31 +6889,31 @@
       <c r="AU18" t="s">
         <v>50</v>
       </c>
-      <c r="AV18" s="8">
+      <c r="AV18" s="6">
         <v>12.4796</v>
       </c>
-      <c r="AW18" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AX18" s="8">
+      <c r="AW18" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AX18" s="6">
         <v>1.33</v>
       </c>
-      <c r="AY18" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AZ18" s="8">
+      <c r="AY18" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AZ18" s="6">
         <v>1.38</v>
       </c>
-      <c r="BA18" s="8">
+      <c r="BA18" s="6">
         <v>1.38</v>
       </c>
-      <c r="BB18" s="7">
+      <c r="BB18" s="5">
         <v>45838</v>
       </c>
       <c r="BC18" t="s">
         <v>50</v>
       </c>
-      <c r="BD18" s="8">
+      <c r="BD18" s="6">
         <v>2.1700000000000001E-3</v>
       </c>
       <c r="BE18" t="s">
@@ -6920,7 +6925,7 @@
       <c r="BG18" t="s">
         <v>241</v>
       </c>
-      <c r="BH18" s="9">
+      <c r="BH18" s="7">
         <v>2.5700000000000001E-2</v>
       </c>
       <c r="BI18" t="s">
@@ -6929,7 +6934,7 @@
       <c r="BJ18">
         <v>13</v>
       </c>
-      <c r="BK18" s="9">
+      <c r="BK18" s="7">
         <v>1.6799999999999999E-2</v>
       </c>
       <c r="BL18" t="s">
@@ -6938,7 +6943,7 @@
       <c r="BM18">
         <v>8</v>
       </c>
-      <c r="BN18" s="9">
+      <c r="BN18" s="7">
         <v>1.9800000000000002E-2</v>
       </c>
       <c r="BO18" t="s">
@@ -6947,7 +6952,7 @@
       <c r="BP18">
         <v>8</v>
       </c>
-      <c r="BQ18" s="11">
+      <c r="BQ18" s="9">
         <v>0</v>
       </c>
       <c r="BR18" t="s">
@@ -6956,7 +6961,7 @@
       <c r="BS18">
         <v>0</v>
       </c>
-      <c r="BT18" s="9">
+      <c r="BT18" s="7">
         <v>3.4099999999999998E-2</v>
       </c>
       <c r="BU18" t="s">
@@ -6986,7 +6991,7 @@
       <c r="CC18" t="s">
         <v>120</v>
       </c>
-      <c r="CD18" s="9">
+      <c r="CD18" s="7">
         <v>1.5599999999999999E-2</v>
       </c>
       <c r="CE18">
@@ -6995,7 +7000,7 @@
       <c r="CF18" t="s">
         <v>184</v>
       </c>
-      <c r="CG18" s="11">
+      <c r="CG18" s="9">
         <v>0</v>
       </c>
       <c r="CH18" t="s">
@@ -7013,75 +7018,75 @@
       <c r="CL18" t="s">
         <v>208</v>
       </c>
-      <c r="CM18" s="9">
+      <c r="CM18" s="7">
         <v>0.97189999999999999</v>
       </c>
-      <c r="CN18" s="9">
+      <c r="CN18" s="7">
         <v>0.64219999999999999</v>
       </c>
-      <c r="CO18" s="10">
+      <c r="CO18" s="8">
         <v>1431</v>
       </c>
-      <c r="CP18" s="9">
+      <c r="CP18" s="7">
         <v>0.96209999999999996</v>
       </c>
-      <c r="CQ18" s="9">
+      <c r="CQ18" s="7">
         <v>0.96209999999999996</v>
       </c>
-      <c r="CR18" s="9">
-        <v>0</v>
-      </c>
-      <c r="CS18" s="9">
-        <v>0</v>
-      </c>
-      <c r="CT18" s="9">
-        <v>0</v>
-      </c>
-      <c r="CU18" s="9">
-        <v>0</v>
-      </c>
-      <c r="CV18" s="9">
-        <v>0</v>
-      </c>
-      <c r="CW18" s="9">
-        <v>0</v>
-      </c>
-      <c r="CX18" s="9">
+      <c r="CR18" s="7">
+        <v>0</v>
+      </c>
+      <c r="CS18" s="7">
+        <v>0</v>
+      </c>
+      <c r="CT18" s="7">
+        <v>0</v>
+      </c>
+      <c r="CU18" s="7">
+        <v>0</v>
+      </c>
+      <c r="CV18" s="7">
+        <v>0</v>
+      </c>
+      <c r="CW18" s="7">
+        <v>0</v>
+      </c>
+      <c r="CX18" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:102" x14ac:dyDescent="0.2">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="30" t="s">
         <v>168</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="31">
         <v>368</v>
       </c>
-      <c r="D19" t="s">
-        <v>50</v>
-      </c>
-      <c r="E19" t="s">
+      <c r="D19" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="E19" s="31" t="s">
         <v>169</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F19" s="31" t="s">
         <v>170</v>
       </c>
-      <c r="G19" s="7">
+      <c r="G19" s="32">
         <v>44292</v>
       </c>
-      <c r="H19" s="8">
+      <c r="H19" s="33">
         <v>0.35</v>
       </c>
-      <c r="I19" s="8">
+      <c r="I19" s="33">
         <v>0.2</v>
       </c>
-      <c r="J19" s="8">
+      <c r="J19" s="33">
         <v>234070256.94</v>
       </c>
-      <c r="K19" s="7">
+      <c r="K19" s="5">
         <v>45873</v>
       </c>
       <c r="L19" t="s">
@@ -7102,25 +7107,25 @@
       <c r="Q19" t="s">
         <v>92</v>
       </c>
-      <c r="R19" s="8">
+      <c r="R19" s="6">
         <v>3.3755000000000002</v>
       </c>
-      <c r="S19" s="7">
-        <v>45838</v>
-      </c>
-      <c r="T19" s="8">
+      <c r="S19" s="5">
+        <v>45838</v>
+      </c>
+      <c r="T19" s="6">
         <v>17.822240078731152</v>
       </c>
-      <c r="U19" s="7">
+      <c r="U19" s="5">
         <v>45873</v>
       </c>
-      <c r="V19" s="8">
+      <c r="V19" s="6">
         <v>19.11</v>
       </c>
-      <c r="W19" s="8">
+      <c r="W19" s="6">
         <v>17.84</v>
       </c>
-      <c r="X19" s="8">
+      <c r="X19" s="6">
         <v>14.14</v>
       </c>
       <c r="Y19" t="s">
@@ -7129,19 +7134,19 @@
       <c r="Z19" t="s">
         <v>50</v>
       </c>
-      <c r="AA19" s="8">
+      <c r="AA19" s="6">
         <v>5.86</v>
       </c>
-      <c r="AB19" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AC19" s="8">
+      <c r="AB19" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AC19" s="6">
         <v>19.170000000000002</v>
       </c>
-      <c r="AD19" s="8">
+      <c r="AD19" s="6">
         <v>17.72</v>
       </c>
-      <c r="AE19" s="8">
+      <c r="AE19" s="6">
         <v>14.12</v>
       </c>
       <c r="AF19" t="s">
@@ -7150,19 +7155,19 @@
       <c r="AG19" t="s">
         <v>50</v>
       </c>
-      <c r="AH19" s="8">
+      <c r="AH19" s="6">
         <v>5.84</v>
       </c>
-      <c r="AI19" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AJ19" s="8">
+      <c r="AI19" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AJ19" s="6">
         <v>16.489999999999998</v>
       </c>
-      <c r="AK19" s="8">
+      <c r="AK19" s="6">
         <v>12.14</v>
       </c>
-      <c r="AL19" s="8">
+      <c r="AL19" s="6">
         <v>11.44</v>
       </c>
       <c r="AM19" t="s">
@@ -7171,19 +7176,19 @@
       <c r="AN19" t="s">
         <v>50</v>
       </c>
-      <c r="AO19" s="8">
+      <c r="AO19" s="6">
         <v>5.2</v>
       </c>
-      <c r="AP19" s="7">
+      <c r="AP19" s="5">
         <v>45869</v>
       </c>
-      <c r="AQ19" s="8">
+      <c r="AQ19" s="6">
         <v>19.170000000000002</v>
       </c>
-      <c r="AR19" s="8">
+      <c r="AR19" s="6">
         <v>17.72</v>
       </c>
-      <c r="AS19" s="8">
+      <c r="AS19" s="6">
         <v>14.12</v>
       </c>
       <c r="AT19" t="s">
@@ -7192,31 +7197,31 @@
       <c r="AU19" t="s">
         <v>50</v>
       </c>
-      <c r="AV19" s="8">
+      <c r="AV19" s="6">
         <v>5.84</v>
       </c>
-      <c r="AW19" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AX19" s="8">
+      <c r="AW19" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AX19" s="6">
         <v>3.3755000000000002</v>
       </c>
-      <c r="AY19" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AZ19" s="8">
+      <c r="AY19" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AZ19" s="6">
         <v>2.4266000000000001</v>
       </c>
-      <c r="BA19" s="8">
+      <c r="BA19" s="6">
         <v>2.2774999999999999</v>
       </c>
-      <c r="BB19" s="7">
+      <c r="BB19" s="5">
         <v>45838</v>
       </c>
       <c r="BC19" t="s">
         <v>50</v>
       </c>
-      <c r="BD19" s="8">
+      <c r="BD19" s="6">
         <v>6.8900000000000003E-3</v>
       </c>
       <c r="BE19" t="s">
@@ -7228,7 +7233,7 @@
       <c r="BG19" t="s">
         <v>242</v>
       </c>
-      <c r="BH19" s="9">
+      <c r="BH19" s="7">
         <v>9.8400000000000001E-2</v>
       </c>
       <c r="BI19" t="s">
@@ -7237,7 +7242,7 @@
       <c r="BJ19">
         <v>36</v>
       </c>
-      <c r="BK19" s="9">
+      <c r="BK19" s="7">
         <v>4.2599999999999999E-2</v>
       </c>
       <c r="BL19" t="s">
@@ -7246,7 +7251,7 @@
       <c r="BM19">
         <v>10</v>
       </c>
-      <c r="BN19" s="11">
+      <c r="BN19" s="9">
         <v>0.17</v>
       </c>
       <c r="BO19" t="s">
@@ -7255,7 +7260,7 @@
       <c r="BP19">
         <v>44</v>
       </c>
-      <c r="BQ19" s="9">
+      <c r="BQ19" s="7">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="BR19" t="s">
@@ -7264,7 +7269,7 @@
       <c r="BS19">
         <v>1</v>
       </c>
-      <c r="BT19" s="9">
+      <c r="BT19" s="7">
         <v>4.5199999999999997E-2</v>
       </c>
       <c r="BU19" t="s">
@@ -7294,7 +7299,7 @@
       <c r="CC19" t="s">
         <v>119</v>
       </c>
-      <c r="CD19" s="9">
+      <c r="CD19" s="7">
         <v>0.1598</v>
       </c>
       <c r="CE19">
@@ -7303,7 +7308,7 @@
       <c r="CF19" t="s">
         <v>186</v>
       </c>
-      <c r="CG19" s="9">
+      <c r="CG19" s="7">
         <v>4.2500000000000003E-2</v>
       </c>
       <c r="CH19" t="s">
@@ -7321,75 +7326,75 @@
       <c r="CL19" t="s">
         <v>202</v>
       </c>
-      <c r="CM19" s="9">
+      <c r="CM19" s="7">
         <v>1</v>
       </c>
-      <c r="CN19" s="9">
+      <c r="CN19" s="7">
         <v>0.91679999999999995</v>
       </c>
       <c r="CO19">
         <v>853</v>
       </c>
-      <c r="CP19" s="9">
+      <c r="CP19" s="7">
         <v>0.98299999999999998</v>
       </c>
-      <c r="CQ19" s="9">
+      <c r="CQ19" s="7">
         <v>0.98299999999999998</v>
       </c>
-      <c r="CR19" s="9">
-        <v>0</v>
-      </c>
-      <c r="CS19" s="9">
+      <c r="CR19" s="7">
+        <v>0</v>
+      </c>
+      <c r="CS19" s="7">
         <v>1.6000000000000001E-3</v>
       </c>
-      <c r="CT19" s="9">
-        <v>0</v>
-      </c>
-      <c r="CU19" s="9">
-        <v>0</v>
-      </c>
-      <c r="CV19" s="9">
-        <v>0</v>
-      </c>
-      <c r="CW19" s="9">
-        <v>0</v>
-      </c>
-      <c r="CX19" s="9">
+      <c r="CT19" s="7">
+        <v>0</v>
+      </c>
+      <c r="CU19" s="7">
+        <v>0</v>
+      </c>
+      <c r="CV19" s="7">
+        <v>0</v>
+      </c>
+      <c r="CW19" s="7">
+        <v>0</v>
+      </c>
+      <c r="CX19" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:102" x14ac:dyDescent="0.2">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="30" t="s">
         <v>171</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="30" t="s">
         <v>172</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="31">
         <v>469</v>
       </c>
-      <c r="D20" t="s">
-        <v>50</v>
-      </c>
-      <c r="E20" t="s">
+      <c r="D20" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="E20" s="31" t="s">
         <v>173</v>
       </c>
-      <c r="F20" t="s">
+      <c r="F20" s="31" t="s">
         <v>174</v>
       </c>
-      <c r="G20" s="7">
+      <c r="G20" s="32">
         <v>45308</v>
       </c>
-      <c r="H20" s="8">
+      <c r="H20" s="33">
         <v>0.12</v>
       </c>
-      <c r="I20" s="8">
+      <c r="I20" s="33">
         <v>0.12</v>
       </c>
-      <c r="J20" s="8">
+      <c r="J20" s="33">
         <v>208173774.78999999</v>
       </c>
-      <c r="K20" s="7">
+      <c r="K20" s="5">
         <v>45873</v>
       </c>
       <c r="L20" t="s">
@@ -7410,22 +7415,22 @@
       <c r="Q20" t="s">
         <v>49</v>
       </c>
-      <c r="R20" s="8">
+      <c r="R20" s="6">
         <v>2.4300000000000002</v>
       </c>
-      <c r="S20" s="7">
-        <v>45838</v>
-      </c>
-      <c r="T20" s="8">
+      <c r="S20" s="5">
+        <v>45838</v>
+      </c>
+      <c r="T20" s="6">
         <v>17.493104225841936</v>
       </c>
-      <c r="U20" s="7">
+      <c r="U20" s="5">
         <v>45873</v>
       </c>
-      <c r="V20" s="8">
+      <c r="V20" s="6">
         <v>19.29</v>
       </c>
-      <c r="W20" s="8">
+      <c r="W20" s="6">
         <v>18.73</v>
       </c>
       <c r="X20" t="s">
@@ -7437,16 +7442,16 @@
       <c r="Z20" t="s">
         <v>50</v>
       </c>
-      <c r="AA20" s="8">
+      <c r="AA20" s="6">
         <v>18.37</v>
       </c>
-      <c r="AB20" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AC20" s="8">
+      <c r="AB20" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AC20" s="6">
         <v>19.48</v>
       </c>
-      <c r="AD20" s="8">
+      <c r="AD20" s="6">
         <v>18.739999999999998</v>
       </c>
       <c r="AE20" t="s">
@@ -7458,16 +7463,16 @@
       <c r="AG20" t="s">
         <v>50</v>
       </c>
-      <c r="AH20" s="8">
+      <c r="AH20" s="6">
         <v>18.62</v>
       </c>
-      <c r="AI20" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AJ20" s="8">
+      <c r="AI20" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AJ20" s="6">
         <v>15.86</v>
       </c>
-      <c r="AK20" s="8">
+      <c r="AK20" s="6">
         <v>11.26</v>
       </c>
       <c r="AL20" t="s">
@@ -7479,16 +7484,16 @@
       <c r="AN20" t="s">
         <v>50</v>
       </c>
-      <c r="AO20" s="8">
+      <c r="AO20" s="6">
         <v>15.07</v>
       </c>
-      <c r="AP20" s="7">
+      <c r="AP20" s="5">
         <v>45869</v>
       </c>
-      <c r="AQ20" s="8">
+      <c r="AQ20" s="6">
         <v>19.48</v>
       </c>
-      <c r="AR20" s="8">
+      <c r="AR20" s="6">
         <v>18.739999999999998</v>
       </c>
       <c r="AS20" t="s">
@@ -7500,31 +7505,31 @@
       <c r="AU20" t="s">
         <v>50</v>
       </c>
-      <c r="AV20" s="8">
+      <c r="AV20" s="6">
         <v>18.62</v>
       </c>
-      <c r="AW20" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AX20" s="8">
+      <c r="AW20" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AX20" s="6">
         <v>2.4300000000000002</v>
       </c>
-      <c r="AY20" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AZ20" s="8">
+      <c r="AY20" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AZ20" s="6">
         <v>2.2042999999999999</v>
       </c>
-      <c r="BA20" s="8">
+      <c r="BA20" s="6">
         <v>2.2042999999999999</v>
       </c>
-      <c r="BB20" s="7">
+      <c r="BB20" s="5">
         <v>45838</v>
       </c>
       <c r="BC20" t="s">
         <v>50</v>
       </c>
-      <c r="BD20" s="8">
+      <c r="BD20" s="6">
         <v>1.7799999999999999E-3</v>
       </c>
       <c r="BE20" t="s">
@@ -7536,7 +7541,7 @@
       <c r="BG20" t="s">
         <v>243</v>
       </c>
-      <c r="BH20" s="9">
+      <c r="BH20" s="7">
         <v>2.1600000000000001E-2</v>
       </c>
       <c r="BI20" t="s">
@@ -7545,7 +7550,7 @@
       <c r="BJ20">
         <v>9</v>
       </c>
-      <c r="BK20" s="9">
+      <c r="BK20" s="7">
         <v>2.8799999999999999E-2</v>
       </c>
       <c r="BL20" t="s">
@@ -7554,7 +7559,7 @@
       <c r="BM20">
         <v>12</v>
       </c>
-      <c r="BN20" s="11">
+      <c r="BN20" s="9">
         <v>0.11</v>
       </c>
       <c r="BO20" t="s">
@@ -7563,7 +7568,7 @@
       <c r="BP20">
         <v>40</v>
       </c>
-      <c r="BQ20" s="9">
+      <c r="BQ20" s="7">
         <v>8.3000000000000001E-3</v>
       </c>
       <c r="BR20" t="s">
@@ -7572,7 +7577,7 @@
       <c r="BS20">
         <v>1</v>
       </c>
-      <c r="BT20" s="9">
+      <c r="BT20" s="7">
         <v>1.6500000000000001E-2</v>
       </c>
       <c r="BU20" t="s">
@@ -7602,7 +7607,7 @@
       <c r="CC20" t="s">
         <v>119</v>
       </c>
-      <c r="CD20" s="9">
+      <c r="CD20" s="7">
         <v>0.14249999999999999</v>
       </c>
       <c r="CE20">
@@ -7611,7 +7616,7 @@
       <c r="CF20" t="s">
         <v>188</v>
       </c>
-      <c r="CG20" s="11">
+      <c r="CG20" s="9">
         <v>0</v>
       </c>
       <c r="CH20" t="s">
@@ -7629,19 +7634,19 @@
       <c r="CL20" t="s">
         <v>224</v>
       </c>
-      <c r="CM20" s="9">
+      <c r="CM20" s="7">
         <v>1</v>
       </c>
-      <c r="CN20" s="9">
+      <c r="CN20" s="7">
         <v>0.90149999999999997</v>
       </c>
       <c r="CO20">
         <v>853</v>
       </c>
-      <c r="CP20" s="9">
+      <c r="CP20" s="7">
         <v>0.99319999999999997</v>
       </c>
-      <c r="CQ20" s="9">
+      <c r="CQ20" s="7">
         <v>0.99319999999999997</v>
       </c>
       <c r="CR20" t="s">
@@ -7667,37 +7672,37 @@
       </c>
     </row>
     <row r="21" spans="1:102" x14ac:dyDescent="0.2">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="30" t="s">
         <v>175</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="30" t="s">
         <v>176</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="31">
         <v>150</v>
       </c>
-      <c r="D21" t="s">
-        <v>50</v>
-      </c>
-      <c r="E21" t="s">
+      <c r="D21" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="E21" s="31" t="s">
         <v>177</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F21" s="31" t="s">
         <v>178</v>
       </c>
-      <c r="G21" s="7">
+      <c r="G21" s="32">
         <v>42480</v>
       </c>
-      <c r="H21" s="8">
+      <c r="H21" s="33">
         <v>0.49</v>
       </c>
-      <c r="I21" s="8">
+      <c r="I21" s="33">
         <v>0.49</v>
       </c>
-      <c r="J21" s="8">
+      <c r="J21" s="33">
         <v>167008602.28999999</v>
       </c>
-      <c r="K21" s="7">
+      <c r="K21" s="5">
         <v>45873</v>
       </c>
       <c r="L21" t="s">
@@ -7718,121 +7723,121 @@
       <c r="Q21" t="s">
         <v>49</v>
       </c>
-      <c r="R21" s="8">
+      <c r="R21" s="6">
         <v>1.8673</v>
       </c>
-      <c r="S21" s="7">
-        <v>45838</v>
-      </c>
-      <c r="T21" s="8">
+      <c r="S21" s="5">
+        <v>45838</v>
+      </c>
+      <c r="T21" s="6">
         <v>11.626358995466866</v>
       </c>
-      <c r="U21" s="7">
+      <c r="U21" s="5">
         <v>45873</v>
       </c>
-      <c r="V21" s="8">
+      <c r="V21" s="6">
         <v>6.8</v>
       </c>
-      <c r="W21" s="8">
+      <c r="W21" s="6">
         <v>3.11</v>
       </c>
-      <c r="X21" s="8">
+      <c r="X21" s="6">
         <v>0.24</v>
       </c>
-      <c r="Y21" s="8">
+      <c r="Y21" s="6">
         <v>4.13</v>
       </c>
       <c r="Z21" t="s">
         <v>50</v>
       </c>
-      <c r="AA21" s="8">
+      <c r="AA21" s="6">
         <v>6.95</v>
       </c>
-      <c r="AB21" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AC21" s="8">
+      <c r="AB21" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AC21" s="6">
         <v>7.16</v>
       </c>
-      <c r="AD21" s="8">
+      <c r="AD21" s="6">
         <v>2.97</v>
       </c>
-      <c r="AE21" s="8">
+      <c r="AE21" s="6">
         <v>0.14000000000000001</v>
       </c>
-      <c r="AF21" s="8">
+      <c r="AF21" s="6">
         <v>3.94</v>
       </c>
       <c r="AG21" t="s">
         <v>50</v>
       </c>
-      <c r="AH21" s="8">
+      <c r="AH21" s="6">
         <v>6.91</v>
       </c>
-      <c r="AI21" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AJ21" s="8">
+      <c r="AI21" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AJ21" s="6">
         <v>9.8699999999999992</v>
       </c>
-      <c r="AK21" s="8">
+      <c r="AK21" s="6">
         <v>2.5299999999999998</v>
       </c>
-      <c r="AL21" s="8">
+      <c r="AL21" s="6">
         <v>0.01</v>
       </c>
-      <c r="AM21" s="8">
+      <c r="AM21" s="6">
         <v>3.13</v>
       </c>
       <c r="AN21" t="s">
         <v>50</v>
       </c>
-      <c r="AO21" s="8">
+      <c r="AO21" s="6">
         <v>7.21</v>
       </c>
-      <c r="AP21" s="7">
+      <c r="AP21" s="5">
         <v>45869</v>
       </c>
-      <c r="AQ21" s="8">
+      <c r="AQ21" s="6">
         <v>7.16</v>
       </c>
-      <c r="AR21" s="8">
+      <c r="AR21" s="6">
         <v>2.97</v>
       </c>
-      <c r="AS21" s="8">
+      <c r="AS21" s="6">
         <v>0.14000000000000001</v>
       </c>
-      <c r="AT21" s="8">
+      <c r="AT21" s="6">
         <v>3.94</v>
       </c>
       <c r="AU21" t="s">
         <v>50</v>
       </c>
-      <c r="AV21" s="8">
+      <c r="AV21" s="6">
         <v>6.91</v>
       </c>
-      <c r="AW21" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AX21" s="8">
+      <c r="AW21" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AX21" s="6">
         <v>1.8673</v>
       </c>
-      <c r="AY21" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AZ21" s="8">
+      <c r="AY21" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AZ21" s="6">
         <v>1.7462</v>
       </c>
-      <c r="BA21" s="8">
+      <c r="BA21" s="6">
         <v>1.7462</v>
       </c>
-      <c r="BB21" s="7">
+      <c r="BB21" s="5">
         <v>45838</v>
       </c>
       <c r="BC21" t="s">
         <v>50</v>
       </c>
-      <c r="BD21" s="8">
+      <c r="BD21" s="6">
         <v>7.7999999999999999E-4</v>
       </c>
       <c r="BE21" t="s">
@@ -7844,7 +7849,7 @@
       <c r="BG21" t="s">
         <v>244</v>
       </c>
-      <c r="BH21" s="9">
+      <c r="BH21" s="7">
         <v>4.1999999999999997E-3</v>
       </c>
       <c r="BI21" t="s">
@@ -7853,7 +7858,7 @@
       <c r="BJ21">
         <v>2</v>
       </c>
-      <c r="BK21" s="11">
+      <c r="BK21" s="9">
         <v>0</v>
       </c>
       <c r="BL21" t="s">
@@ -7862,7 +7867,7 @@
       <c r="BM21">
         <v>0</v>
       </c>
-      <c r="BN21" s="11">
+      <c r="BN21" s="9">
         <v>0.16</v>
       </c>
       <c r="BO21" t="s">
@@ -7871,7 +7876,7 @@
       <c r="BP21">
         <v>15</v>
       </c>
-      <c r="BQ21" s="11">
+      <c r="BQ21" s="9">
         <v>0</v>
       </c>
       <c r="BR21" t="s">
@@ -7880,7 +7885,7 @@
       <c r="BS21">
         <v>0</v>
       </c>
-      <c r="BT21" s="11">
+      <c r="BT21" s="9">
         <v>0</v>
       </c>
       <c r="BU21" t="s">
@@ -7910,7 +7915,7 @@
       <c r="CC21" t="s">
         <v>120</v>
       </c>
-      <c r="CD21" s="9">
+      <c r="CD21" s="7">
         <v>0.37190000000000001</v>
       </c>
       <c r="CE21">
@@ -7919,7 +7924,7 @@
       <c r="CF21" t="s">
         <v>190</v>
       </c>
-      <c r="CG21" s="11">
+      <c r="CG21" s="9">
         <v>0</v>
       </c>
       <c r="CH21" t="s">
@@ -7937,75 +7942,75 @@
       <c r="CL21" t="s">
         <v>208</v>
       </c>
-      <c r="CM21" s="9">
+      <c r="CM21" s="7">
         <v>1</v>
       </c>
-      <c r="CN21" s="9">
+      <c r="CN21" s="7">
         <v>0.84530000000000005</v>
       </c>
-      <c r="CO21" s="10">
+      <c r="CO21" s="8">
         <v>5449</v>
       </c>
-      <c r="CP21" s="9">
+      <c r="CP21" s="7">
         <v>0.96519999999999995</v>
       </c>
-      <c r="CQ21" s="9">
+      <c r="CQ21" s="7">
         <v>0.95389999999999997</v>
       </c>
-      <c r="CR21" s="9">
-        <v>0</v>
-      </c>
-      <c r="CS21" s="9">
-        <v>0</v>
-      </c>
-      <c r="CT21" s="9">
-        <v>0</v>
-      </c>
-      <c r="CU21" s="9">
-        <v>0</v>
-      </c>
-      <c r="CV21" s="9">
-        <v>0</v>
-      </c>
-      <c r="CW21" s="9">
-        <v>0</v>
-      </c>
-      <c r="CX21" s="9">
+      <c r="CR21" s="7">
+        <v>0</v>
+      </c>
+      <c r="CS21" s="7">
+        <v>0</v>
+      </c>
+      <c r="CT21" s="7">
+        <v>0</v>
+      </c>
+      <c r="CU21" s="7">
+        <v>0</v>
+      </c>
+      <c r="CV21" s="7">
+        <v>0</v>
+      </c>
+      <c r="CW21" s="7">
+        <v>0</v>
+      </c>
+      <c r="CX21" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:102" x14ac:dyDescent="0.2">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="30" t="s">
         <v>179</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="30" t="s">
         <v>180</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="31">
         <v>548</v>
       </c>
-      <c r="D22" t="s">
-        <v>50</v>
-      </c>
-      <c r="E22" t="s">
+      <c r="D22" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="E22" s="31" t="s">
         <v>181</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F22" s="31" t="s">
         <v>182</v>
       </c>
-      <c r="G22" s="7">
+      <c r="G22" s="32">
         <v>44110</v>
       </c>
-      <c r="H22" s="8">
+      <c r="H22" s="33">
         <v>0.17</v>
       </c>
-      <c r="I22" s="8">
+      <c r="I22" s="33">
         <v>0.17</v>
       </c>
-      <c r="J22" s="8">
+      <c r="J22" s="33">
         <v>106662263.48</v>
       </c>
-      <c r="K22" s="7">
+      <c r="K22" s="5">
         <v>45873</v>
       </c>
       <c r="L22" t="s">
@@ -8026,25 +8031,25 @@
       <c r="Q22" t="s">
         <v>49</v>
       </c>
-      <c r="R22" s="8">
+      <c r="R22" s="6">
         <v>3.0811000000000002</v>
       </c>
-      <c r="S22" s="7">
-        <v>45838</v>
-      </c>
-      <c r="T22" s="8">
+      <c r="S22" s="5">
+        <v>45838</v>
+      </c>
+      <c r="T22" s="6">
         <v>16.508225840647377</v>
       </c>
-      <c r="U22" s="7">
+      <c r="U22" s="5">
         <v>45873</v>
       </c>
-      <c r="V22" s="8">
+      <c r="V22" s="6">
         <v>16.14</v>
       </c>
-      <c r="W22" s="8">
+      <c r="W22" s="6">
         <v>20.05</v>
       </c>
-      <c r="X22" s="8">
+      <c r="X22" s="6">
         <v>8.39</v>
       </c>
       <c r="Y22" t="s">
@@ -8053,19 +8058,19 @@
       <c r="Z22" t="s">
         <v>50</v>
       </c>
-      <c r="AA22" s="8">
+      <c r="AA22" s="6">
         <v>6.42</v>
       </c>
-      <c r="AB22" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AC22" s="8">
+      <c r="AB22" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AC22" s="6">
         <v>16.510000000000002</v>
       </c>
-      <c r="AD22" s="8">
+      <c r="AD22" s="6">
         <v>20.76</v>
       </c>
-      <c r="AE22" s="8">
+      <c r="AE22" s="6">
         <v>8.52</v>
       </c>
       <c r="AF22" t="s">
@@ -8074,19 +8079,19 @@
       <c r="AG22" t="s">
         <v>50</v>
       </c>
-      <c r="AH22" s="8">
+      <c r="AH22" s="6">
         <v>6.57</v>
       </c>
-      <c r="AI22" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AJ22" s="8">
+      <c r="AI22" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AJ22" s="6">
         <v>16.28</v>
       </c>
-      <c r="AK22" s="8">
+      <c r="AK22" s="6">
         <v>18.87</v>
       </c>
-      <c r="AL22" s="8">
+      <c r="AL22" s="6">
         <v>8.85</v>
       </c>
       <c r="AM22" t="s">
@@ -8095,19 +8100,19 @@
       <c r="AN22" t="s">
         <v>50</v>
       </c>
-      <c r="AO22" s="8">
+      <c r="AO22" s="6">
         <v>6.33</v>
       </c>
-      <c r="AP22" s="7">
+      <c r="AP22" s="5">
         <v>45869</v>
       </c>
-      <c r="AQ22" s="8">
+      <c r="AQ22" s="6">
         <v>16.510000000000002</v>
       </c>
-      <c r="AR22" s="8">
+      <c r="AR22" s="6">
         <v>20.76</v>
       </c>
-      <c r="AS22" s="8">
+      <c r="AS22" s="6">
         <v>8.52</v>
       </c>
       <c r="AT22" t="s">
@@ -8116,31 +8121,31 @@
       <c r="AU22" t="s">
         <v>50</v>
       </c>
-      <c r="AV22" s="8">
+      <c r="AV22" s="6">
         <v>6.57</v>
       </c>
-      <c r="AW22" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AX22" s="8">
+      <c r="AW22" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AX22" s="6">
         <v>3.0811000000000002</v>
       </c>
-      <c r="AY22" s="7">
-        <v>45838</v>
-      </c>
-      <c r="AZ22" s="8">
+      <c r="AY22" s="5">
+        <v>45838</v>
+      </c>
+      <c r="AZ22" s="6">
         <v>2.4649999999999999</v>
       </c>
-      <c r="BA22" s="8">
+      <c r="BA22" s="6">
         <v>2.4649999999999999</v>
       </c>
-      <c r="BB22" s="7">
+      <c r="BB22" s="5">
         <v>45838</v>
       </c>
       <c r="BC22" t="s">
         <v>50</v>
       </c>
-      <c r="BD22" s="8">
+      <c r="BD22" s="6">
         <v>2.7699999999999999E-3</v>
       </c>
       <c r="BE22" t="s">
@@ -8152,7 +8157,7 @@
       <c r="BG22" t="s">
         <v>239</v>
       </c>
-      <c r="BH22" s="9">
+      <c r="BH22" s="7">
         <v>1.5299999999999999E-2</v>
       </c>
       <c r="BI22" t="s">
@@ -8161,7 +8166,7 @@
       <c r="BJ22">
         <v>7</v>
       </c>
-      <c r="BK22" s="11">
+      <c r="BK22" s="9">
         <v>0</v>
       </c>
       <c r="BL22" t="s">
@@ -8170,7 +8175,7 @@
       <c r="BM22">
         <v>0</v>
       </c>
-      <c r="BN22" s="9">
+      <c r="BN22" s="7">
         <v>5.7700000000000001E-2</v>
       </c>
       <c r="BO22" t="s">
@@ -8179,7 +8184,7 @@
       <c r="BP22">
         <v>27</v>
       </c>
-      <c r="BQ22" s="11">
+      <c r="BQ22" s="9">
         <v>0</v>
       </c>
       <c r="BR22" t="s">
@@ -8188,7 +8193,7 @@
       <c r="BS22">
         <v>0</v>
       </c>
-      <c r="BT22" s="9">
+      <c r="BT22" s="7">
         <v>1.55E-2</v>
       </c>
       <c r="BU22" t="s">
@@ -8218,7 +8223,7 @@
       <c r="CC22" t="s">
         <v>120</v>
       </c>
-      <c r="CD22" s="9">
+      <c r="CD22" s="7">
         <v>8.3799999999999999E-2</v>
       </c>
       <c r="CE22">
@@ -8227,7 +8232,7 @@
       <c r="CF22" t="s">
         <v>192</v>
       </c>
-      <c r="CG22" s="11">
+      <c r="CG22" s="9">
         <v>0</v>
       </c>
       <c r="CH22" t="s">
@@ -8245,66 +8250,48 @@
       <c r="CL22" t="s">
         <v>208</v>
       </c>
-      <c r="CM22" s="9">
+      <c r="CM22" s="7">
         <v>1</v>
       </c>
-      <c r="CN22" s="9">
+      <c r="CN22" s="7">
         <v>0.97030000000000005</v>
       </c>
-      <c r="CO22" s="10">
+      <c r="CO22" s="8">
         <v>1314</v>
       </c>
-      <c r="CP22" s="9">
+      <c r="CP22" s="7">
         <v>0.99319999999999997</v>
       </c>
-      <c r="CQ22" s="9">
+      <c r="CQ22" s="7">
         <v>0.97819999999999996</v>
       </c>
-      <c r="CR22" s="9">
-        <v>0</v>
-      </c>
-      <c r="CS22" s="9">
-        <v>0</v>
-      </c>
-      <c r="CT22" s="9">
-        <v>0</v>
-      </c>
-      <c r="CU22" s="9">
-        <v>0</v>
-      </c>
-      <c r="CV22" s="9">
-        <v>0</v>
-      </c>
-      <c r="CW22" s="9">
-        <v>0</v>
-      </c>
-      <c r="CX22" s="9">
+      <c r="CR22" s="7">
+        <v>0</v>
+      </c>
+      <c r="CS22" s="7">
+        <v>0</v>
+      </c>
+      <c r="CT22" s="7">
+        <v>0</v>
+      </c>
+      <c r="CU22" s="7">
+        <v>0</v>
+      </c>
+      <c r="CV22" s="7">
+        <v>0</v>
+      </c>
+      <c r="CW22" s="7">
+        <v>0</v>
+      </c>
+      <c r="CX22" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:102" ht="18" x14ac:dyDescent="0.2">
-      <c r="BV26" s="14"/>
+      <c r="BV26" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="CD1:CF1"/>
-    <mergeCell ref="AC1:AI1"/>
-    <mergeCell ref="AJ1:AP1"/>
-    <mergeCell ref="AQ1:AW1"/>
-    <mergeCell ref="AX1:BB1"/>
-    <mergeCell ref="BC1:BF1"/>
-    <mergeCell ref="BH1:BJ1"/>
-    <mergeCell ref="BW1:CC1"/>
-    <mergeCell ref="BG1:BG2"/>
-    <mergeCell ref="BK1:BM1"/>
-    <mergeCell ref="BN1:BP1"/>
-    <mergeCell ref="BQ1:BS1"/>
-    <mergeCell ref="BT1:BV1"/>
-    <mergeCell ref="N1:N2"/>
-    <mergeCell ref="O1:O2"/>
-    <mergeCell ref="P1:P2"/>
-    <mergeCell ref="Q1:Q2"/>
-    <mergeCell ref="R1:U1"/>
     <mergeCell ref="CH1:CQ1"/>
     <mergeCell ref="CR1:CX1"/>
     <mergeCell ref="G1:G2"/>
@@ -8321,6 +8308,24 @@
     <mergeCell ref="K1:K2"/>
     <mergeCell ref="L1:L2"/>
     <mergeCell ref="M1:M2"/>
+    <mergeCell ref="N1:N2"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="P1:P2"/>
+    <mergeCell ref="Q1:Q2"/>
+    <mergeCell ref="R1:U1"/>
+    <mergeCell ref="CD1:CF1"/>
+    <mergeCell ref="AC1:AI1"/>
+    <mergeCell ref="AJ1:AP1"/>
+    <mergeCell ref="AQ1:AW1"/>
+    <mergeCell ref="AX1:BB1"/>
+    <mergeCell ref="BC1:BF1"/>
+    <mergeCell ref="BH1:BJ1"/>
+    <mergeCell ref="BW1:CC1"/>
+    <mergeCell ref="BG1:BG2"/>
+    <mergeCell ref="BK1:BM1"/>
+    <mergeCell ref="BN1:BP1"/>
+    <mergeCell ref="BQ1:BS1"/>
+    <mergeCell ref="BT1:BV1"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <hyperlinks>
